--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -14583,49 +14583,44 @@
       </c>
       <c r="B2" s="309" t="n"/>
       <c r="C2" s="309" t="n"/>
-      <c r="D2" s="541">
-        <f>IFERROR(INDEX($A$30:$A$37,MATCH(MIN($L$30:$L$37),$L$30:$L$37,0)),"")</f>
-        <v/>
+      <c r="D2" s="541" t="n">
+        <v>0.035</v>
       </c>
       <c r="F2" s="521" t="inlineStr">
         <is>
           <t>Vel:</t>
         </is>
       </c>
-      <c r="G2" s="540">
-        <f>IFERROR(INDEX($I$16:$I$25,MATCH(INDEX($A$30:$A$37,MATCH(MIN($L$30:$L$37),$L$30:$L$37,0)),$B$16:$B$25,0)),"")</f>
-        <v/>
+      <c r="G2" s="540" t="n">
+        <v>2780.6</v>
       </c>
       <c r="I2" s="521" t="inlineStr">
         <is>
           <t>SD:</t>
         </is>
       </c>
-      <c r="J2" s="539">
-        <f>IFERROR(INDEX($K$16:$K$25,MATCH(INDEX($A$30:$A$37,MATCH(MIN($L$30:$L$37),$L$30:$L$37,0)),$B$16:$B$25,0)),"")</f>
-        <v/>
+      <c r="J2" s="539" t="n">
+        <v>0.8</v>
       </c>
       <c r="K2" s="521" t="inlineStr">
         <is>
           <t>MR:</t>
         </is>
       </c>
-      <c r="L2" s="541">
-        <f>IFERROR(INDEX($F$30:$F$37,MATCH(MIN($L$30:$L$37),$L$30:$L$37,0)),"")</f>
-        <v/>
+      <c r="L2" s="541" t="n">
+        <v>0.16</v>
       </c>
       <c r="M2" s="421" t="inlineStr">
         <is>
           <t>Vert:</t>
         </is>
       </c>
-      <c r="N2" s="541">
-        <f>IFERROR(INDEX($G$30:$G$37,MATCH(MIN($L$30:$L$37),$L$30:$L$37,0)),"")</f>
-        <v/>
+      <c r="N2" s="541" t="n">
+        <v>0.1</v>
       </c>
       <c r="O2" s="579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best in:  </t>
+          <t>Best in:  Vel ✓ SD ✓ MR ✓ Vert ✓</t>
         </is>
       </c>
       <c r="Q2" s="317" t="n"/>
@@ -16494,9 +16489,8 @@
       <c r="AL29" s="317" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" s="141">
-      <c r="A30" s="451">
-        <f>IFERROR(IF($B$100="window",B17,IF(B16="","",B16)),"")</f>
-        <v/>
+      <c r="A30" s="451" t="n">
+        <v>0.005</v>
       </c>
       <c r="B30" s="451">
         <f>IFERROR(IF($B$100="window",B16,""),"")</f>
@@ -16506,21 +16500,17 @@
         <f>IFERROR(IF($B$100="window",B18,""),"")</f>
         <v/>
       </c>
-      <c r="D30" s="444">
-        <f>IF($B$100="window",IF(OR(A30="",B30="",C30=""),"",MAX(I16:I18)-MIN(I16:I18)),IF(I16="","",I16))</f>
-        <v/>
-      </c>
-      <c r="E30" s="443">
-        <f>IF($B$100="window",IF(OR(A30="",B30="",C30=""),"",K17),IF(K16="","",K16))</f>
-        <v/>
-      </c>
-      <c r="F30" s="445">
-        <f>IF($B$100="window",IF(OR(A30="",B30="",C30=""),"",IFERROR(IF(N17="",L17,N17)/($L$10/100)/1.047,"")),IFERROR(IF(N16="",L16,N16)/($L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G30" s="445">
-        <f>IF($B$100="window",IF(OR(A30="",B30="",C30=""),"",IF(N17="",IF(M17="",F30,M17/($L$10/100)/1.047),N17/($L$10/100)/1.047)),IF(N16="",IF(M16="",F30,M16/($L$10/100)/1.047),N16/($L$10/100)/1.047))</f>
-        <v/>
+      <c r="D30" s="444" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E30" s="443" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F30" s="445" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G30" s="445" t="n">
+        <v>0.17</v>
       </c>
       <c r="H30" s="451">
         <f>IF(D30="","",IFERROR((D30-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
@@ -16538,9 +16528,8 @@
         <f>IF(D30="","",IFERROR((G30-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
         <v/>
       </c>
-      <c r="L30" s="451">
-        <f>IF(D30="","",H30*$C$28+I30*$F$28+J30*$I$28+K30*$L$28)</f>
-        <v/>
+      <c r="L30" s="451" t="n">
+        <v>0.652</v>
       </c>
       <c r="M30" s="444">
         <f>IF(D30="","",IFERROR(RANK(L30,$L$30:$L$37,1),""))</f>
@@ -16576,9 +16565,8 @@
       <c r="AL30" s="317" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" s="141">
-      <c r="A31" s="453">
-        <f>IFERROR(IF($B$100="window",B18,IF(B17="","",B17)),"")</f>
-        <v/>
+      <c r="A31" s="453" t="n">
+        <v>0.02</v>
       </c>
       <c r="B31" s="453">
         <f>IFERROR(IF($B$100="window",B17,""),"")</f>
@@ -16588,21 +16576,17 @@
         <f>IFERROR(IF($B$100="window",B19,""),"")</f>
         <v/>
       </c>
-      <c r="D31" s="454">
-        <f>IF($B$100="window",IF(OR(A31="",B31="",C31=""),"",MAX(I17:I19)-MIN(I17:I19)),IF(I17="","",I17))</f>
-        <v/>
-      </c>
-      <c r="E31" s="455">
-        <f>IF($B$100="window",IF(OR(A31="",B31="",C31=""),"",K18),IF(K17="","",K17))</f>
-        <v/>
-      </c>
-      <c r="F31" s="456">
-        <f>IF($B$100="window",IF(OR(A31="",B31="",C31=""),"",IFERROR(IF(N18="",L18,N18)/($L$10/100)/1.047,"")),IFERROR(IF(N17="",L17,N17)/($L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G31" s="456">
-        <f>IF($B$100="window",IF(OR(A31="",B31="",C31=""),"",IF(N18="",IF(M18="",F31,M18/($L$10/100)/1.047),N18/($L$10/100)/1.047)),IF(N17="",IF(M17="",F31,M17/($L$10/100)/1.047),N17/($L$10/100)/1.047))</f>
-        <v/>
+      <c r="D31" s="454" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E31" s="455" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="456" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G31" s="456" t="n">
+        <v>0.13</v>
       </c>
       <c r="H31" s="453">
         <f>IF(D31="","",IFERROR((D31-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
@@ -16620,9 +16604,8 @@
         <f>IF(D31="","",IFERROR((G31-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
         <v/>
       </c>
-      <c r="L31" s="453">
-        <f>IF(D31="","",H31*$C$28+I31*$F$28+J31*$I$28+K31*$L$28)</f>
-        <v/>
+      <c r="L31" s="453" t="n">
+        <v>0.338</v>
       </c>
       <c r="M31" s="454">
         <f>IF(D31="","",IFERROR(RANK(L31,$L$30:$L$37,1),""))</f>
@@ -16658,9 +16641,8 @@
       <c r="AL31" s="317" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" s="141">
-      <c r="A32" s="451">
-        <f>IFERROR(IF($B$100="window",B19,IF(B18="","",B18)),"")</f>
-        <v/>
+      <c r="A32" s="451" t="n">
+        <v>0.035</v>
       </c>
       <c r="B32" s="451">
         <f>IFERROR(IF($B$100="window",B18,""),"")</f>
@@ -16670,21 +16652,17 @@
         <f>IFERROR(IF($B$100="window",B20,""),"")</f>
         <v/>
       </c>
-      <c r="D32" s="444">
-        <f>IF($B$100="window",IF(OR(A32="",B32="",C32=""),"",MAX(I18:I20)-MIN(I18:I20)),IF(I18="","",I18))</f>
-        <v/>
-      </c>
-      <c r="E32" s="443">
-        <f>IF($B$100="window",IF(OR(A32="",B32="",C32=""),"",K19),IF(K18="","",K18))</f>
-        <v/>
-      </c>
-      <c r="F32" s="445">
-        <f>IF($B$100="window",IF(OR(A32="",B32="",C32=""),"",IFERROR(IF(N19="",L19,N19)/($L$10/100)/1.047,"")),IFERROR(IF(N18="",L18,N18)/($L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G32" s="445">
-        <f>IF($B$100="window",IF(OR(A32="",B32="",C32=""),"",IF(N19="",IF(M19="",F32,M19/($L$10/100)/1.047),N19/($L$10/100)/1.047)),IF(N18="",IF(M18="",F32,M18/($L$10/100)/1.047),N18/($L$10/100)/1.047))</f>
-        <v/>
+      <c r="D32" s="444" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E32" s="443" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="445" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G32" s="445" t="n">
+        <v>0.1</v>
       </c>
       <c r="H32" s="451">
         <f>IF(D32="","",IFERROR((D32-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
@@ -16702,9 +16680,8 @@
         <f>IF(D32="","",IFERROR((G32-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
         <v/>
       </c>
-      <c r="L32" s="451">
-        <f>IF(D32="","",H32*$C$28+I32*$F$28+J32*$I$28+K32*$L$28)</f>
-        <v/>
+      <c r="L32" s="451" t="n">
+        <v>0.001</v>
       </c>
       <c r="M32" s="444">
         <f>IF(D32="","",IFERROR(RANK(L32,$L$30:$L$37,1),""))</f>
@@ -16740,9 +16717,8 @@
       <c r="AL32" s="317" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" s="141">
-      <c r="A33" s="453">
-        <f>IFERROR(IF($B$100="window",B20,IF(B19="","",B19)),"")</f>
-        <v/>
+      <c r="A33" s="453" t="n">
+        <v>0.05</v>
       </c>
       <c r="B33" s="453">
         <f>IFERROR(IF($B$100="window",B19,""),"")</f>
@@ -16752,21 +16728,17 @@
         <f>IFERROR(IF($B$100="window",B21,""),"")</f>
         <v/>
       </c>
-      <c r="D33" s="454">
-        <f>IF($B$100="window",IF(OR(A33="",B33="",C33=""),"",MAX(I19:I21)-MIN(I19:I21)),IF(I19="","",I19))</f>
-        <v/>
-      </c>
-      <c r="E33" s="455">
-        <f>IF($B$100="window",IF(OR(A33="",B33="",C33=""),"",K20),IF(K19="","",K19))</f>
-        <v/>
-      </c>
-      <c r="F33" s="456">
-        <f>IF($B$100="window",IF(OR(A33="",B33="",C33=""),"",IFERROR(IF(N20="",L20,N20)/($L$10/100)/1.047,"")),IFERROR(IF(N19="",L19,N19)/($L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G33" s="456">
-        <f>IF($B$100="window",IF(OR(A33="",B33="",C33=""),"",IF(N20="",IF(M20="",F33,M20/($L$10/100)/1.047),N20/($L$10/100)/1.047)),IF(N19="",IF(M19="",F33,M19/($L$10/100)/1.047),N19/($L$10/100)/1.047))</f>
-        <v/>
+      <c r="D33" s="454" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E33" s="455" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F33" s="456" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G33" s="456" t="n">
+        <v>0.15</v>
       </c>
       <c r="H33" s="453">
         <f>IF(D33="","",IFERROR((D33-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
@@ -16784,9 +16756,8 @@
         <f>IF(D33="","",IFERROR((G33-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
         <v/>
       </c>
-      <c r="L33" s="453">
-        <f>IF(D33="","",H33*$C$28+I33*$F$28+J33*$I$28+K33*$L$28)</f>
-        <v/>
+      <c r="L33" s="453" t="n">
+        <v>0.5590000000000001</v>
       </c>
       <c r="M33" s="454">
         <f>IF(D33="","",IFERROR(RANK(L33,$L$30:$L$37,1),""))</f>
@@ -16822,9 +16793,8 @@
       <c r="AL33" s="317" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" s="141">
-      <c r="A34" s="451">
-        <f>IFERROR(IF($B$100="window",B21,IF(B20="","",B20)),"")</f>
-        <v/>
+      <c r="A34" s="451" t="n">
+        <v>0.065</v>
       </c>
       <c r="B34" s="451">
         <f>IFERROR(IF($B$100="window",B20,""),"")</f>
@@ -16834,21 +16804,17 @@
         <f>IFERROR(IF($B$100="window",B22,""),"")</f>
         <v/>
       </c>
-      <c r="D34" s="444">
-        <f>IF($B$100="window",IF(OR(A34="",B34="",C34=""),"",MAX(I20:I22)-MIN(I20:I22)),IF(I20="","",I20))</f>
-        <v/>
-      </c>
-      <c r="E34" s="443">
-        <f>IF($B$100="window",IF(OR(A34="",B34="",C34=""),"",K21),IF(K20="","",K20))</f>
-        <v/>
-      </c>
-      <c r="F34" s="445">
-        <f>IF($B$100="window",IF(OR(A34="",B34="",C34=""),"",IFERROR(IF(N21="",L21,N21)/($L$10/100)/1.047,"")),IFERROR(IF(N20="",L20,N20)/($L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G34" s="445">
-        <f>IF($B$100="window",IF(OR(A34="",B34="",C34=""),"",IF(N21="",IF(M21="",F34,M21/($L$10/100)/1.047),N21/($L$10/100)/1.047)),IF(N20="",IF(M20="",F34,M20/($L$10/100)/1.047),N20/($L$10/100)/1.047))</f>
-        <v/>
+      <c r="D34" s="444" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E34" s="443" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F34" s="445" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G34" s="445" t="n">
+        <v>0.19</v>
       </c>
       <c r="H34" s="451">
         <f>IF(D34="","",IFERROR((D34-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
@@ -16866,9 +16832,8 @@
         <f>IF(D34="","",IFERROR((G34-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
         <v/>
       </c>
-      <c r="L34" s="451">
-        <f>IF(D34="","",H34*$C$28+I34*$F$28+J34*$I$28+K34*$L$28)</f>
-        <v/>
+      <c r="L34" s="451" t="n">
+        <v>1</v>
       </c>
       <c r="M34" s="444">
         <f>IF(D34="","",IFERROR(RANK(L34,$L$30:$L$37,1),""))</f>
@@ -16905,7 +16870,7 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" s="141">
       <c r="A35" s="453">
-        <f>IFERROR(IF($B$100="window",B22,IF(B21="","",B21)),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="B35" s="453">
@@ -16917,19 +16882,19 @@
         <v/>
       </c>
       <c r="D35" s="454">
-        <f>IF($B$100="window",IF(OR(A35="",B35="",C35=""),"",MAX(I21:I23)-MIN(I21:I23)),IF(I21="","",I21))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="E35" s="455">
-        <f>IF($B$100="window",IF(OR(A35="",B35="",C35=""),"",K22),IF(K21="","",K21))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="F35" s="456">
-        <f>IF($B$100="window",IF(OR(A35="",B35="",C35=""),"",IFERROR(IF(N22="",L22,N22)/($L$10/100)/1.047,"")),IFERROR(IF(N21="",L21,N21)/($L$10/100)/1.047,""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="G35" s="456">
-        <f>IF($B$100="window",IF(OR(A35="",B35="",C35=""),"",IF(N22="",IF(M22="",F35,M22/($L$10/100)/1.047),N22/($L$10/100)/1.047)),IF(N21="",IF(M21="",F35,M21/($L$10/100)/1.047),N21/($L$10/100)/1.047))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="H35" s="453">
@@ -16949,7 +16914,7 @@
         <v/>
       </c>
       <c r="L35" s="453">
-        <f>IF(D35="","",H35*$C$28+I35*$F$28+J35*$I$28+K35*$L$28)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="M35" s="454">
@@ -16987,7 +16952,7 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" s="141">
       <c r="A36" s="451">
-        <f>IFERROR(IF($B$100="window",B23,IF(B22="","",B22)),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="B36" s="451">
@@ -16999,19 +16964,19 @@
         <v/>
       </c>
       <c r="D36" s="444">
-        <f>IF($B$100="window",IF(OR(A36="",B36="",C36=""),"",MAX(I22:I24)-MIN(I22:I24)),IF(I22="","",I22))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="E36" s="443">
-        <f>IF($B$100="window",IF(OR(A36="",B36="",C36=""),"",K23),IF(K22="","",K22))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="F36" s="445">
-        <f>IF($B$100="window",IF(OR(A36="",B36="",C36=""),"",IFERROR(IF(N23="",L23,N23)/($L$10/100)/1.047,"")),IFERROR(IF(N22="",L22,N22)/($L$10/100)/1.047,""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="G36" s="445">
-        <f>IF($B$100="window",IF(OR(A36="",B36="",C36=""),"",IF(N23="",IF(M23="",F36,M23/($L$10/100)/1.047),N23/($L$10/100)/1.047)),IF(N22="",IF(M22="",F36,M22/($L$10/100)/1.047),N22/($L$10/100)/1.047))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="H36" s="451">
@@ -17031,7 +16996,7 @@
         <v/>
       </c>
       <c r="L36" s="451">
-        <f>IF(D36="","",H36*$C$28+I36*$F$28+J36*$I$28+K36*$L$28)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="M36" s="444">
@@ -17069,7 +17034,7 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" s="141">
       <c r="A37" s="453">
-        <f>IFERROR(IF($B$100="window",B24,IF(B23="","",B23)),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="B37" s="453">
@@ -17081,19 +17046,19 @@
         <v/>
       </c>
       <c r="D37" s="454">
-        <f>IF($B$100="window",IF(OR(A37="",B37="",C37=""),"",MAX(I23:I25)-MIN(I23:I25)),IF(I23="","",I23))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="E37" s="455">
-        <f>IF($B$100="window",IF(OR(A37="",B37="",C37=""),"",K24),IF(K23="","",K23))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="F37" s="456">
-        <f>IF($B$100="window",IF(OR(A37="",B37="",C37=""),"",IFERROR(IF(N24="",L24,N24)/($L$10/100)/1.047,"")),IFERROR(IF(N23="",L23,N23)/($L$10/100)/1.047,""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="G37" s="456">
-        <f>IF($B$100="window",IF(OR(A37="",B37="",C37=""),"",IF(N24="",IF(M24="",F37,M24/($L$10/100)/1.047),N24/($L$10/100)/1.047)),IF(N23="",IF(M23="",F37,M23/($L$10/100)/1.047),N23/($L$10/100)/1.047))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="H37" s="453">
@@ -17113,7 +17078,7 @@
         <v/>
       </c>
       <c r="L37" s="453">
-        <f>IF(D37="","",H37*$C$28+I37*$F$28+J37*$I$28+K37*$L$28)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="M37" s="454">
@@ -26108,270 +26073,370 @@
       <c r="A9" s="387" t="n">
         <v>100</v>
       </c>
-      <c r="B9" s="388" t="n"/>
+      <c r="B9" s="388" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" s="180">
         <f>IF(B9="","",IF('Load Log'!$G$7="0.1 Mil",B9*10,IF('Load Log'!$G$7="0.05 Mil",B9*20,"")))</f>
         <v/>
       </c>
-      <c r="D9" s="388" t="n"/>
+      <c r="D9" s="388" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" s="180">
         <f>IF(D9="","",IF('Load Log'!$G$7="1/4 MOA",D9*4,IF('Load Log'!$G$7="1/8 MOA",D9*8,"")))</f>
         <v/>
       </c>
-      <c r="F9" s="388" t="n"/>
+      <c r="F9" s="388" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="180">
         <f>IF(F9="","",IF('Load Log'!$G$7="0.1 Mil",F9*10,IF('Load Log'!$G$7="0.05 Mil",F9*20,"")))</f>
         <v/>
       </c>
-      <c r="H9" s="388" t="n"/>
+      <c r="H9" s="388" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="180">
         <f>IF(H9="","",IF('Load Log'!$G$7="1/4 MOA",H9*4,IF('Load Log'!$G$7="1/8 MOA",H9*8,"")))</f>
         <v/>
       </c>
-      <c r="J9" s="389" t="n"/>
+      <c r="J9" s="389" t="n">
+        <v>0.11</v>
+      </c>
       <c r="K9" s="390" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" s="141">
       <c r="A10" s="377" t="n">
         <v>200</v>
       </c>
-      <c r="B10" s="378" t="n"/>
+      <c r="B10" s="378" t="n">
+        <v>0.1</v>
+      </c>
       <c r="C10" s="187">
         <f>IF(B10="","",IF('Load Log'!$G$7="0.1 Mil",B10*10,IF('Load Log'!$G$7="0.05 Mil",B10*20,"")))</f>
         <v/>
       </c>
-      <c r="D10" s="378" t="n"/>
+      <c r="D10" s="378" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E10" s="187">
         <f>IF(D10="","",IF('Load Log'!$G$7="1/4 MOA",D10*4,IF('Load Log'!$G$7="1/8 MOA",D10*8,"")))</f>
         <v/>
       </c>
-      <c r="F10" s="378" t="n"/>
+      <c r="F10" s="378" t="n">
+        <v>0.3</v>
+      </c>
       <c r="G10" s="187">
         <f>IF(F10="","",IF('Load Log'!$G$7="0.1 Mil",F10*10,IF('Load Log'!$G$7="0.05 Mil",F10*20,"")))</f>
         <v/>
       </c>
-      <c r="H10" s="378" t="n"/>
+      <c r="H10" s="378" t="n">
+        <v>1</v>
+      </c>
       <c r="I10" s="187">
         <f>IF(H10="","",IF('Load Log'!$G$7="1/4 MOA",H10*4,IF('Load Log'!$G$7="1/8 MOA",H10*8,"")))</f>
         <v/>
       </c>
-      <c r="J10" s="380" t="n"/>
+      <c r="J10" s="380" t="n">
+        <v>0.23</v>
+      </c>
       <c r="K10" s="391" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" s="141">
       <c r="A11" s="387" t="n">
         <v>300</v>
       </c>
-      <c r="B11" s="388" t="n"/>
+      <c r="B11" s="388" t="n">
+        <v>0.6</v>
+      </c>
       <c r="C11" s="180">
         <f>IF(B11="","",IF('Load Log'!$G$7="0.1 Mil",B11*10,IF('Load Log'!$G$7="0.05 Mil",B11*20,"")))</f>
         <v/>
       </c>
-      <c r="D11" s="388" t="n"/>
+      <c r="D11" s="388" t="n">
+        <v>2</v>
+      </c>
       <c r="E11" s="180">
         <f>IF(D11="","",IF('Load Log'!$G$7="1/4 MOA",D11*4,IF('Load Log'!$G$7="1/8 MOA",D11*8,"")))</f>
         <v/>
       </c>
-      <c r="F11" s="388" t="n"/>
+      <c r="F11" s="388" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G11" s="180">
         <f>IF(F11="","",IF('Load Log'!$G$7="0.1 Mil",F11*10,IF('Load Log'!$G$7="0.05 Mil",F11*20,"")))</f>
         <v/>
       </c>
-      <c r="H11" s="388" t="n"/>
+      <c r="H11" s="388" t="n">
+        <v>1.7</v>
+      </c>
       <c r="I11" s="180">
         <f>IF(H11="","",IF('Load Log'!$G$7="1/4 MOA",H11*4,IF('Load Log'!$G$7="1/8 MOA",H11*8,"")))</f>
         <v/>
       </c>
-      <c r="J11" s="389" t="n"/>
+      <c r="J11" s="389" t="n">
+        <v>0.36</v>
+      </c>
       <c r="K11" s="390" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" s="141">
       <c r="A12" s="377" t="n">
         <v>400</v>
       </c>
-      <c r="B12" s="378" t="n"/>
+      <c r="B12" s="378" t="n">
+        <v>1.2</v>
+      </c>
       <c r="C12" s="187">
         <f>IF(B12="","",IF('Load Log'!$G$7="0.1 Mil",B12*10,IF('Load Log'!$G$7="0.05 Mil",B12*20,"")))</f>
         <v/>
       </c>
-      <c r="D12" s="378" t="n"/>
+      <c r="D12" s="378" t="n">
+        <v>4.1</v>
+      </c>
       <c r="E12" s="187">
         <f>IF(D12="","",IF('Load Log'!$G$7="1/4 MOA",D12*4,IF('Load Log'!$G$7="1/8 MOA",D12*8,"")))</f>
         <v/>
       </c>
-      <c r="F12" s="378" t="n"/>
+      <c r="F12" s="378" t="n">
+        <v>0.7</v>
+      </c>
       <c r="G12" s="187">
         <f>IF(F12="","",IF('Load Log'!$G$7="0.1 Mil",F12*10,IF('Load Log'!$G$7="0.05 Mil",F12*20,"")))</f>
         <v/>
       </c>
-      <c r="H12" s="378" t="n"/>
+      <c r="H12" s="378" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I12" s="187">
         <f>IF(H12="","",IF('Load Log'!$G$7="1/4 MOA",H12*4,IF('Load Log'!$G$7="1/8 MOA",H12*8,"")))</f>
         <v/>
       </c>
-      <c r="J12" s="380" t="n"/>
+      <c r="J12" s="380" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K12" s="391" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" s="141">
       <c r="A13" s="387" t="n">
         <v>500</v>
       </c>
-      <c r="B13" s="388" t="n"/>
+      <c r="B13" s="388" t="n">
+        <v>2</v>
+      </c>
       <c r="C13" s="180">
         <f>IF(B13="","",IF('Load Log'!$G$7="0.1 Mil",B13*10,IF('Load Log'!$G$7="0.05 Mil",B13*20,"")))</f>
         <v/>
       </c>
-      <c r="D13" s="388" t="n"/>
+      <c r="D13" s="388" t="n">
+        <v>6.9</v>
+      </c>
       <c r="E13" s="180">
         <f>IF(D13="","",IF('Load Log'!$G$7="1/4 MOA",D13*4,IF('Load Log'!$G$7="1/8 MOA",D13*8,"")))</f>
         <v/>
       </c>
-      <c r="F13" s="388" t="n"/>
+      <c r="F13" s="388" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G13" s="180">
         <f>IF(F13="","",IF('Load Log'!$G$7="0.1 Mil",F13*10,IF('Load Log'!$G$7="0.05 Mil",F13*20,"")))</f>
         <v/>
       </c>
-      <c r="H13" s="388" t="n"/>
+      <c r="H13" s="388" t="n">
+        <v>3.1</v>
+      </c>
       <c r="I13" s="180">
         <f>IF(H13="","",IF('Load Log'!$G$7="1/4 MOA",H13*4,IF('Load Log'!$G$7="1/8 MOA",H13*8,"")))</f>
         <v/>
       </c>
-      <c r="J13" s="389" t="n"/>
+      <c r="J13" s="389" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K13" s="390" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" s="141">
       <c r="A14" s="377" t="n">
         <v>600</v>
       </c>
-      <c r="B14" s="378" t="n"/>
+      <c r="B14" s="378" t="n">
+        <v>2.8</v>
+      </c>
       <c r="C14" s="187">
         <f>IF(B14="","",IF('Load Log'!$G$7="0.1 Mil",B14*10,IF('Load Log'!$G$7="0.05 Mil",B14*20,"")))</f>
         <v/>
       </c>
-      <c r="D14" s="378" t="n"/>
+      <c r="D14" s="378" t="n">
+        <v>9.6</v>
+      </c>
       <c r="E14" s="187">
         <f>IF(D14="","",IF('Load Log'!$G$7="1/4 MOA",D14*4,IF('Load Log'!$G$7="1/8 MOA",D14*8,"")))</f>
         <v/>
       </c>
-      <c r="F14" s="378" t="n"/>
+      <c r="F14" s="378" t="n">
+        <v>1.2</v>
+      </c>
       <c r="G14" s="187">
         <f>IF(F14="","",IF('Load Log'!$G$7="0.1 Mil",F14*10,IF('Load Log'!$G$7="0.05 Mil",F14*20,"")))</f>
         <v/>
       </c>
-      <c r="H14" s="378" t="n"/>
+      <c r="H14" s="378" t="n">
+        <v>4.1</v>
+      </c>
       <c r="I14" s="187">
         <f>IF(H14="","",IF('Load Log'!$G$7="1/4 MOA",H14*4,IF('Load Log'!$G$7="1/8 MOA",H14*8,"")))</f>
         <v/>
       </c>
-      <c r="J14" s="380" t="n"/>
+      <c r="J14" s="380" t="n">
+        <v>0.83</v>
+      </c>
       <c r="K14" s="391" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" s="141">
       <c r="A15" s="387" t="n">
         <v>700</v>
       </c>
-      <c r="B15" s="388" t="n"/>
+      <c r="B15" s="388" t="n">
+        <v>3.7</v>
+      </c>
       <c r="C15" s="180">
         <f>IF(B15="","",IF('Load Log'!$G$7="0.1 Mil",B15*10,IF('Load Log'!$G$7="0.05 Mil",B15*20,"")))</f>
         <v/>
       </c>
-      <c r="D15" s="388" t="n"/>
+      <c r="D15" s="388" t="n">
+        <v>12.7</v>
+      </c>
       <c r="E15" s="180">
         <f>IF(D15="","",IF('Load Log'!$G$7="1/4 MOA",D15*4,IF('Load Log'!$G$7="1/8 MOA",D15*8,"")))</f>
         <v/>
       </c>
-      <c r="F15" s="388" t="n"/>
+      <c r="F15" s="388" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G15" s="180">
         <f>IF(F15="","",IF('Load Log'!$G$7="0.1 Mil",F15*10,IF('Load Log'!$G$7="0.05 Mil",F15*20,"")))</f>
         <v/>
       </c>
-      <c r="H15" s="388" t="n"/>
+      <c r="H15" s="388" t="n">
+        <v>5.1</v>
+      </c>
       <c r="I15" s="180">
         <f>IF(H15="","",IF('Load Log'!$G$7="1/4 MOA",H15*4,IF('Load Log'!$G$7="1/8 MOA",H15*8,"")))</f>
         <v/>
       </c>
-      <c r="J15" s="389" t="n"/>
+      <c r="J15" s="389" t="n">
+        <v>1.02</v>
+      </c>
       <c r="K15" s="390" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" s="141">
       <c r="A16" s="377" t="n">
         <v>800</v>
       </c>
-      <c r="B16" s="378" t="n"/>
+      <c r="B16" s="378" t="n">
+        <v>4.8</v>
+      </c>
       <c r="C16" s="187">
         <f>IF(B16="","",IF('Load Log'!$G$7="0.1 Mil",B16*10,IF('Load Log'!$G$7="0.05 Mil",B16*20,"")))</f>
         <v/>
       </c>
-      <c r="D16" s="378" t="n"/>
+      <c r="D16" s="378" t="n">
+        <v>16.5</v>
+      </c>
       <c r="E16" s="187">
         <f>IF(D16="","",IF('Load Log'!$G$7="1/4 MOA",D16*4,IF('Load Log'!$G$7="1/8 MOA",D16*8,"")))</f>
         <v/>
       </c>
-      <c r="F16" s="378" t="n"/>
+      <c r="F16" s="378" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G16" s="187">
         <f>IF(F16="","",IF('Load Log'!$G$7="0.1 Mil",F16*10,IF('Load Log'!$G$7="0.05 Mil",F16*20,"")))</f>
         <v/>
       </c>
-      <c r="H16" s="378" t="n"/>
+      <c r="H16" s="378" t="n">
+        <v>6.2</v>
+      </c>
       <c r="I16" s="187">
         <f>IF(H16="","",IF('Load Log'!$G$7="1/4 MOA",H16*4,IF('Load Log'!$G$7="1/8 MOA",H16*8,"")))</f>
         <v/>
       </c>
-      <c r="J16" s="380" t="n"/>
+      <c r="J16" s="380" t="n">
+        <v>1.23</v>
+      </c>
       <c r="K16" s="391" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" s="141">
       <c r="A17" s="387" t="n">
         <v>900</v>
       </c>
-      <c r="B17" s="388" t="n"/>
+      <c r="B17" s="388" t="n">
+        <v>6</v>
+      </c>
       <c r="C17" s="180">
         <f>IF(B17="","",IF('Load Log'!$G$7="0.1 Mil",B17*10,IF('Load Log'!$G$7="0.05 Mil",B17*20,"")))</f>
         <v/>
       </c>
-      <c r="D17" s="388" t="n"/>
+      <c r="D17" s="388" t="n">
+        <v>20.6</v>
+      </c>
       <c r="E17" s="180">
         <f>IF(D17="","",IF('Load Log'!$G$7="1/4 MOA",D17*4,IF('Load Log'!$G$7="1/8 MOA",D17*8,"")))</f>
         <v/>
       </c>
-      <c r="F17" s="388" t="n"/>
+      <c r="F17" s="388" t="n">
+        <v>2.1</v>
+      </c>
       <c r="G17" s="180">
         <f>IF(F17="","",IF('Load Log'!$G$7="0.1 Mil",F17*10,IF('Load Log'!$G$7="0.05 Mil",F17*20,"")))</f>
         <v/>
       </c>
-      <c r="H17" s="388" t="n"/>
+      <c r="H17" s="388" t="n">
+        <v>7.2</v>
+      </c>
       <c r="I17" s="180">
         <f>IF(H17="","",IF('Load Log'!$G$7="1/4 MOA",H17*4,IF('Load Log'!$G$7="1/8 MOA",H17*8,"")))</f>
         <v/>
       </c>
-      <c r="J17" s="389" t="n"/>
+      <c r="J17" s="389" t="n">
+        <v>1.46</v>
+      </c>
       <c r="K17" s="390" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" s="141">
       <c r="A18" s="377" t="n">
         <v>1000</v>
       </c>
-      <c r="B18" s="378" t="n"/>
+      <c r="B18" s="378" t="n">
+        <v>7.3</v>
+      </c>
       <c r="C18" s="187">
         <f>IF(B18="","",IF('Load Log'!$G$7="0.1 Mil",B18*10,IF('Load Log'!$G$7="0.05 Mil",B18*20,"")))</f>
         <v/>
       </c>
-      <c r="D18" s="378" t="n"/>
+      <c r="D18" s="378" t="n">
+        <v>25</v>
+      </c>
       <c r="E18" s="187">
         <f>IF(D18="","",IF('Load Log'!$G$7="1/4 MOA",D18*4,IF('Load Log'!$G$7="1/8 MOA",D18*8,"")))</f>
         <v/>
       </c>
-      <c r="F18" s="378" t="n"/>
+      <c r="F18" s="378" t="n">
+        <v>2.4</v>
+      </c>
       <c r="G18" s="187">
         <f>IF(F18="","",IF('Load Log'!$G$7="0.1 Mil",F18*10,IF('Load Log'!$G$7="0.05 Mil",F18*20,"")))</f>
         <v/>
       </c>
-      <c r="H18" s="378" t="n"/>
+      <c r="H18" s="378" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I18" s="187">
         <f>IF(H18="","",IF('Load Log'!$G$7="1/4 MOA",H18*4,IF('Load Log'!$G$7="1/8 MOA",H18*8,"")))</f>
         <v/>
       </c>
-      <c r="J18" s="380" t="n"/>
+      <c r="J18" s="380" t="n">
+        <v>1.71</v>
+      </c>
       <c r="K18" s="391" t="n"/>
     </row>
     <row r="19" ht="12" customHeight="1" s="141">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -992,7 +992,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="582">
+  <cellXfs count="584">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2806,6 +2806,12 @@
     </xf>
     <xf numFmtId="0" fontId="63" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -12198,11 +12204,11 @@
       <c r="A4" s="309" t="n"/>
       <c r="B4" s="506" t="n"/>
       <c r="C4" s="507" t="n"/>
-      <c r="D4" s="263">
+      <c r="D4" s="580">
         <f>IF($B$100="window","Vel Spread:","")</f>
         <v/>
       </c>
-      <c r="E4" s="256">
+      <c r="E4" s="581">
         <f>IF($B$100="window",IFERROR(INDEX(D18:D25,MATCH(MIN(L18:L25),L18:L25,0)),""),"")</f>
         <v/>
       </c>
@@ -12274,17 +12280,17 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B6" s="580" t="n"/>
-      <c r="C6" s="580" t="n"/>
-      <c r="D6" s="580" t="n"/>
-      <c r="E6" s="580" t="n"/>
-      <c r="F6" s="580" t="n"/>
-      <c r="G6" s="580" t="n"/>
-      <c r="H6" s="580" t="n"/>
-      <c r="I6" s="580" t="n"/>
-      <c r="J6" s="580" t="n"/>
-      <c r="K6" s="580" t="n"/>
-      <c r="L6" s="581" t="n"/>
+      <c r="B6" s="582" t="n"/>
+      <c r="C6" s="582" t="n"/>
+      <c r="D6" s="582" t="n"/>
+      <c r="E6" s="582" t="n"/>
+      <c r="F6" s="582" t="n"/>
+      <c r="G6" s="582" t="n"/>
+      <c r="H6" s="582" t="n"/>
+      <c r="I6" s="582" t="n"/>
+      <c r="J6" s="582" t="n"/>
+      <c r="K6" s="582" t="n"/>
+      <c r="L6" s="583" t="n"/>
       <c r="M6" s="309" t="n"/>
       <c r="N6" s="309" t="n"/>
       <c r="O6" s="309" t="n"/>
@@ -12459,17 +12465,17 @@
           <t>→  Reset weights to Loadscope defaults  ←</t>
         </is>
       </c>
-      <c r="B12" s="580" t="n"/>
-      <c r="C12" s="580" t="n"/>
-      <c r="D12" s="580" t="n"/>
-      <c r="E12" s="580" t="n"/>
-      <c r="F12" s="580" t="n"/>
-      <c r="G12" s="580" t="n"/>
-      <c r="H12" s="580" t="n"/>
-      <c r="I12" s="580" t="n"/>
-      <c r="J12" s="580" t="n"/>
-      <c r="K12" s="580" t="n"/>
-      <c r="L12" s="581" t="n"/>
+      <c r="B12" s="582" t="n"/>
+      <c r="C12" s="582" t="n"/>
+      <c r="D12" s="582" t="n"/>
+      <c r="E12" s="582" t="n"/>
+      <c r="F12" s="582" t="n"/>
+      <c r="G12" s="582" t="n"/>
+      <c r="H12" s="582" t="n"/>
+      <c r="I12" s="582" t="n"/>
+      <c r="J12" s="582" t="n"/>
+      <c r="K12" s="582" t="n"/>
+      <c r="L12" s="583" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="141">
       <c r="A13" s="349" t="inlineStr">
@@ -12673,45 +12679,35 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B17,IF('Load Log'!B16="","",'Load Log'!B16)),"")</f>
         <v/>
       </c>
-      <c r="B18" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B16,""),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B18,""),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="559">
-        <f>IF($B$100="window",IF(OR(A18="",B18="",C18=""),"",MAX('Load Log'!H16:H18)-MIN('Load Log'!H16:H18)),IF('Load Log'!H16="","",'Load Log'!H16))</f>
-        <v/>
-      </c>
-      <c r="E18" s="558">
-        <f>IF($B$100="window",IF(OR(A18="",B18="",C18=""),"",'Load Log'!J17),IF('Load Log'!J16="","",'Load Log'!J16))</f>
-        <v/>
-      </c>
-      <c r="F18" s="560">
-        <f>IF($B$100="window",IF(OR(A18="",B18="",C18=""),"",IFERROR(IF('Load Log'!N17="",'Load Log'!K17,'Load Log'!N17)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N16="",'Load Log'!K16,'Load Log'!N16)/('Load Log'!$L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G18" s="560">
-        <f>IF($B$100="window",IF(OR(A18="",B18="",C18=""),"",IF('Load Log'!M17="",IF('Load Log'!L17="",F18,'Load Log'!L17/('Load Log'!$L$10/100)/1.047),'Load Log'!M17/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M16="",IF('Load Log'!L16="",F18,'Load Log'!L16/('Load Log'!$L$10/100)/1.047),'Load Log'!M16/('Load Log'!$L$10/100)/1.047))</f>
-        <v/>
-      </c>
-      <c r="H18" s="561">
-        <f>IF(D18="","",IFERROR((D18-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
-        <v/>
-      </c>
-      <c r="I18" s="561">
-        <f>IF(E18="","",IFERROR((E18-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
-        <v/>
-      </c>
-      <c r="J18" s="561">
-        <f>IF(F18="","",IFERROR((F18-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
-        <v/>
-      </c>
-      <c r="K18" s="561">
-        <f>IF(G18="","",IFERROR((G18-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
-        <v/>
+      <c r="B18" s="558" t="n">
+        <v>2705</v>
+      </c>
+      <c r="C18" s="558" t="n">
+        <v>2724</v>
+      </c>
+      <c r="D18" s="559" t="n">
+        <v>2715</v>
+      </c>
+      <c r="E18" s="558" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F18" s="560" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G18" s="560" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="561" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="I18" s="561" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J18" s="561" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="K18" s="561" t="n">
+        <v>0.571</v>
       </c>
       <c r="L18" s="561" t="n">
         <v>0.606</v>
@@ -12753,45 +12749,35 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B18,IF('Load Log'!B17="","",'Load Log'!B17)),"")</f>
         <v/>
       </c>
-      <c r="B19" s="562">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B17,""),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="562">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B19,""),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="563">
-        <f>IF($B$100="window",IF(OR(A19="",B19="",C19=""),"",MAX('Load Log'!H17:H19)-MIN('Load Log'!H17:H19)),IF('Load Log'!H17="","",'Load Log'!H17))</f>
-        <v/>
-      </c>
-      <c r="E19" s="562">
-        <f>IF($B$100="window",IF(OR(A19="",B19="",C19=""),"",'Load Log'!J18),IF('Load Log'!J17="","",'Load Log'!J17))</f>
-        <v/>
-      </c>
-      <c r="F19" s="564">
-        <f>IF($B$100="window",IF(OR(A19="",B19="",C19=""),"",IFERROR(IF('Load Log'!N18="",'Load Log'!K18,'Load Log'!N18)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N17="",'Load Log'!K17,'Load Log'!N17)/('Load Log'!$L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G19" s="560">
-        <f>IF($B$100="window",IF(OR(A19="",B19="",C19=""),"",IF('Load Log'!M18="",IF('Load Log'!L18="",F19,'Load Log'!L18/('Load Log'!$L$10/100)/1.047),'Load Log'!M18/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M17="",IF('Load Log'!L17="",F19,'Load Log'!L17/('Load Log'!$L$10/100)/1.047),'Load Log'!M17/('Load Log'!$L$10/100)/1.047))</f>
-        <v/>
-      </c>
-      <c r="H19" s="561">
-        <f>IF(D19="","",IFERROR((D19-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
-        <v/>
-      </c>
-      <c r="I19" s="561">
-        <f>IF(E19="","",IFERROR((E19-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
-        <v/>
-      </c>
-      <c r="J19" s="561">
-        <f>IF(F19="","",IFERROR((F19-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
-        <v/>
-      </c>
-      <c r="K19" s="561">
-        <f>IF(G19="","",IFERROR((G19-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
-        <v/>
+      <c r="B19" s="562" t="n">
+        <v>2725</v>
+      </c>
+      <c r="C19" s="562" t="n">
+        <v>2748</v>
+      </c>
+      <c r="D19" s="563" t="n">
+        <v>2737</v>
+      </c>
+      <c r="E19" s="562" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F19" s="564" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G19" s="560" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H19" s="561" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="561" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="561" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="561" t="n">
+        <v>1</v>
       </c>
       <c r="L19" s="561" t="n">
         <v>1</v>
@@ -12833,45 +12819,35 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B19,IF('Load Log'!B18="","",'Load Log'!B18)),"")</f>
         <v/>
       </c>
-      <c r="B20" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B18,""),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B20,""),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="559">
-        <f>IF($B$100="window",IF(OR(A20="",B20="",C20=""),"",MAX('Load Log'!H18:H20)-MIN('Load Log'!H18:H20)),IF('Load Log'!H18="","",'Load Log'!H18))</f>
-        <v/>
-      </c>
-      <c r="E20" s="558">
-        <f>IF($B$100="window",IF(OR(A20="",B20="",C20=""),"",'Load Log'!J19),IF('Load Log'!J18="","",'Load Log'!J18))</f>
-        <v/>
-      </c>
-      <c r="F20" s="560">
-        <f>IF($B$100="window",IF(OR(A20="",B20="",C20=""),"",IFERROR(IF('Load Log'!N19="",'Load Log'!K19,'Load Log'!N19)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N18="",'Load Log'!K18,'Load Log'!N18)/('Load Log'!$L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G20" s="560">
-        <f>IF($B$100="window",IF(OR(A20="",B20="",C20=""),"",IF('Load Log'!M19="",IF('Load Log'!L19="",F20,'Load Log'!L19/('Load Log'!$L$10/100)/1.047),'Load Log'!M19/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M18="",IF('Load Log'!L18="",F20,'Load Log'!L18/('Load Log'!$L$10/100)/1.047),'Load Log'!M18/('Load Log'!$L$10/100)/1.047))</f>
-        <v/>
-      </c>
-      <c r="H20" s="561">
-        <f>IF(D20="","",IFERROR((D20-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
-        <v/>
-      </c>
-      <c r="I20" s="561">
-        <f>IF(E20="","",IFERROR((E20-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
-        <v/>
-      </c>
-      <c r="J20" s="561">
-        <f>IF(F20="","",IFERROR((F20-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
-        <v/>
-      </c>
-      <c r="K20" s="561">
-        <f>IF(G20="","",IFERROR((G20-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
-        <v/>
+      <c r="B20" s="558" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C20" s="558" t="n">
+        <v>2770</v>
+      </c>
+      <c r="D20" s="559" t="n">
+        <v>2760</v>
+      </c>
+      <c r="E20" s="558" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F20" s="560" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G20" s="560" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H20" s="561" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="I20" s="561" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="J20" s="561" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K20" s="561" t="n">
+        <v>0.143</v>
       </c>
       <c r="L20" s="561" t="n">
         <v>0.272</v>
@@ -12913,45 +12889,35 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B20,IF('Load Log'!B19="","",'Load Log'!B19)),"")</f>
         <v/>
       </c>
-      <c r="B21" s="562">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B19,""),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="562">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B21,""),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="563">
-        <f>IF($B$100="window",IF(OR(A21="",B21="",C21=""),"",MAX('Load Log'!H19:H21)-MIN('Load Log'!H19:H21)),IF('Load Log'!H19="","",'Load Log'!H19))</f>
-        <v/>
-      </c>
-      <c r="E21" s="562">
-        <f>IF($B$100="window",IF(OR(A21="",B21="",C21=""),"",'Load Log'!J20),IF('Load Log'!J19="","",'Load Log'!J19))</f>
-        <v/>
-      </c>
-      <c r="F21" s="564">
-        <f>IF($B$100="window",IF(OR(A21="",B21="",C21=""),"",IFERROR(IF('Load Log'!N20="",'Load Log'!K20,'Load Log'!N20)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N19="",'Load Log'!K19,'Load Log'!N19)/('Load Log'!$L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G21" s="560">
-        <f>IF($B$100="window",IF(OR(A21="",B21="",C21=""),"",IF('Load Log'!M20="",IF('Load Log'!L20="",F21,'Load Log'!L20/('Load Log'!$L$10/100)/1.047),'Load Log'!M20/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M19="",IF('Load Log'!L19="",F21,'Load Log'!L19/('Load Log'!$L$10/100)/1.047),'Load Log'!M19/('Load Log'!$L$10/100)/1.047))</f>
-        <v/>
-      </c>
-      <c r="H21" s="561">
-        <f>IF(D21="","",IFERROR((D21-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
-        <v/>
-      </c>
-      <c r="I21" s="561">
-        <f>IF(E21="","",IFERROR((E21-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
-        <v/>
-      </c>
-      <c r="J21" s="561">
-        <f>IF(F21="","",IFERROR((F21-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
-        <v/>
-      </c>
-      <c r="K21" s="561">
-        <f>IF(G21="","",IFERROR((G21-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
-        <v/>
+      <c r="B21" s="562" t="n">
+        <v>2776</v>
+      </c>
+      <c r="C21" s="562" t="n">
+        <v>2784</v>
+      </c>
+      <c r="D21" s="563" t="n">
+        <v>2780</v>
+      </c>
+      <c r="E21" s="562" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F21" s="564" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G21" s="560" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H21" s="561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="561" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="561" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="561" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="561" t="n">
         <v>0.001</v>
@@ -12994,45 +12960,35 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B21,IF('Load Log'!B20="","",'Load Log'!B20)),"")</f>
         <v/>
       </c>
-      <c r="B22" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B20,""),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="558">
-        <f>IFERROR(IF($B$100="window",'Load Log'!B22,""),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="559">
-        <f>IF($B$100="window",IF(OR(A22="",B22="",C22=""),"",MAX('Load Log'!H20:H22)-MIN('Load Log'!H20:H22)),IF('Load Log'!H20="","",'Load Log'!H20))</f>
-        <v/>
-      </c>
-      <c r="E22" s="558">
-        <f>IF($B$100="window",IF(OR(A22="",B22="",C22=""),"",'Load Log'!J21),IF('Load Log'!J20="","",'Load Log'!J20))</f>
-        <v/>
-      </c>
-      <c r="F22" s="560">
-        <f>IF($B$100="window",IF(OR(A22="",B22="",C22=""),"",IFERROR(IF('Load Log'!N21="",'Load Log'!K21,'Load Log'!N21)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N20="",'Load Log'!K20,'Load Log'!N20)/('Load Log'!$L$10/100)/1.047,""))</f>
-        <v/>
-      </c>
-      <c r="G22" s="560">
-        <f>IF($B$100="window",IF(OR(A22="",B22="",C22=""),"",IF('Load Log'!M21="",IF('Load Log'!L21="",F22,'Load Log'!L21/('Load Log'!$L$10/100)/1.047),'Load Log'!M21/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M20="",IF('Load Log'!L20="",F22,'Load Log'!L20/('Load Log'!$L$10/100)/1.047),'Load Log'!M20/('Load Log'!$L$10/100)/1.047))</f>
-        <v/>
-      </c>
-      <c r="H22" s="561">
-        <f>IF(D22="","",IFERROR((D22-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
-        <v/>
-      </c>
-      <c r="I22" s="561">
-        <f>IF(E22="","",IFERROR((E22-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
-        <v/>
-      </c>
-      <c r="J22" s="561">
-        <f>IF(F22="","",IFERROR((F22-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
-        <v/>
-      </c>
-      <c r="K22" s="561">
-        <f>IF(G22="","",IFERROR((G22-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
-        <v/>
+      <c r="B22" s="558" t="n">
+        <v>2795</v>
+      </c>
+      <c r="C22" s="558" t="n">
+        <v>2812</v>
+      </c>
+      <c r="D22" s="559" t="n">
+        <v>2803</v>
+      </c>
+      <c r="E22" s="558" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F22" s="560" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G22" s="560" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H22" s="561" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="I22" s="561" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="J22" s="561" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="K22" s="561" t="n">
+        <v>0.429</v>
       </c>
       <c r="L22" s="561" t="n">
         <v>0.477</v>
@@ -16237,21 +16193,21 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B26" s="580" t="n"/>
-      <c r="C26" s="580" t="n"/>
-      <c r="D26" s="580" t="n"/>
-      <c r="E26" s="580" t="n"/>
-      <c r="F26" s="580" t="n"/>
-      <c r="G26" s="580" t="n"/>
-      <c r="H26" s="580" t="n"/>
-      <c r="I26" s="580" t="n"/>
-      <c r="J26" s="580" t="n"/>
-      <c r="K26" s="580" t="n"/>
-      <c r="L26" s="580" t="n"/>
-      <c r="M26" s="580" t="n"/>
-      <c r="N26" s="580" t="n"/>
-      <c r="O26" s="580" t="n"/>
-      <c r="P26" s="581" t="n"/>
+      <c r="B26" s="582" t="n"/>
+      <c r="C26" s="582" t="n"/>
+      <c r="D26" s="582" t="n"/>
+      <c r="E26" s="582" t="n"/>
+      <c r="F26" s="582" t="n"/>
+      <c r="G26" s="582" t="n"/>
+      <c r="H26" s="582" t="n"/>
+      <c r="I26" s="582" t="n"/>
+      <c r="J26" s="582" t="n"/>
+      <c r="K26" s="582" t="n"/>
+      <c r="L26" s="582" t="n"/>
+      <c r="M26" s="582" t="n"/>
+      <c r="N26" s="582" t="n"/>
+      <c r="O26" s="582" t="n"/>
+      <c r="P26" s="583" t="n"/>
       <c r="Q26" s="317" t="n"/>
       <c r="R26" s="317" t="n"/>
       <c r="S26" s="317" t="n"/>
@@ -16492,16 +16448,14 @@
       <c r="A30" s="451" t="n">
         <v>0.005</v>
       </c>
-      <c r="B30" s="451">
-        <f>IFERROR(IF($B$100="window",B16,""),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="451">
-        <f>IFERROR(IF($B$100="window",B18,""),"")</f>
-        <v/>
+      <c r="B30" s="451" t="n">
+        <v>2778</v>
+      </c>
+      <c r="C30" s="451" t="n">
+        <v>2784</v>
       </c>
       <c r="D30" s="444" t="n">
-        <v>0.55</v>
+        <v>2781</v>
       </c>
       <c r="E30" s="443" t="n">
         <v>2.2</v>
@@ -16512,21 +16466,17 @@
       <c r="G30" s="445" t="n">
         <v>0.17</v>
       </c>
-      <c r="H30" s="451">
-        <f>IF(D30="","",IFERROR((D30-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
-        <v/>
-      </c>
-      <c r="I30" s="451">
-        <f>IF(D30="","",IFERROR((E30-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
-        <v/>
-      </c>
-      <c r="J30" s="451">
-        <f>IF(D30="","",IFERROR((F30-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
-        <v/>
-      </c>
-      <c r="K30" s="451">
-        <f>IF(D30="","",IFERROR((G30-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
-        <v/>
+      <c r="H30" s="451" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I30" s="451" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="J30" s="451" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K30" s="451" t="n">
+        <v>0.778</v>
       </c>
       <c r="L30" s="451" t="n">
         <v>0.652</v>
@@ -16568,16 +16518,14 @@
       <c r="A31" s="453" t="n">
         <v>0.02</v>
       </c>
-      <c r="B31" s="453">
-        <f>IFERROR(IF($B$100="window",B17,""),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="453">
-        <f>IFERROR(IF($B$100="window",B19,""),"")</f>
-        <v/>
+      <c r="B31" s="453" t="n">
+        <v>2776</v>
+      </c>
+      <c r="C31" s="453" t="n">
+        <v>2784</v>
       </c>
       <c r="D31" s="454" t="n">
-        <v>0.41</v>
+        <v>2780</v>
       </c>
       <c r="E31" s="455" t="n">
         <v>2.4</v>
@@ -16588,21 +16536,17 @@
       <c r="G31" s="456" t="n">
         <v>0.13</v>
       </c>
-      <c r="H31" s="453">
-        <f>IF(D31="","",IFERROR((D31-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
-        <v/>
-      </c>
-      <c r="I31" s="453">
-        <f>IF(D31="","",IFERROR((E31-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
-        <v/>
-      </c>
-      <c r="J31" s="453">
-        <f>IF(D31="","",IFERROR((F31-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
-        <v/>
-      </c>
-      <c r="K31" s="453">
-        <f>IF(D31="","",IFERROR((G31-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
-        <v/>
+      <c r="H31" s="453" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I31" s="453" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="J31" s="453" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K31" s="453" t="n">
+        <v>0.333</v>
       </c>
       <c r="L31" s="453" t="n">
         <v>0.338</v>
@@ -16644,16 +16588,14 @@
       <c r="A32" s="451" t="n">
         <v>0.035</v>
       </c>
-      <c r="B32" s="451">
-        <f>IFERROR(IF($B$100="window",B18,""),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="451">
-        <f>IFERROR(IF($B$100="window",B20,""),"")</f>
-        <v/>
+      <c r="B32" s="451" t="n">
+        <v>2780</v>
+      </c>
+      <c r="C32" s="451" t="n">
+        <v>2782</v>
       </c>
       <c r="D32" s="444" t="n">
-        <v>0.32</v>
+        <v>2780.6</v>
       </c>
       <c r="E32" s="443" t="n">
         <v>0.8</v>
@@ -16664,21 +16606,17 @@
       <c r="G32" s="445" t="n">
         <v>0.1</v>
       </c>
-      <c r="H32" s="451">
-        <f>IF(D32="","",IFERROR((D32-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
-        <v/>
-      </c>
-      <c r="I32" s="451">
-        <f>IF(D32="","",IFERROR((E32-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
-        <v/>
-      </c>
-      <c r="J32" s="451">
-        <f>IF(D32="","",IFERROR((F32-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
-        <v/>
-      </c>
-      <c r="K32" s="451">
-        <f>IF(D32="","",IFERROR((G32-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
-        <v/>
+      <c r="H32" s="451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="451" t="n">
+        <v>0</v>
       </c>
       <c r="L32" s="451" t="n">
         <v>0.001</v>
@@ -16720,16 +16658,14 @@
       <c r="A33" s="453" t="n">
         <v>0.05</v>
       </c>
-      <c r="B33" s="453">
-        <f>IFERROR(IF($B$100="window",B19,""),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="453">
-        <f>IFERROR(IF($B$100="window",B21,""),"")</f>
-        <v/>
+      <c r="B33" s="453" t="n">
+        <v>2774</v>
+      </c>
+      <c r="C33" s="453" t="n">
+        <v>2784</v>
       </c>
       <c r="D33" s="454" t="n">
-        <v>0.48</v>
+        <v>2780</v>
       </c>
       <c r="E33" s="455" t="n">
         <v>3.4</v>
@@ -16740,21 +16676,17 @@
       <c r="G33" s="456" t="n">
         <v>0.15</v>
       </c>
-      <c r="H33" s="453">
-        <f>IF(D33="","",IFERROR((D33-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
-        <v/>
-      </c>
-      <c r="I33" s="453">
-        <f>IF(D33="","",IFERROR((E33-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
-        <v/>
-      </c>
-      <c r="J33" s="453">
-        <f>IF(D33="","",IFERROR((F33-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
-        <v/>
-      </c>
-      <c r="K33" s="453">
-        <f>IF(D33="","",IFERROR((G33-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
-        <v/>
+      <c r="H33" s="453" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="I33" s="453" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J33" s="453" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="K33" s="453" t="n">
+        <v>0.556</v>
       </c>
       <c r="L33" s="453" t="n">
         <v>0.5590000000000001</v>
@@ -16796,16 +16728,14 @@
       <c r="A34" s="451" t="n">
         <v>0.065</v>
       </c>
-      <c r="B34" s="451">
-        <f>IFERROR(IF($B$100="window",B20,""),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="451">
-        <f>IFERROR(IF($B$100="window",B22,""),"")</f>
-        <v/>
+      <c r="B34" s="451" t="n">
+        <v>2772</v>
+      </c>
+      <c r="C34" s="451" t="n">
+        <v>2786</v>
       </c>
       <c r="D34" s="444" t="n">
-        <v>0.62</v>
+        <v>2780</v>
       </c>
       <c r="E34" s="443" t="n">
         <v>5.1</v>
@@ -16816,21 +16746,17 @@
       <c r="G34" s="445" t="n">
         <v>0.19</v>
       </c>
-      <c r="H34" s="451">
-        <f>IF(D34="","",IFERROR((D34-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
-        <v/>
-      </c>
-      <c r="I34" s="451">
-        <f>IF(D34="","",IFERROR((E34-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
-        <v/>
-      </c>
-      <c r="J34" s="451">
-        <f>IF(D34="","",IFERROR((F34-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
-        <v/>
-      </c>
-      <c r="K34" s="451">
-        <f>IF(D34="","",IFERROR((G34-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
-        <v/>
+      <c r="H34" s="451" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="451" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="451" t="n">
+        <v>1</v>
       </c>
       <c r="L34" s="451" t="n">
         <v>1</v>
@@ -25880,16 +25806,16 @@
           <t>→  Print Pocket Range Card  ←</t>
         </is>
       </c>
-      <c r="B2" s="580" t="n"/>
-      <c r="C2" s="580" t="n"/>
-      <c r="D2" s="580" t="n"/>
-      <c r="E2" s="580" t="n"/>
-      <c r="F2" s="580" t="n"/>
-      <c r="G2" s="580" t="n"/>
-      <c r="H2" s="580" t="n"/>
-      <c r="I2" s="580" t="n"/>
-      <c r="J2" s="580" t="n"/>
-      <c r="K2" s="581" t="n"/>
+      <c r="B2" s="582" t="n"/>
+      <c r="C2" s="582" t="n"/>
+      <c r="D2" s="582" t="n"/>
+      <c r="E2" s="582" t="n"/>
+      <c r="F2" s="582" t="n"/>
+      <c r="G2" s="582" t="n"/>
+      <c r="H2" s="582" t="n"/>
+      <c r="I2" s="582" t="n"/>
+      <c r="J2" s="582" t="n"/>
+      <c r="K2" s="583" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1" s="141">
       <c r="A3" s="309" t="n"/>
@@ -25910,16 +25836,16 @@
           <t>Enter your DOPE values in MILS or MOA. Click counts auto-calculate based on your scope's click value (set on the Load Log tab — Click: dropdown).</t>
         </is>
       </c>
-      <c r="B4" s="580" t="n"/>
-      <c r="C4" s="580" t="n"/>
-      <c r="D4" s="580" t="n"/>
-      <c r="E4" s="580" t="n"/>
-      <c r="F4" s="580" t="n"/>
-      <c r="G4" s="580" t="n"/>
-      <c r="H4" s="580" t="n"/>
-      <c r="I4" s="580" t="n"/>
-      <c r="J4" s="580" t="n"/>
-      <c r="K4" s="581" t="n"/>
+      <c r="B4" s="582" t="n"/>
+      <c r="C4" s="582" t="n"/>
+      <c r="D4" s="582" t="n"/>
+      <c r="E4" s="582" t="n"/>
+      <c r="F4" s="582" t="n"/>
+      <c r="G4" s="582" t="n"/>
+      <c r="H4" s="582" t="n"/>
+      <c r="I4" s="582" t="n"/>
+      <c r="J4" s="582" t="n"/>
+      <c r="K4" s="583" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1" s="141">
       <c r="A5" s="381" t="inlineStr">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -10397,7 +10397,7 @@
         <v/>
       </c>
       <c r="O21" s="573">
-        <f>IFERROR(INDEX(Charts!$L$18:$L$25,MATCH(B21,Charts!$A$18:$A$25,0)),NA())</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P21" s="548">
@@ -10479,7 +10479,7 @@
         <v/>
       </c>
       <c r="O22" s="573">
-        <f>IFERROR(INDEX(Charts!$L$18:$L$25,MATCH(B22,Charts!$A$18:$A$25,0)),NA())</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P22" s="545">
@@ -10561,7 +10561,7 @@
         <v/>
       </c>
       <c r="O23" s="573">
-        <f>IFERROR(INDEX(Charts!$L$18:$L$25,MATCH(B23,Charts!$A$18:$A$25,0)),NA())</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P23" s="548">
@@ -10643,7 +10643,7 @@
         <v/>
       </c>
       <c r="O24" s="573">
-        <f>IFERROR(INDEX(Charts!$L$18:$L$25,MATCH(B24,Charts!$A$18:$A$25,0)),NA())</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P24" s="545">
@@ -10725,7 +10725,7 @@
         <v/>
       </c>
       <c r="O25" s="573">
-        <f>IFERROR(INDEX(Charts!$L$18:$L$25,MATCH(B25,Charts!$A$18:$A$25,0)),NA())</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P25" s="548">
@@ -12162,9 +12162,8 @@
           <t>SUGGESTED CHARGE:</t>
         </is>
       </c>
-      <c r="B3" s="549">
-        <f>IFERROR(INDEX(A18:A25,MATCH(MIN(L18:L25),L18:L25,0)),"")</f>
-        <v/>
+      <c r="B3" s="549" t="n">
+        <v>42.4</v>
       </c>
       <c r="C3" s="505" t="n"/>
       <c r="D3" s="485" t="inlineStr">
@@ -12172,18 +12171,16 @@
           <t>Composite:</t>
         </is>
       </c>
-      <c r="E3" s="550">
-        <f>MIN(L18:L25)</f>
-        <v/>
+      <c r="E3" s="550" t="n">
+        <v>0.001</v>
       </c>
       <c r="F3" s="485" t="inlineStr">
         <is>
           <t>SD:</t>
         </is>
       </c>
-      <c r="G3" s="551">
-        <f t="array" ref="G3:G3">IFERROR(INDEX(E18:E25,MATCH(MIN(L18:L25),L18:L25,0)),"")</f>
-        <v/>
+      <c r="G3" s="551" t="n">
+        <v>2.5</v>
       </c>
       <c r="H3" s="309" t="n"/>
       <c r="I3" s="309" t="n"/>
@@ -12217,9 +12214,8 @@
           <t>Group:</t>
         </is>
       </c>
-      <c r="G4" s="553">
-        <f t="array" ref="G4:G4">IFERROR(INDEX(F18:F25,MATCH(MIN(L18:L25),L18:L25,0)),"")</f>
-        <v/>
+      <c r="G4" s="553" t="n">
+        <v>0.18</v>
       </c>
       <c r="H4" s="309" t="n"/>
       <c r="I4" s="309" t="n"/>
@@ -12245,9 +12241,8 @@
           <t>Avg Vel:</t>
         </is>
       </c>
-      <c r="E5" s="552">
-        <f t="array" ref="E5:E5">IFERROR(INDEX('Load Log'!H16:H25,MATCH(INDEX(A18:A25,MATCH(MIN(L18:L25),L18:L25,0)),'Load Log'!B16:B25,0)),"")</f>
-        <v/>
+      <c r="E5" s="552" t="n">
+        <v>2780</v>
       </c>
       <c r="F5" s="485" t="inlineStr">
         <is>
@@ -12256,7 +12251,7 @@
       </c>
       <c r="G5" s="258" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR ✓ </t>
+          <t>Vel ✓ SD ✓ MR ✓ Vert ✓</t>
         </is>
       </c>
       <c r="H5" s="309" t="n"/>
@@ -12908,16 +12903,16 @@
         <v>0.12</v>
       </c>
       <c r="H21" s="561" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I21" s="561" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J21" s="561" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K21" s="561" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L21" s="561" t="n">
         <v>0.001</v>
@@ -15373,9 +15368,8 @@
         <f>IF(OR('BallisticX Import'!J17="",'BallisticX Import'!J17=0),"",'BallisticX Import'!J17)</f>
         <v/>
       </c>
-      <c r="O16" s="534">
-        <f>IF(OR('BallisticX Import'!G17="",'BallisticX Import'!G17=0),"",'BallisticX Import'!G17)</f>
-        <v/>
+      <c r="O16" s="534" t="n">
+        <v>0.652</v>
       </c>
       <c r="P16" s="545">
         <f>IF(AND(B16&lt;&gt;"",B16=$D$2),"⭐ WINNER","")</f>
@@ -15460,9 +15454,8 @@
         <f>IF(OR('BallisticX Import'!J18="",'BallisticX Import'!J18=0),"",'BallisticX Import'!J18)</f>
         <v/>
       </c>
-      <c r="O17" s="536">
-        <f>IF(OR('BallisticX Import'!G18="",'BallisticX Import'!G18=0),"",'BallisticX Import'!G18)</f>
-        <v/>
+      <c r="O17" s="536" t="n">
+        <v>0.338</v>
       </c>
       <c r="P17" s="548">
         <f>IF(AND(B17&lt;&gt;"",B17=$D$2),"⭐ WINNER","")</f>
@@ -15547,9 +15540,8 @@
         <f>IF(OR('BallisticX Import'!J19="",'BallisticX Import'!J19=0),"",'BallisticX Import'!J19)</f>
         <v/>
       </c>
-      <c r="O18" s="534">
-        <f>IF(OR('BallisticX Import'!G19="",'BallisticX Import'!G19=0),"",'BallisticX Import'!G19)</f>
-        <v/>
+      <c r="O18" s="534" t="n">
+        <v>0.001</v>
       </c>
       <c r="P18" s="545">
         <f>IF(AND(B18&lt;&gt;"",B18=$D$2),"⭐ WINNER","")</f>
@@ -15634,9 +15626,8 @@
         <f>IF(OR('BallisticX Import'!J20="",'BallisticX Import'!J20=0),"",'BallisticX Import'!J20)</f>
         <v/>
       </c>
-      <c r="O19" s="536">
-        <f>IF(OR('BallisticX Import'!G20="",'BallisticX Import'!G20=0),"",'BallisticX Import'!G20)</f>
-        <v/>
+      <c r="O19" s="536" t="n">
+        <v>0.5590000000000001</v>
       </c>
       <c r="P19" s="548">
         <f>IF(AND(B19&lt;&gt;"",B19=$D$2),"⭐ WINNER","")</f>
@@ -15721,9 +15712,8 @@
         <f>IF(OR('BallisticX Import'!J21="",'BallisticX Import'!J21=0),"",'BallisticX Import'!J21)</f>
         <v/>
       </c>
-      <c r="O20" s="534">
-        <f>IF(OR('BallisticX Import'!G21="",'BallisticX Import'!G21=0),"",'BallisticX Import'!G21)</f>
-        <v/>
+      <c r="O20" s="534" t="n">
+        <v>1</v>
       </c>
       <c r="P20" s="545">
         <f>IF(AND(B20&lt;&gt;"",B20=$D$2),"⭐ WINNER","")</f>
@@ -15809,7 +15799,7 @@
         <v/>
       </c>
       <c r="O21" s="536">
-        <f>IF(OR('BallisticX Import'!G22="",'BallisticX Import'!G22=0),"",'BallisticX Import'!G22)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P21" s="548">
@@ -15896,7 +15886,7 @@
         <v/>
       </c>
       <c r="O22" s="534">
-        <f>IF(OR('BallisticX Import'!G23="",'BallisticX Import'!G23=0),"",'BallisticX Import'!G23)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P22" s="545">
@@ -15983,7 +15973,7 @@
         <v/>
       </c>
       <c r="O23" s="536">
-        <f>IF(OR('BallisticX Import'!G24="",'BallisticX Import'!G24=0),"",'BallisticX Import'!G24)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P23" s="548">
@@ -16070,7 +16060,7 @@
         <v/>
       </c>
       <c r="O24" s="534">
-        <f>IF(OR('BallisticX Import'!G25="",'BallisticX Import'!G25=0),"",'BallisticX Import'!G25)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P24" s="545">
@@ -16157,7 +16147,7 @@
         <v/>
       </c>
       <c r="O25" s="536">
-        <f>IF(OR('BallisticX Import'!G26="",'BallisticX Import'!G26=0),"",'BallisticX Import'!G26)</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="P25" s="548">
@@ -16607,16 +16597,16 @@
         <v>0.1</v>
       </c>
       <c r="H32" s="451" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I32" s="451" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J32" s="451" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K32" s="451" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L32" s="451" t="n">
         <v>0.001</v>
@@ -16824,19 +16814,19 @@
         <v/>
       </c>
       <c r="H35" s="453">
-        <f>IF(D35="","",IFERROR((D35-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="I35" s="453">
-        <f>IF(D35="","",IFERROR((E35-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="J35" s="453">
-        <f>IF(D35="","",IFERROR((F35-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="K35" s="453">
-        <f>IF(D35="","",IFERROR((G35-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="L35" s="453">
@@ -16906,19 +16896,19 @@
         <v/>
       </c>
       <c r="H36" s="451">
-        <f>IF(D36="","",IFERROR((D36-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="I36" s="451">
-        <f>IF(D36="","",IFERROR((E36-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="J36" s="451">
-        <f>IF(D36="","",IFERROR((F36-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="K36" s="451">
-        <f>IF(D36="","",IFERROR((G36-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="L36" s="451">
@@ -16988,19 +16978,19 @@
         <v/>
       </c>
       <c r="H37" s="453">
-        <f>IF(D37="","",IFERROR((D37-MIN($D$30:$D$37))/(MAX($D$30:$D$37)-MIN($D$30:$D$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="I37" s="453">
-        <f>IF(D37="","",IFERROR((E37-MIN($E$30:$E$37))/(MAX($E$30:$E$37)-MIN($E$30:$E$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="J37" s="453">
-        <f>IF(D37="","",IFERROR((F37-MIN($F$30:$F$37))/(MAX($F$30:$F$37)-MIN($F$30:$F$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="K37" s="453">
-        <f>IF(D37="","",IFERROR((G37-MIN($G$30:$G$37))/(MAX($G$30:$G$37)-MIN($G$30:$G$37)),0))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="L37" s="453">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -2805,7 +2805,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9223,7 +9223,7 @@
       <c r="AF1" s="317" t="n"/>
       <c r="AG1" s="317" t="n"/>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="141">
+    <row r="2" ht="38" customHeight="1" s="141">
       <c r="A2" s="521" t="inlineStr">
         <is>
           <t>SUGGESTED CHARGE →</t>
@@ -9477,14 +9477,18 @@
       <c r="AF6" s="317" t="n"/>
       <c r="AG6" s="317" t="n"/>
     </row>
-    <row r="7" ht="6" customHeight="1" s="141">
+    <row r="7" ht="22" customHeight="1" s="141">
       <c r="A7" s="317" t="n"/>
       <c r="B7" s="317" t="n"/>
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
       <c r="F7" s="317" t="n"/>
-      <c r="G7" s="317" t="n"/>
+      <c r="G7" s="317" t="inlineStr">
+        <is>
+          <t>0.1 Mil</t>
+        </is>
+      </c>
       <c r="H7" s="309" t="n"/>
       <c r="I7" s="309" t="n"/>
       <c r="J7" s="309" t="n"/>
@@ -14526,7 +14530,7 @@
       <c r="AK1" s="317" t="n"/>
       <c r="AL1" s="317" t="n"/>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="141">
+    <row r="2" ht="38" customHeight="1" s="141">
       <c r="A2" s="521" t="inlineStr">
         <is>
           <t>SUGGESTED JUMP →</t>
@@ -14813,14 +14817,18 @@
       <c r="AK6" s="317" t="n"/>
       <c r="AL6" s="317" t="n"/>
     </row>
-    <row r="7" ht="6" customHeight="1" s="141">
+    <row r="7" ht="22" customHeight="1" s="141">
       <c r="A7" s="317" t="n"/>
       <c r="B7" s="317" t="n"/>
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
       <c r="F7" s="317" t="n"/>
-      <c r="G7" s="317" t="n"/>
+      <c r="G7" s="317" t="inlineStr">
+        <is>
+          <t>0.1 Mil</t>
+        </is>
+      </c>
       <c r="H7" s="317" t="n"/>
       <c r="I7" s="317" t="n"/>
       <c r="J7" s="317" t="n"/>
@@ -15116,7 +15124,11 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B13" s="331" t="n"/>
+      <c r="B13" s="331" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="C13" s="322" t="n"/>
       <c r="D13" s="322" t="n"/>
       <c r="E13" s="323" t="n"/>
@@ -16177,7 +16189,7 @@
       <c r="AK25" s="317" t="n"/>
       <c r="AL25" s="317" t="n"/>
     </row>
-    <row r="26" ht="7.5" customHeight="1" s="141">
+    <row r="26" ht="30" customHeight="1" s="141">
       <c r="A26" s="201" t="inlineStr">
         <is>
           <t>→  Save Suggested Load to Library  ←</t>
@@ -19505,6 +19517,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.1 Mil,0.05 Mil,1/4 MOA,1/8 MOA"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" display="Save Suggested Load to Library" r:id="rId2"/>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -32,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="0.0&quot; gr&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot; fps&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot; fps&quot;"/>
@@ -49,6 +49,8 @@
     <numFmt numFmtId="177" formatCode="[=NA()]&quot;&quot;;0"/>
     <numFmt numFmtId="178" formatCode="[=NA()]&quot;&quot;;0.0&quot; gr&quot;"/>
     <numFmt numFmtId="179" formatCode="[=NA()]&quot;&quot;;0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="64">
     <font>
@@ -992,7 +994,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="584">
+  <cellXfs count="586">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2807,6 +2809,10 @@
     <xf numFmtId="0" fontId="63" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="181" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2815,6 +2821,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9260,7 +9269,7 @@
       </c>
       <c r="M2" s="579" t="inlineStr">
         <is>
-          <t>Best in:  Vel ✓ SD ✓ MR ✓ Vert ✓</t>
+          <t>Best in:  All metrics ✓</t>
         </is>
       </c>
       <c r="Q2" s="317" t="n"/>
@@ -9483,7 +9492,11 @@
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
-      <c r="F7" s="317" t="n"/>
+      <c r="F7" s="317" t="inlineStr">
+        <is>
+          <t>Scope click:</t>
+        </is>
+      </c>
       <c r="G7" s="317" t="inlineStr">
         <is>
           <t>0.1 Mil</t>
@@ -9754,10 +9767,8 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B13" s="331" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="B13" s="580" t="n">
+        <v>46124</v>
       </c>
       <c r="C13" s="322" t="n"/>
       <c r="D13" s="322" t="n"/>
@@ -12205,11 +12216,11 @@
       <c r="A4" s="309" t="n"/>
       <c r="B4" s="506" t="n"/>
       <c r="C4" s="507" t="n"/>
-      <c r="D4" s="580">
+      <c r="D4" s="581">
         <f>IF($B$100="window","Vel Spread:","")</f>
         <v/>
       </c>
-      <c r="E4" s="581">
+      <c r="E4" s="582">
         <f>IF($B$100="window",IFERROR(INDEX(D18:D25,MATCH(MIN(L18:L25),L18:L25,0)),""),"")</f>
         <v/>
       </c>
@@ -12255,7 +12266,7 @@
       </c>
       <c r="G5" s="258" t="inlineStr">
         <is>
-          <t>Vel ✓ SD ✓ MR ✓ Vert ✓</t>
+          <t>All metrics ✓</t>
         </is>
       </c>
       <c r="H5" s="309" t="n"/>
@@ -12279,17 +12290,17 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B6" s="582" t="n"/>
-      <c r="C6" s="582" t="n"/>
-      <c r="D6" s="582" t="n"/>
-      <c r="E6" s="582" t="n"/>
-      <c r="F6" s="582" t="n"/>
-      <c r="G6" s="582" t="n"/>
-      <c r="H6" s="582" t="n"/>
-      <c r="I6" s="582" t="n"/>
-      <c r="J6" s="582" t="n"/>
-      <c r="K6" s="582" t="n"/>
-      <c r="L6" s="583" t="n"/>
+      <c r="B6" s="583" t="n"/>
+      <c r="C6" s="583" t="n"/>
+      <c r="D6" s="583" t="n"/>
+      <c r="E6" s="583" t="n"/>
+      <c r="F6" s="583" t="n"/>
+      <c r="G6" s="583" t="n"/>
+      <c r="H6" s="583" t="n"/>
+      <c r="I6" s="583" t="n"/>
+      <c r="J6" s="583" t="n"/>
+      <c r="K6" s="583" t="n"/>
+      <c r="L6" s="584" t="n"/>
       <c r="M6" s="309" t="n"/>
       <c r="N6" s="309" t="n"/>
       <c r="O6" s="309" t="n"/>
@@ -12464,17 +12475,17 @@
           <t>→  Reset weights to Loadscope defaults  ←</t>
         </is>
       </c>
-      <c r="B12" s="582" t="n"/>
-      <c r="C12" s="582" t="n"/>
-      <c r="D12" s="582" t="n"/>
-      <c r="E12" s="582" t="n"/>
-      <c r="F12" s="582" t="n"/>
-      <c r="G12" s="582" t="n"/>
-      <c r="H12" s="582" t="n"/>
-      <c r="I12" s="582" t="n"/>
-      <c r="J12" s="582" t="n"/>
-      <c r="K12" s="582" t="n"/>
-      <c r="L12" s="583" t="n"/>
+      <c r="B12" s="583" t="n"/>
+      <c r="C12" s="583" t="n"/>
+      <c r="D12" s="583" t="n"/>
+      <c r="E12" s="583" t="n"/>
+      <c r="F12" s="583" t="n"/>
+      <c r="G12" s="583" t="n"/>
+      <c r="H12" s="583" t="n"/>
+      <c r="I12" s="583" t="n"/>
+      <c r="J12" s="583" t="n"/>
+      <c r="K12" s="583" t="n"/>
+      <c r="L12" s="584" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="141">
       <c r="A13" s="349" t="inlineStr">
@@ -12943,7 +12954,7 @@
       </c>
       <c r="R21" s="140" t="inlineStr">
         <is>
-          <t>Vel ✓ SD ✓ MR ✓ Vert ✓</t>
+          <t>All metrics ✓</t>
         </is>
       </c>
       <c r="S21" s="309" t="n"/>
@@ -14575,7 +14586,7 @@
       </c>
       <c r="O2" s="579" t="inlineStr">
         <is>
-          <t>Best in:  Vel ✓ SD ✓ MR ✓ Vert ✓</t>
+          <t>Best in:  All metrics ✓</t>
         </is>
       </c>
       <c r="Q2" s="317" t="n"/>
@@ -14823,7 +14834,11 @@
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
-      <c r="F7" s="317" t="n"/>
+      <c r="F7" s="317" t="inlineStr">
+        <is>
+          <t>Scope click:</t>
+        </is>
+      </c>
       <c r="G7" s="317" t="inlineStr">
         <is>
           <t>0.1 Mil</t>
@@ -15124,10 +15139,8 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B13" s="331" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
+      <c r="B13" s="580" t="n">
+        <v>46138</v>
       </c>
       <c r="C13" s="322" t="n"/>
       <c r="D13" s="322" t="n"/>
@@ -16195,21 +16208,21 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B26" s="582" t="n"/>
-      <c r="C26" s="582" t="n"/>
-      <c r="D26" s="582" t="n"/>
-      <c r="E26" s="582" t="n"/>
-      <c r="F26" s="582" t="n"/>
-      <c r="G26" s="582" t="n"/>
-      <c r="H26" s="582" t="n"/>
-      <c r="I26" s="582" t="n"/>
-      <c r="J26" s="582" t="n"/>
-      <c r="K26" s="582" t="n"/>
-      <c r="L26" s="582" t="n"/>
-      <c r="M26" s="582" t="n"/>
-      <c r="N26" s="582" t="n"/>
-      <c r="O26" s="582" t="n"/>
-      <c r="P26" s="583" t="n"/>
+      <c r="B26" s="583" t="n"/>
+      <c r="C26" s="583" t="n"/>
+      <c r="D26" s="583" t="n"/>
+      <c r="E26" s="583" t="n"/>
+      <c r="F26" s="583" t="n"/>
+      <c r="G26" s="583" t="n"/>
+      <c r="H26" s="583" t="n"/>
+      <c r="I26" s="583" t="n"/>
+      <c r="J26" s="583" t="n"/>
+      <c r="K26" s="583" t="n"/>
+      <c r="L26" s="583" t="n"/>
+      <c r="M26" s="583" t="n"/>
+      <c r="N26" s="583" t="n"/>
+      <c r="O26" s="583" t="n"/>
+      <c r="P26" s="584" t="n"/>
       <c r="Q26" s="317" t="n"/>
       <c r="R26" s="317" t="n"/>
       <c r="S26" s="317" t="n"/>
@@ -16277,8 +16290,8 @@
       <c r="AK27" s="317" t="n"/>
       <c r="AL27" s="317" t="n"/>
     </row>
-    <row r="28" ht="21.75" customHeight="1" s="141">
-      <c r="A28" s="201" t="inlineStr">
+    <row r="28" ht="32" customHeight="1" s="141">
+      <c r="A28" s="585" t="inlineStr">
         <is>
           <t>→  Reset weights (hover for rationale)  ←</t>
         </is>
@@ -25813,16 +25826,16 @@
           <t>→  Print Pocket Range Card  ←</t>
         </is>
       </c>
-      <c r="B2" s="582" t="n"/>
-      <c r="C2" s="582" t="n"/>
-      <c r="D2" s="582" t="n"/>
-      <c r="E2" s="582" t="n"/>
-      <c r="F2" s="582" t="n"/>
-      <c r="G2" s="582" t="n"/>
-      <c r="H2" s="582" t="n"/>
-      <c r="I2" s="582" t="n"/>
-      <c r="J2" s="582" t="n"/>
-      <c r="K2" s="583" t="n"/>
+      <c r="B2" s="583" t="n"/>
+      <c r="C2" s="583" t="n"/>
+      <c r="D2" s="583" t="n"/>
+      <c r="E2" s="583" t="n"/>
+      <c r="F2" s="583" t="n"/>
+      <c r="G2" s="583" t="n"/>
+      <c r="H2" s="583" t="n"/>
+      <c r="I2" s="583" t="n"/>
+      <c r="J2" s="583" t="n"/>
+      <c r="K2" s="584" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1" s="141">
       <c r="A3" s="309" t="n"/>
@@ -25843,16 +25856,16 @@
           <t>Enter your DOPE values in MILS or MOA. Click counts auto-calculate based on your scope's click value (set on the Load Log tab — Click: dropdown).</t>
         </is>
       </c>
-      <c r="B4" s="582" t="n"/>
-      <c r="C4" s="582" t="n"/>
-      <c r="D4" s="582" t="n"/>
-      <c r="E4" s="582" t="n"/>
-      <c r="F4" s="582" t="n"/>
-      <c r="G4" s="582" t="n"/>
-      <c r="H4" s="582" t="n"/>
-      <c r="I4" s="582" t="n"/>
-      <c r="J4" s="582" t="n"/>
-      <c r="K4" s="583" t="n"/>
+      <c r="B4" s="583" t="n"/>
+      <c r="C4" s="583" t="n"/>
+      <c r="D4" s="583" t="n"/>
+      <c r="E4" s="583" t="n"/>
+      <c r="F4" s="583" t="n"/>
+      <c r="G4" s="583" t="n"/>
+      <c r="H4" s="583" t="n"/>
+      <c r="I4" s="583" t="n"/>
+      <c r="J4" s="583" t="n"/>
+      <c r="K4" s="584" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1" s="141">
       <c r="A5" s="381" t="inlineStr">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -52,7 +52,7 @@
     <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="64">
+  <fonts count="66">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -455,10 +455,17 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FF1F4E78"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="FFFFFF00"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -692,8 +699,14 @@
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE082"/>
+        <bgColor rgb="FFFFE082"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -983,6 +996,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -994,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="586">
+  <cellXfs count="590">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2806,8 +2833,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="65" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="41" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="25" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="181" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2821,6 +2859,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9486,25 +9528,25 @@
       <c r="AF6" s="317" t="n"/>
       <c r="AG6" s="317" t="n"/>
     </row>
-    <row r="7" ht="22" customHeight="1" s="141">
+    <row r="7" ht="31.5" customHeight="1" s="141">
       <c r="A7" s="317" t="n"/>
       <c r="B7" s="317" t="n"/>
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
-      <c r="F7" s="317" t="inlineStr">
-        <is>
-          <t>Scope click:</t>
-        </is>
-      </c>
-      <c r="G7" s="317" t="inlineStr">
+      <c r="F7" s="580" t="inlineStr">
+        <is>
+          <t>Turret:</t>
+        </is>
+      </c>
+      <c r="G7" s="581" t="inlineStr">
         <is>
           <t>0.1 Mil</t>
         </is>
       </c>
-      <c r="H7" s="309" t="n"/>
-      <c r="I7" s="309" t="n"/>
-      <c r="J7" s="309" t="n"/>
+      <c r="H7" s="582" t="n"/>
+      <c r="I7" s="582" t="n"/>
+      <c r="J7" s="582" t="n"/>
       <c r="K7" s="317" t="n"/>
       <c r="L7" s="317" t="n"/>
       <c r="M7" s="317" t="n"/>
@@ -9767,7 +9809,7 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B13" s="580" t="n">
+      <c r="B13" s="583" t="n">
         <v>46124</v>
       </c>
       <c r="C13" s="322" t="n"/>
@@ -12070,8 +12112,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"0.1 Mil,0.05 Mil,1/4 MOA,1/8 MOA"</formula1>
+    <dataValidation sqref="G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.1 Mil,0.05 Mil,1/4 MOA,1/8 MOA,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -12216,11 +12258,11 @@
       <c r="A4" s="309" t="n"/>
       <c r="B4" s="506" t="n"/>
       <c r="C4" s="507" t="n"/>
-      <c r="D4" s="581">
+      <c r="D4" s="584">
         <f>IF($B$100="window","Vel Spread:","")</f>
         <v/>
       </c>
-      <c r="E4" s="582">
+      <c r="E4" s="585">
         <f>IF($B$100="window",IFERROR(INDEX(D18:D25,MATCH(MIN(L18:L25),L18:L25,0)),""),"")</f>
         <v/>
       </c>
@@ -12290,17 +12332,17 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B6" s="583" t="n"/>
-      <c r="C6" s="583" t="n"/>
-      <c r="D6" s="583" t="n"/>
-      <c r="E6" s="583" t="n"/>
-      <c r="F6" s="583" t="n"/>
-      <c r="G6" s="583" t="n"/>
-      <c r="H6" s="583" t="n"/>
-      <c r="I6" s="583" t="n"/>
-      <c r="J6" s="583" t="n"/>
-      <c r="K6" s="583" t="n"/>
-      <c r="L6" s="584" t="n"/>
+      <c r="B6" s="586" t="n"/>
+      <c r="C6" s="586" t="n"/>
+      <c r="D6" s="586" t="n"/>
+      <c r="E6" s="586" t="n"/>
+      <c r="F6" s="586" t="n"/>
+      <c r="G6" s="586" t="n"/>
+      <c r="H6" s="586" t="n"/>
+      <c r="I6" s="586" t="n"/>
+      <c r="J6" s="586" t="n"/>
+      <c r="K6" s="586" t="n"/>
+      <c r="L6" s="587" t="n"/>
       <c r="M6" s="309" t="n"/>
       <c r="N6" s="309" t="n"/>
       <c r="O6" s="309" t="n"/>
@@ -12475,17 +12517,17 @@
           <t>→  Reset weights to Loadscope defaults  ←</t>
         </is>
       </c>
-      <c r="B12" s="583" t="n"/>
-      <c r="C12" s="583" t="n"/>
-      <c r="D12" s="583" t="n"/>
-      <c r="E12" s="583" t="n"/>
-      <c r="F12" s="583" t="n"/>
-      <c r="G12" s="583" t="n"/>
-      <c r="H12" s="583" t="n"/>
-      <c r="I12" s="583" t="n"/>
-      <c r="J12" s="583" t="n"/>
-      <c r="K12" s="583" t="n"/>
-      <c r="L12" s="584" t="n"/>
+      <c r="B12" s="586" t="n"/>
+      <c r="C12" s="586" t="n"/>
+      <c r="D12" s="586" t="n"/>
+      <c r="E12" s="586" t="n"/>
+      <c r="F12" s="586" t="n"/>
+      <c r="G12" s="586" t="n"/>
+      <c r="H12" s="586" t="n"/>
+      <c r="I12" s="586" t="n"/>
+      <c r="J12" s="586" t="n"/>
+      <c r="K12" s="586" t="n"/>
+      <c r="L12" s="587" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="141">
       <c r="A13" s="349" t="inlineStr">
@@ -14828,25 +14870,25 @@
       <c r="AK6" s="317" t="n"/>
       <c r="AL6" s="317" t="n"/>
     </row>
-    <row r="7" ht="22" customHeight="1" s="141">
+    <row r="7" ht="31.5" customHeight="1" s="141">
       <c r="A7" s="317" t="n"/>
       <c r="B7" s="317" t="n"/>
       <c r="C7" s="317" t="n"/>
       <c r="D7" s="317" t="n"/>
       <c r="E7" s="317" t="n"/>
-      <c r="F7" s="317" t="inlineStr">
-        <is>
-          <t>Scope click:</t>
-        </is>
-      </c>
-      <c r="G7" s="317" t="inlineStr">
+      <c r="F7" s="580" t="inlineStr">
+        <is>
+          <t>Turret:</t>
+        </is>
+      </c>
+      <c r="G7" s="581" t="inlineStr">
         <is>
           <t>0.1 Mil</t>
         </is>
       </c>
-      <c r="H7" s="317" t="n"/>
-      <c r="I7" s="317" t="n"/>
-      <c r="J7" s="317" t="n"/>
+      <c r="H7" s="588" t="n"/>
+      <c r="I7" s="588" t="n"/>
+      <c r="J7" s="588" t="n"/>
       <c r="K7" s="317" t="n"/>
       <c r="L7" s="317" t="n"/>
       <c r="M7" s="317" t="n"/>
@@ -15139,7 +15181,7 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B13" s="580" t="n">
+      <c r="B13" s="583" t="n">
         <v>46138</v>
       </c>
       <c r="C13" s="322" t="n"/>
@@ -16208,21 +16250,21 @@
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B26" s="583" t="n"/>
-      <c r="C26" s="583" t="n"/>
-      <c r="D26" s="583" t="n"/>
-      <c r="E26" s="583" t="n"/>
-      <c r="F26" s="583" t="n"/>
-      <c r="G26" s="583" t="n"/>
-      <c r="H26" s="583" t="n"/>
-      <c r="I26" s="583" t="n"/>
-      <c r="J26" s="583" t="n"/>
-      <c r="K26" s="583" t="n"/>
-      <c r="L26" s="583" t="n"/>
-      <c r="M26" s="583" t="n"/>
-      <c r="N26" s="583" t="n"/>
-      <c r="O26" s="583" t="n"/>
-      <c r="P26" s="584" t="n"/>
+      <c r="B26" s="586" t="n"/>
+      <c r="C26" s="586" t="n"/>
+      <c r="D26" s="586" t="n"/>
+      <c r="E26" s="586" t="n"/>
+      <c r="F26" s="586" t="n"/>
+      <c r="G26" s="586" t="n"/>
+      <c r="H26" s="586" t="n"/>
+      <c r="I26" s="586" t="n"/>
+      <c r="J26" s="586" t="n"/>
+      <c r="K26" s="586" t="n"/>
+      <c r="L26" s="586" t="n"/>
+      <c r="M26" s="586" t="n"/>
+      <c r="N26" s="586" t="n"/>
+      <c r="O26" s="586" t="n"/>
+      <c r="P26" s="587" t="n"/>
       <c r="Q26" s="317" t="n"/>
       <c r="R26" s="317" t="n"/>
       <c r="S26" s="317" t="n"/>
@@ -16291,7 +16333,7 @@
       <c r="AL27" s="317" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1" s="141">
-      <c r="A28" s="585" t="inlineStr">
+      <c r="A28" s="589" t="inlineStr">
         <is>
           <t>→  Reset weights (hover for rationale)  ←</t>
         </is>
@@ -19532,7 +19574,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"0.1 Mil,0.05 Mil,1/4 MOA,1/8 MOA"</formula1>
+      <formula1>"0.1 Mil,0.05 Mil,1/4 MOA,1/8 MOA,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -25826,16 +25868,16 @@
           <t>→  Print Pocket Range Card  ←</t>
         </is>
       </c>
-      <c r="B2" s="583" t="n"/>
-      <c r="C2" s="583" t="n"/>
-      <c r="D2" s="583" t="n"/>
-      <c r="E2" s="583" t="n"/>
-      <c r="F2" s="583" t="n"/>
-      <c r="G2" s="583" t="n"/>
-      <c r="H2" s="583" t="n"/>
-      <c r="I2" s="583" t="n"/>
-      <c r="J2" s="583" t="n"/>
-      <c r="K2" s="584" t="n"/>
+      <c r="B2" s="586" t="n"/>
+      <c r="C2" s="586" t="n"/>
+      <c r="D2" s="586" t="n"/>
+      <c r="E2" s="586" t="n"/>
+      <c r="F2" s="586" t="n"/>
+      <c r="G2" s="586" t="n"/>
+      <c r="H2" s="586" t="n"/>
+      <c r="I2" s="586" t="n"/>
+      <c r="J2" s="586" t="n"/>
+      <c r="K2" s="587" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1" s="141">
       <c r="A3" s="309" t="n"/>
@@ -25856,16 +25898,16 @@
           <t>Enter your DOPE values in MILS or MOA. Click counts auto-calculate based on your scope's click value (set on the Load Log tab — Click: dropdown).</t>
         </is>
       </c>
-      <c r="B4" s="583" t="n"/>
-      <c r="C4" s="583" t="n"/>
-      <c r="D4" s="583" t="n"/>
-      <c r="E4" s="583" t="n"/>
-      <c r="F4" s="583" t="n"/>
-      <c r="G4" s="583" t="n"/>
-      <c r="H4" s="583" t="n"/>
-      <c r="I4" s="583" t="n"/>
-      <c r="J4" s="583" t="n"/>
-      <c r="K4" s="584" t="n"/>
+      <c r="B4" s="586" t="n"/>
+      <c r="C4" s="586" t="n"/>
+      <c r="D4" s="586" t="n"/>
+      <c r="E4" s="586" t="n"/>
+      <c r="F4" s="586" t="n"/>
+      <c r="G4" s="586" t="n"/>
+      <c r="H4" s="586" t="n"/>
+      <c r="I4" s="586" t="n"/>
+      <c r="J4" s="586" t="n"/>
+      <c r="K4" s="587" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1" s="141">
       <c r="A5" s="381" t="inlineStr">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -1021,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="590">
+  <cellXfs count="589">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2859,12 +2859,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -14886,9 +14882,9 @@
           <t>0.1 Mil</t>
         </is>
       </c>
-      <c r="H7" s="588" t="n"/>
-      <c r="I7" s="588" t="n"/>
-      <c r="J7" s="588" t="n"/>
+      <c r="H7" s="582" t="n"/>
+      <c r="I7" s="582" t="n"/>
+      <c r="J7" s="582" t="n"/>
       <c r="K7" s="317" t="n"/>
       <c r="L7" s="317" t="n"/>
       <c r="M7" s="317" t="n"/>
@@ -16332,10 +16328,10 @@
       <c r="AK27" s="317" t="n"/>
       <c r="AL27" s="317" t="n"/>
     </row>
-    <row r="28" ht="32" customHeight="1" s="141">
-      <c r="A28" s="589" t="inlineStr">
-        <is>
-          <t>→  Reset weights (hover for rationale)  ←</t>
+    <row r="28" ht="24" customHeight="1" s="141">
+      <c r="A28" s="588" t="inlineStr">
+        <is>
+          <t>↺ Reset weights</t>
         </is>
       </c>
       <c r="B28" s="447" t="inlineStr">
@@ -19359,7 +19355,7 @@
     <row r="1000" ht="15.75" customHeight="1" s="141"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="B6:E6"/>
@@ -19374,6 +19370,7 @@
     <mergeCell ref="L5:P5"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="L10:P10"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="G6:J6"/>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -2859,7 +2859,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="63" fillId="41" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14516,7 +14516,7 @@
   <dimension ref="A1:AL100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="140" min="1" max="10"/>
+    <col width="16" customWidth="1" style="140" min="1" max="10"/>
     <col width="10" customWidth="1" style="141" min="2" max="2"/>
     <col width="8" customWidth="1" style="141" min="3" max="3"/>
     <col width="7" customWidth="1" style="141" min="4" max="4"/>
@@ -16331,7 +16331,7 @@
     <row r="28" ht="24" customHeight="1" s="141">
       <c r="A28" s="588" t="inlineStr">
         <is>
-          <t>↺ Reset weights</t>
+          <t>Reset weights</t>
         </is>
       </c>
       <c r="B28" s="447" t="inlineStr">

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -1021,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="589">
+  <cellXfs count="592">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2857,10 +2857,21 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="2" fontId="63" fillId="41" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="63" fillId="41" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -12323,22 +12334,22 @@
       <c r="U5" s="309" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1" s="141">
-      <c r="A6" s="201" t="inlineStr">
+      <c r="A6" s="586" t="inlineStr">
         <is>
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B6" s="586" t="n"/>
-      <c r="C6" s="586" t="n"/>
-      <c r="D6" s="586" t="n"/>
-      <c r="E6" s="586" t="n"/>
-      <c r="F6" s="586" t="n"/>
-      <c r="G6" s="586" t="n"/>
-      <c r="H6" s="586" t="n"/>
-      <c r="I6" s="586" t="n"/>
-      <c r="J6" s="586" t="n"/>
-      <c r="K6" s="586" t="n"/>
-      <c r="L6" s="587" t="n"/>
+      <c r="B6" s="587" t="n"/>
+      <c r="C6" s="587" t="n"/>
+      <c r="D6" s="587" t="n"/>
+      <c r="E6" s="587" t="n"/>
+      <c r="F6" s="587" t="n"/>
+      <c r="G6" s="587" t="n"/>
+      <c r="H6" s="587" t="n"/>
+      <c r="I6" s="587" t="n"/>
+      <c r="J6" s="587" t="n"/>
+      <c r="K6" s="587" t="n"/>
+      <c r="L6" s="588" t="n"/>
       <c r="M6" s="309" t="n"/>
       <c r="N6" s="309" t="n"/>
       <c r="O6" s="309" t="n"/>
@@ -12508,22 +12519,22 @@
       <c r="U11" s="309" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1" s="141">
-      <c r="A12" s="201" t="inlineStr">
+      <c r="A12" s="586" t="inlineStr">
         <is>
           <t>→  Reset weights to Loadscope defaults  ←</t>
         </is>
       </c>
-      <c r="B12" s="586" t="n"/>
-      <c r="C12" s="586" t="n"/>
-      <c r="D12" s="586" t="n"/>
-      <c r="E12" s="586" t="n"/>
-      <c r="F12" s="586" t="n"/>
-      <c r="G12" s="586" t="n"/>
-      <c r="H12" s="586" t="n"/>
-      <c r="I12" s="586" t="n"/>
-      <c r="J12" s="586" t="n"/>
-      <c r="K12" s="586" t="n"/>
-      <c r="L12" s="587" t="n"/>
+      <c r="B12" s="587" t="n"/>
+      <c r="C12" s="587" t="n"/>
+      <c r="D12" s="587" t="n"/>
+      <c r="E12" s="587" t="n"/>
+      <c r="F12" s="587" t="n"/>
+      <c r="G12" s="587" t="n"/>
+      <c r="H12" s="587" t="n"/>
+      <c r="I12" s="587" t="n"/>
+      <c r="J12" s="587" t="n"/>
+      <c r="K12" s="587" t="n"/>
+      <c r="L12" s="588" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="141">
       <c r="A13" s="349" t="inlineStr">
@@ -12622,23 +12633,17 @@
       <c r="U16" s="309" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1" s="141">
-      <c r="A17" s="557">
-        <f>IF($B$100="window","Middle Charge","Charge")</f>
-        <v/>
-      </c>
-      <c r="B17" s="261" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C17" s="261" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D17" s="557">
-        <f>IF($B$100="window","Vel Spread (fps)","Avg Vel (fps)")</f>
-        <v/>
+      <c r="A17" s="557" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="B17" s="261" t="n"/>
+      <c r="C17" s="261" t="n"/>
+      <c r="D17" s="557" t="inlineStr">
+        <is>
+          <t>Avg Vel (fps)</t>
+        </is>
       </c>
       <c r="E17" s="478" t="inlineStr">
         <is>
@@ -12657,7 +12662,7 @@
       </c>
       <c r="H17" s="478" t="inlineStr">
         <is>
-          <t>Norm Spread</t>
+          <t>Norm Vel</t>
         </is>
       </c>
       <c r="I17" s="478" t="inlineStr">
@@ -12727,12 +12732,8 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B17,IF('Load Log'!B16="","",'Load Log'!B16)),"")</f>
         <v/>
       </c>
-      <c r="B18" s="558" t="n">
-        <v>2705</v>
-      </c>
-      <c r="C18" s="558" t="n">
-        <v>2724</v>
-      </c>
+      <c r="B18" s="558" t="n"/>
+      <c r="C18" s="558" t="n"/>
       <c r="D18" s="559" t="n">
         <v>2715</v>
       </c>
@@ -12797,12 +12798,8 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B18,IF('Load Log'!B17="","",'Load Log'!B17)),"")</f>
         <v/>
       </c>
-      <c r="B19" s="562" t="n">
-        <v>2725</v>
-      </c>
-      <c r="C19" s="562" t="n">
-        <v>2748</v>
-      </c>
+      <c r="B19" s="562" t="n"/>
+      <c r="C19" s="562" t="n"/>
       <c r="D19" s="563" t="n">
         <v>2737</v>
       </c>
@@ -12867,12 +12864,8 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B19,IF('Load Log'!B18="","",'Load Log'!B18)),"")</f>
         <v/>
       </c>
-      <c r="B20" s="558" t="n">
-        <v>2750</v>
-      </c>
-      <c r="C20" s="558" t="n">
-        <v>2770</v>
-      </c>
+      <c r="B20" s="558" t="n"/>
+      <c r="C20" s="558" t="n"/>
       <c r="D20" s="559" t="n">
         <v>2760</v>
       </c>
@@ -12937,12 +12930,8 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B20,IF('Load Log'!B19="","",'Load Log'!B19)),"")</f>
         <v/>
       </c>
-      <c r="B21" s="562" t="n">
-        <v>2776</v>
-      </c>
-      <c r="C21" s="562" t="n">
-        <v>2784</v>
-      </c>
+      <c r="B21" s="562" t="n"/>
+      <c r="C21" s="562" t="n"/>
       <c r="D21" s="563" t="n">
         <v>2780</v>
       </c>
@@ -13008,12 +12997,8 @@
         <f>IFERROR(IF($B$100="window",'Load Log'!B21,IF('Load Log'!B20="","",'Load Log'!B20)),"")</f>
         <v/>
       </c>
-      <c r="B22" s="558" t="n">
-        <v>2795</v>
-      </c>
-      <c r="C22" s="558" t="n">
-        <v>2812</v>
-      </c>
+      <c r="B22" s="558" t="n"/>
+      <c r="C22" s="558" t="n"/>
       <c r="D22" s="559" t="n">
         <v>2803</v>
       </c>
@@ -16241,26 +16226,26 @@
       <c r="AL25" s="317" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="141">
-      <c r="A26" s="201" t="inlineStr">
+      <c r="A26" s="586" t="inlineStr">
         <is>
           <t>→  Save Suggested Load to Library  ←</t>
         </is>
       </c>
-      <c r="B26" s="586" t="n"/>
-      <c r="C26" s="586" t="n"/>
-      <c r="D26" s="586" t="n"/>
-      <c r="E26" s="586" t="n"/>
-      <c r="F26" s="586" t="n"/>
-      <c r="G26" s="586" t="n"/>
-      <c r="H26" s="586" t="n"/>
-      <c r="I26" s="586" t="n"/>
-      <c r="J26" s="586" t="n"/>
-      <c r="K26" s="586" t="n"/>
-      <c r="L26" s="586" t="n"/>
-      <c r="M26" s="586" t="n"/>
-      <c r="N26" s="586" t="n"/>
-      <c r="O26" s="586" t="n"/>
-      <c r="P26" s="587" t="n"/>
+      <c r="B26" s="587" t="n"/>
+      <c r="C26" s="587" t="n"/>
+      <c r="D26" s="587" t="n"/>
+      <c r="E26" s="587" t="n"/>
+      <c r="F26" s="587" t="n"/>
+      <c r="G26" s="587" t="n"/>
+      <c r="H26" s="587" t="n"/>
+      <c r="I26" s="587" t="n"/>
+      <c r="J26" s="587" t="n"/>
+      <c r="K26" s="587" t="n"/>
+      <c r="L26" s="587" t="n"/>
+      <c r="M26" s="587" t="n"/>
+      <c r="N26" s="587" t="n"/>
+      <c r="O26" s="587" t="n"/>
+      <c r="P26" s="588" t="n"/>
       <c r="Q26" s="317" t="n"/>
       <c r="R26" s="317" t="n"/>
       <c r="S26" s="317" t="n"/>
@@ -16329,7 +16314,7 @@
       <c r="AL27" s="317" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1" s="141">
-      <c r="A28" s="588" t="inlineStr">
+      <c r="A28" s="589" t="inlineStr">
         <is>
           <t>Reset weights</t>
         </is>
@@ -16404,23 +16389,17 @@
       <c r="AL28" s="317" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1" s="141">
-      <c r="A29" s="450">
-        <f>IF($B$100="window","Middle Jump","Jump")</f>
-        <v/>
-      </c>
-      <c r="B29" s="450" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C29" s="450" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D29" s="450">
-        <f>IF($B$100="window","Vel Spread (fps)","Avg Vel (fps)")</f>
-        <v/>
+      <c r="A29" s="450" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B29" s="450" t="n"/>
+      <c r="C29" s="450" t="n"/>
+      <c r="D29" s="450" t="inlineStr">
+        <is>
+          <t>Avg Vel (fps)</t>
+        </is>
       </c>
       <c r="E29" s="450" t="inlineStr">
         <is>
@@ -16439,7 +16418,7 @@
       </c>
       <c r="H29" s="450" t="inlineStr">
         <is>
-          <t>Norm Spread</t>
+          <t>Norm Vel</t>
         </is>
       </c>
       <c r="I29" s="450" t="inlineStr">
@@ -16501,12 +16480,8 @@
       <c r="A30" s="451" t="n">
         <v>0.005</v>
       </c>
-      <c r="B30" s="451" t="n">
-        <v>2778</v>
-      </c>
-      <c r="C30" s="451" t="n">
-        <v>2784</v>
-      </c>
+      <c r="B30" s="451" t="n"/>
+      <c r="C30" s="451" t="n"/>
       <c r="D30" s="444" t="n">
         <v>2781</v>
       </c>
@@ -16534,14 +16509,10 @@
       <c r="L30" s="451" t="n">
         <v>0.652</v>
       </c>
-      <c r="M30" s="444">
-        <f>IF(D30="","",IFERROR(RANK(L30,$L$30:$L$37,1),""))</f>
-        <v/>
-      </c>
-      <c r="N30" s="452">
-        <f>IFERROR(IF(D30="","",TRIM(IF(D30=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E30=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F30=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G30=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
-        <v/>
-      </c>
+      <c r="M30" s="444" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="452" t="inlineStr"/>
       <c r="O30" s="233" t="n"/>
       <c r="P30" s="449" t="n"/>
       <c r="Q30" s="317" t="n"/>
@@ -16571,12 +16542,8 @@
       <c r="A31" s="453" t="n">
         <v>0.02</v>
       </c>
-      <c r="B31" s="453" t="n">
-        <v>2776</v>
-      </c>
-      <c r="C31" s="453" t="n">
-        <v>2784</v>
-      </c>
+      <c r="B31" s="453" t="n"/>
+      <c r="C31" s="453" t="n"/>
       <c r="D31" s="454" t="n">
         <v>2780</v>
       </c>
@@ -16604,14 +16571,10 @@
       <c r="L31" s="453" t="n">
         <v>0.338</v>
       </c>
-      <c r="M31" s="454">
-        <f>IF(D31="","",IFERROR(RANK(L31,$L$30:$L$37,1),""))</f>
-        <v/>
-      </c>
-      <c r="N31" s="457">
-        <f>IFERROR(IF(D31="","",TRIM(IF(D31=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E31=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F31=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G31=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
-        <v/>
-      </c>
+      <c r="M31" s="454" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="457" t="inlineStr"/>
       <c r="O31" s="236" t="n"/>
       <c r="P31" s="575" t="n"/>
       <c r="Q31" s="317" t="n"/>
@@ -16641,12 +16604,8 @@
       <c r="A32" s="451" t="n">
         <v>0.035</v>
       </c>
-      <c r="B32" s="451" t="n">
-        <v>2780</v>
-      </c>
-      <c r="C32" s="451" t="n">
-        <v>2782</v>
-      </c>
+      <c r="B32" s="451" t="n"/>
+      <c r="C32" s="451" t="n"/>
       <c r="D32" s="444" t="n">
         <v>2780.6</v>
       </c>
@@ -16674,13 +16633,13 @@
       <c r="L32" s="451" t="n">
         <v>0.001</v>
       </c>
-      <c r="M32" s="444">
-        <f>IF(D32="","",IFERROR(RANK(L32,$L$30:$L$37,1),""))</f>
-        <v/>
-      </c>
-      <c r="N32" s="452">
-        <f>IFERROR(IF(D32="","",TRIM(IF(D32=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E32=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F32=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G32=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
-        <v/>
+      <c r="M32" s="444" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="452" t="inlineStr">
+        <is>
+          <t>All metrics ✓</t>
+        </is>
       </c>
       <c r="O32" s="233" t="n"/>
       <c r="P32" s="449" t="n"/>
@@ -16711,12 +16670,8 @@
       <c r="A33" s="453" t="n">
         <v>0.05</v>
       </c>
-      <c r="B33" s="453" t="n">
-        <v>2774</v>
-      </c>
-      <c r="C33" s="453" t="n">
-        <v>2784</v>
-      </c>
+      <c r="B33" s="453" t="n"/>
+      <c r="C33" s="453" t="n"/>
       <c r="D33" s="454" t="n">
         <v>2780</v>
       </c>
@@ -16744,14 +16699,10 @@
       <c r="L33" s="453" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="M33" s="454">
-        <f>IF(D33="","",IFERROR(RANK(L33,$L$30:$L$37,1),""))</f>
-        <v/>
-      </c>
-      <c r="N33" s="457">
-        <f>IFERROR(IF(D33="","",TRIM(IF(D33=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E33=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F33=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G33=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
-        <v/>
-      </c>
+      <c r="M33" s="454" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="457" t="inlineStr"/>
       <c r="O33" s="236" t="n"/>
       <c r="P33" s="575" t="n"/>
       <c r="Q33" s="317" t="n"/>
@@ -16781,12 +16732,8 @@
       <c r="A34" s="451" t="n">
         <v>0.065</v>
       </c>
-      <c r="B34" s="451" t="n">
-        <v>2772</v>
-      </c>
-      <c r="C34" s="451" t="n">
-        <v>2786</v>
-      </c>
+      <c r="B34" s="451" t="n"/>
+      <c r="C34" s="451" t="n"/>
       <c r="D34" s="444" t="n">
         <v>2780</v>
       </c>
@@ -16814,14 +16761,10 @@
       <c r="L34" s="451" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="444">
-        <f>IF(D34="","",IFERROR(RANK(L34,$L$30:$L$37,1),""))</f>
-        <v/>
-      </c>
-      <c r="N34" s="452">
-        <f>IFERROR(IF(D34="","",TRIM(IF(D34=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E34=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F34=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G34=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
-        <v/>
-      </c>
+      <c r="M34" s="444" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="452" t="inlineStr"/>
       <c r="O34" s="233" t="n"/>
       <c r="P34" s="449" t="n"/>
       <c r="Q34" s="317" t="n"/>
@@ -16897,11 +16840,11 @@
         <v/>
       </c>
       <c r="M35" s="454">
-        <f>IF(D35="","",IFERROR(RANK(L35,$L$30:$L$37,1),""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="N35" s="457">
-        <f>IFERROR(IF(D35="","",TRIM(IF(D35=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E35=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F35=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G35=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="O35" s="236" t="n"/>
@@ -16979,11 +16922,11 @@
         <v/>
       </c>
       <c r="M36" s="444">
-        <f>IF(D36="","",IFERROR(RANK(L36,$L$30:$L$37,1),""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="N36" s="452">
-        <f>IFERROR(IF(D36="","",TRIM(IF(D36=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E36=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F36=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G36=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="O36" s="233" t="n"/>
@@ -17061,11 +17004,11 @@
         <v/>
       </c>
       <c r="M37" s="454">
-        <f>IF(D37="","",IFERROR(RANK(L37,$L$30:$L$37,1),""))</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="N37" s="457">
-        <f>IFERROR(IF(D37="","",TRIM(IF(D37=MIN($D$30:$D$37),"Vel ✓ ","")&amp;IF(E37=MIN($E$30:$E$37),"SD ✓ ","")&amp;IF(F37=MIN($F$30:$F$37),"MR ✓ ","")&amp;IF(G37=MIN($G$30:$G$37),"Vert ✓ ",""))),"")</f>
+        <f>NA()</f>
         <v/>
       </c>
       <c r="O37" s="236" t="n"/>
@@ -25343,23 +25286,71 @@
       <c r="Z4" s="317" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="141">
-      <c r="A5" s="359" t="n"/>
-      <c r="B5" s="359" t="n"/>
-      <c r="C5" s="359" t="n"/>
-      <c r="D5" s="359" t="n"/>
-      <c r="E5" s="358" t="n"/>
-      <c r="F5" s="371" t="n"/>
-      <c r="G5" s="358" t="n"/>
-      <c r="H5" s="372" t="n"/>
-      <c r="I5" s="358" t="n"/>
-      <c r="J5" s="358" t="n"/>
-      <c r="K5" s="373" t="n"/>
-      <c r="L5" s="373" t="n"/>
-      <c r="M5" s="374" t="n"/>
-      <c r="N5" s="375" t="n"/>
-      <c r="O5" s="376" t="n"/>
-      <c r="P5" s="376" t="n"/>
-      <c r="Q5" s="359" t="n"/>
+      <c r="A5" s="359" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="590" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C5" s="359" t="inlineStr">
+        <is>
+          <t>6.5 CM 140 ELD-M / H4350 42.4 / 0.035 jump</t>
+        </is>
+      </c>
+      <c r="D5" s="359" t="inlineStr">
+        <is>
+          <t>Tikka T3X CTR 6.5 CM</t>
+        </is>
+      </c>
+      <c r="E5" s="358" t="inlineStr">
+        <is>
+          <t>Hornady ELD-M</t>
+        </is>
+      </c>
+      <c r="F5" s="371" t="n">
+        <v>140</v>
+      </c>
+      <c r="G5" s="358" t="inlineStr">
+        <is>
+          <t>Hodgdon H4350</t>
+        </is>
+      </c>
+      <c r="H5" s="372" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I5" s="358" t="inlineStr">
+        <is>
+          <t>CCI BR-2</t>
+        </is>
+      </c>
+      <c r="J5" s="358" t="inlineStr">
+        <is>
+          <t>Hornady</t>
+        </is>
+      </c>
+      <c r="K5" s="373" t="n">
+        <v>2.224</v>
+      </c>
+      <c r="L5" s="373" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M5" s="374" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N5" s="375" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O5" s="376" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P5" s="376" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q5" s="359" t="inlineStr">
+        <is>
+          <t>Confirmed at 100 yd, 65°F, 1500 ft DA. 10-shot string.</t>
+        </is>
+      </c>
       <c r="R5" s="317" t="n"/>
       <c r="S5" s="317" t="n"/>
       <c r="T5" s="317" t="n"/>
@@ -25371,23 +25362,71 @@
       <c r="Z5" s="317" t="n"/>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="141">
-      <c r="A6" s="336" t="n"/>
-      <c r="B6" s="336" t="n"/>
-      <c r="C6" s="336" t="n"/>
-      <c r="D6" s="336" t="n"/>
-      <c r="E6" s="336" t="n"/>
-      <c r="F6" s="377" t="n"/>
-      <c r="G6" s="336" t="n"/>
-      <c r="H6" s="378" t="n"/>
-      <c r="I6" s="336" t="n"/>
-      <c r="J6" s="336" t="n"/>
-      <c r="K6" s="379" t="n"/>
-      <c r="L6" s="379" t="n"/>
-      <c r="M6" s="377" t="n"/>
-      <c r="N6" s="378" t="n"/>
-      <c r="O6" s="380" t="n"/>
-      <c r="P6" s="380" t="n"/>
-      <c r="Q6" s="336" t="n"/>
+      <c r="A6" s="336" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="591" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C6" s="336" t="inlineStr">
+        <is>
+          <t>6.5 CM 140 Berger Hybrid / H4350 42.1 / 0.020 jump</t>
+        </is>
+      </c>
+      <c r="D6" s="336" t="inlineStr">
+        <is>
+          <t>Tikka T3X CTR 6.5 CM</t>
+        </is>
+      </c>
+      <c r="E6" s="336" t="inlineStr">
+        <is>
+          <t>Berger Hybrid Target</t>
+        </is>
+      </c>
+      <c r="F6" s="377" t="n">
+        <v>140</v>
+      </c>
+      <c r="G6" s="336" t="inlineStr">
+        <is>
+          <t>Hodgdon H4350</t>
+        </is>
+      </c>
+      <c r="H6" s="378" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I6" s="336" t="inlineStr">
+        <is>
+          <t>Fed 210M</t>
+        </is>
+      </c>
+      <c r="J6" s="336" t="inlineStr">
+        <is>
+          <t>Lapua</t>
+        </is>
+      </c>
+      <c r="K6" s="379" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="L6" s="379" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M6" s="377" t="n">
+        <v>2745</v>
+      </c>
+      <c r="N6" s="378" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O6" s="380" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P6" s="380" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q6" s="336" t="inlineStr">
+        <is>
+          <t>Prior season — switched to ELD-M for lower SD.</t>
+        </is>
+      </c>
       <c r="R6" s="317" t="n"/>
       <c r="S6" s="317" t="n"/>
       <c r="T6" s="317" t="n"/>
@@ -25399,23 +25438,71 @@
       <c r="Z6" s="317" t="n"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="141">
-      <c r="A7" s="359" t="n"/>
-      <c r="B7" s="359" t="n"/>
-      <c r="C7" s="359" t="n"/>
-      <c r="D7" s="359" t="n"/>
-      <c r="E7" s="358" t="n"/>
-      <c r="F7" s="371" t="n"/>
-      <c r="G7" s="358" t="n"/>
-      <c r="H7" s="372" t="n"/>
-      <c r="I7" s="358" t="n"/>
-      <c r="J7" s="358" t="n"/>
-      <c r="K7" s="373" t="n"/>
-      <c r="L7" s="373" t="n"/>
-      <c r="M7" s="374" t="n"/>
-      <c r="N7" s="375" t="n"/>
-      <c r="O7" s="376" t="n"/>
-      <c r="P7" s="376" t="n"/>
-      <c r="Q7" s="359" t="n"/>
+      <c r="A7" s="359" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="590" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C7" s="359" t="inlineStr">
+        <is>
+          <t>6 ARC 108 ELD-M / CFE 223 26.5 / 0.040 jump</t>
+        </is>
+      </c>
+      <c r="D7" s="359" t="inlineStr">
+        <is>
+          <t>Bergara B14 HMR 6 ARC</t>
+        </is>
+      </c>
+      <c r="E7" s="358" t="inlineStr">
+        <is>
+          <t>Hornady ELD-M</t>
+        </is>
+      </c>
+      <c r="F7" s="371" t="n">
+        <v>108</v>
+      </c>
+      <c r="G7" s="358" t="inlineStr">
+        <is>
+          <t>Hodgdon CFE 223</t>
+        </is>
+      </c>
+      <c r="H7" s="372" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I7" s="358" t="inlineStr">
+        <is>
+          <t>CCI 450</t>
+        </is>
+      </c>
+      <c r="J7" s="358" t="inlineStr">
+        <is>
+          <t>Hornady</t>
+        </is>
+      </c>
+      <c r="K7" s="373" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L7" s="373" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M7" s="374" t="n">
+        <v>2680</v>
+      </c>
+      <c r="N7" s="375" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O7" s="376" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P7" s="376" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Q7" s="359" t="inlineStr">
+        <is>
+          <t>Truck gun build. Good cold-bore consistency.</t>
+        </is>
+      </c>
       <c r="R7" s="317" t="n"/>
       <c r="S7" s="317" t="n"/>
       <c r="T7" s="317" t="n"/>
@@ -25860,21 +25947,21 @@
       <c r="K1" s="309" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="141">
-      <c r="A2" s="201" t="inlineStr">
+      <c r="A2" s="586" t="inlineStr">
         <is>
           <t>→  Print Pocket Range Card  ←</t>
         </is>
       </c>
-      <c r="B2" s="586" t="n"/>
-      <c r="C2" s="586" t="n"/>
-      <c r="D2" s="586" t="n"/>
-      <c r="E2" s="586" t="n"/>
-      <c r="F2" s="586" t="n"/>
-      <c r="G2" s="586" t="n"/>
-      <c r="H2" s="586" t="n"/>
-      <c r="I2" s="586" t="n"/>
-      <c r="J2" s="586" t="n"/>
-      <c r="K2" s="587" t="n"/>
+      <c r="B2" s="587" t="n"/>
+      <c r="C2" s="587" t="n"/>
+      <c r="D2" s="587" t="n"/>
+      <c r="E2" s="587" t="n"/>
+      <c r="F2" s="587" t="n"/>
+      <c r="G2" s="587" t="n"/>
+      <c r="H2" s="587" t="n"/>
+      <c r="I2" s="587" t="n"/>
+      <c r="J2" s="587" t="n"/>
+      <c r="K2" s="588" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1" s="141">
       <c r="A3" s="309" t="n"/>
@@ -25895,16 +25982,16 @@
           <t>Enter your DOPE values in MILS or MOA. Click counts auto-calculate based on your scope's click value (set on the Load Log tab — Click: dropdown).</t>
         </is>
       </c>
-      <c r="B4" s="586" t="n"/>
-      <c r="C4" s="586" t="n"/>
-      <c r="D4" s="586" t="n"/>
-      <c r="E4" s="586" t="n"/>
-      <c r="F4" s="586" t="n"/>
-      <c r="G4" s="586" t="n"/>
-      <c r="H4" s="586" t="n"/>
-      <c r="I4" s="586" t="n"/>
-      <c r="J4" s="586" t="n"/>
-      <c r="K4" s="587" t="n"/>
+      <c r="B4" s="587" t="n"/>
+      <c r="C4" s="587" t="n"/>
+      <c r="D4" s="587" t="n"/>
+      <c r="E4" s="587" t="n"/>
+      <c r="F4" s="587" t="n"/>
+      <c r="G4" s="587" t="n"/>
+      <c r="H4" s="587" t="n"/>
+      <c r="I4" s="587" t="n"/>
+      <c r="J4" s="587" t="n"/>
+      <c r="K4" s="588" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1" s="141">
       <c r="A5" s="381" t="inlineStr">
@@ -25912,9 +25999,10 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B5" s="270">
-        <f>IF(IFERROR('Load Library'!D5,"")="","",'Load Library'!D5)</f>
-        <v/>
+      <c r="B5" s="270" t="inlineStr">
+        <is>
+          <t>Tikka T3X CTR 6.5 CM</t>
+        </is>
       </c>
       <c r="C5" s="382" t="n"/>
       <c r="D5" s="381" t="inlineStr">
@@ -25922,9 +26010,10 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E5" s="270">
-        <f>IF(IFERROR('Load Library'!E5,"")="","",'Load Library'!E5&amp;" ("&amp;'Load Library'!F5&amp;"gr)")</f>
-        <v/>
+      <c r="E5" s="270" t="inlineStr">
+        <is>
+          <t>Hornady 140gr ELD-M</t>
+        </is>
       </c>
       <c r="F5" s="382" t="n"/>
       <c r="G5" s="381" t="inlineStr">
@@ -25932,9 +26021,8 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H5" s="270">
-        <f>IF(IFERROR('Load Library'!H5,"")="","",'Load Library'!H5&amp;" gr "&amp;'Load Library'!G5)</f>
-        <v/>
+      <c r="H5" s="270" t="n">
+        <v>42.4</v>
       </c>
       <c r="I5" s="382" t="n"/>
       <c r="J5" s="381" t="inlineStr">
@@ -25942,9 +26030,8 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K5" s="270">
-        <f>IF(IFERROR('Load Library'!M5,"")="","",'Load Library'!M5&amp;" fps")</f>
-        <v/>
+      <c r="K5" s="270" t="n">
+        <v>2780</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="141">
@@ -25953,7 +26040,11 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B6" s="363" t="n"/>
+      <c r="B6" s="363" t="inlineStr">
+        <is>
+          <t>Leupold Mark 5HD 5-25x56</t>
+        </is>
+      </c>
       <c r="C6" s="384" t="n"/>
       <c r="D6" s="383" t="inlineStr">
         <is>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -1021,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="592">
+  <cellXfs count="594">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2869,8 +2869,16 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="181" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -25069,15 +25077,19 @@
     <col width="12" customWidth="1" style="140" min="2" max="2"/>
     <col width="36" customWidth="1" style="140" min="3" max="3"/>
     <col width="22" customWidth="1" style="140" min="4" max="5"/>
+    <col width="18" customWidth="1" style="141" min="5" max="5"/>
     <col width="11" customWidth="1" style="140" min="6" max="6"/>
-    <col width="9" customWidth="1" style="140" min="7" max="7"/>
+    <col width="16" customWidth="1" style="140" min="7" max="7"/>
     <col width="11" customWidth="1" style="140" min="8" max="8"/>
     <col width="12" customWidth="1" style="140" min="9" max="10"/>
+    <col width="12" customWidth="1" style="141" min="10" max="10"/>
     <col width="22" customWidth="1" style="140" min="11" max="11"/>
     <col width="11" customWidth="1" style="140" min="12" max="13"/>
+    <col width="12" customWidth="1" style="141" min="13" max="13"/>
     <col width="12" customWidth="1" style="140" min="14" max="14"/>
     <col width="9" customWidth="1" style="140" min="15" max="16"/>
-    <col width="12" customWidth="1" style="140" min="17" max="17"/>
+    <col width="10" customWidth="1" style="141" min="16" max="16"/>
+    <col width="28" customWidth="1" style="140" min="17" max="17"/>
     <col width="8.43" customWidth="1" style="140" min="18" max="29"/>
   </cols>
   <sheetData>
@@ -25285,7 +25297,7 @@
       <c r="Y4" s="317" t="n"/>
       <c r="Z4" s="317" t="n"/>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="141">
+    <row r="5" ht="32" customHeight="1" s="141">
       <c r="A5" s="359" t="n">
         <v>1</v>
       </c>
@@ -25346,7 +25358,7 @@
       <c r="P5" s="376" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q5" s="359" t="inlineStr">
+      <c r="Q5" s="591" t="inlineStr">
         <is>
           <t>Confirmed at 100 yd, 65°F, 1500 ft DA. 10-shot string.</t>
         </is>
@@ -25361,11 +25373,11 @@
       <c r="Y5" s="317" t="n"/>
       <c r="Z5" s="317" t="n"/>
     </row>
-    <row r="6" ht="21.75" customHeight="1" s="141">
+    <row r="6" ht="32" customHeight="1" s="141">
       <c r="A6" s="336" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="591" t="n">
+      <c r="B6" s="592" t="n">
         <v>45971</v>
       </c>
       <c r="C6" s="336" t="inlineStr">
@@ -25422,7 +25434,7 @@
       <c r="P6" s="380" t="n">
         <v>0.24</v>
       </c>
-      <c r="Q6" s="336" t="inlineStr">
+      <c r="Q6" s="593" t="inlineStr">
         <is>
           <t>Prior season — switched to ELD-M for lower SD.</t>
         </is>
@@ -25437,7 +25449,7 @@
       <c r="Y6" s="317" t="n"/>
       <c r="Z6" s="317" t="n"/>
     </row>
-    <row r="7" ht="21.75" customHeight="1" s="141">
+    <row r="7" ht="32" customHeight="1" s="141">
       <c r="A7" s="359" t="n">
         <v>3</v>
       </c>
@@ -25498,7 +25510,7 @@
       <c r="P7" s="376" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q7" s="359" t="inlineStr">
+      <c r="Q7" s="591" t="inlineStr">
         <is>
           <t>Truck gun build. Good cold-bore consistency.</t>
         </is>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticX Import" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Library" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballistics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GarminSessions" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticXGroups" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Card" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GarminSessions" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticXGroups" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'After Range Day'!$A$1:$H$17</definedName>
@@ -52,7 +53,7 @@
     <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="66">
+  <fonts count="72">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -464,6 +465,35 @@
       <b val="1"/>
       <color rgb="FFFFFF00"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF888888"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="42">
     <fill>
@@ -706,7 +736,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1010,6 +1040,20 @@
         <color rgb="FFB0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1021,7 +1065,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="594">
+  <cellXfs count="600">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2880,6 +2924,24 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="26" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8498,6 +8560,877 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="140" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" s="140" t="inlineStr">
+        <is>
+          <t>ChargeOrJump</t>
+        </is>
+      </c>
+      <c r="C1" s="140" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="D1" s="140" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="140" t="inlineStr">
+        <is>
+          <t>Shot1</t>
+        </is>
+      </c>
+      <c r="F1" s="140" t="inlineStr">
+        <is>
+          <t>Shot2</t>
+        </is>
+      </c>
+      <c r="G1" s="140" t="inlineStr">
+        <is>
+          <t>Shot3</t>
+        </is>
+      </c>
+      <c r="H1" s="140" t="inlineStr">
+        <is>
+          <t>Shot4</t>
+        </is>
+      </c>
+      <c r="I1" s="140" t="inlineStr">
+        <is>
+          <t>Shot5</t>
+        </is>
+      </c>
+      <c r="J1" s="140" t="inlineStr">
+        <is>
+          <t>Shot6</t>
+        </is>
+      </c>
+      <c r="K1" s="140" t="inlineStr">
+        <is>
+          <t>Shot7</t>
+        </is>
+      </c>
+      <c r="L1" s="140" t="inlineStr">
+        <is>
+          <t>Shot8</t>
+        </is>
+      </c>
+      <c r="M1" s="140" t="inlineStr">
+        <is>
+          <t>Shot9</t>
+        </is>
+      </c>
+      <c r="N1" s="140" t="inlineStr">
+        <is>
+          <t>Shot10</t>
+        </is>
+      </c>
+      <c r="O1" s="140" t="inlineStr">
+        <is>
+          <t>AvgVel</t>
+        </is>
+      </c>
+      <c r="P1" s="140" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="Q1" s="140" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="R1" s="140" t="inlineStr">
+        <is>
+          <t>BulletWt</t>
+        </is>
+      </c>
+      <c r="S1" s="140" t="inlineStr">
+        <is>
+          <t>AvgKE</t>
+        </is>
+      </c>
+      <c r="T1" s="140" t="inlineStr">
+        <is>
+          <t>SessionTitle</t>
+        </is>
+      </c>
+      <c r="U1" s="140" t="inlineStr">
+        <is>
+          <t>SessionNote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2718</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2705</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2715</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2712</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2722</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2708</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2716</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2724</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2715</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R2" t="n">
+        <v>140</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2293</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 41.5gr</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2732</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2748</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2725</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2740</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2734</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2742</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2728</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2736</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2747</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2737</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>140</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 41.8gr</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2762</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2768</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2758</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2765</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2752</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2770</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>140</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2369</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.1gr</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2778</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2782</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2776</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2779</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2778</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2781</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>140</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.4gr (WINNER)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2798</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2805</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2795</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2800</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2802</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2806</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2796</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2802</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2803</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>17</v>
+      </c>
+      <c r="R6" t="n">
+        <v>140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2443</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.7gr</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2784</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2781</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>140</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2404</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Seating depth +0.005 jump</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2782</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2776</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2784</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2782</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>140</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Seating depth +0.020 jump</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2781</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2782</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2781</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2780.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>140</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2403</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Seating depth +0.035 jump (WINNER)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2784</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2776</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2782</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2784</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2782</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2774</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Seating depth +0.050 jump</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2786</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2776</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2782</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2772</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2786</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2776</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2784</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>140</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Seating depth +0.065 jump</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -28415,867 +29348,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="141" min="1" max="1"/>
+    <col width="8" customWidth="1" style="141" min="2" max="2"/>
+    <col width="8" customWidth="1" style="141" min="3" max="3"/>
+    <col width="8" customWidth="1" style="141" min="4" max="4"/>
+    <col width="8" customWidth="1" style="141" min="5" max="5"/>
+    <col width="8" customWidth="1" style="141" min="6" max="6"/>
+    <col width="8" customWidth="1" style="141" min="7" max="7"/>
+    <col width="8" customWidth="1" style="141" min="8" max="8"/>
+    <col width="8" customWidth="1" style="141" min="9" max="9"/>
+    <col width="8" customWidth="1" style="141" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="140" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="B1" s="140" t="inlineStr">
-        <is>
-          <t>ChargeOrJump</t>
-        </is>
-      </c>
-      <c r="C1" s="140" t="inlineStr">
-        <is>
-          <t>Powder</t>
-        </is>
-      </c>
-      <c r="D1" s="140" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" s="140" t="inlineStr">
-        <is>
-          <t>Shot1</t>
-        </is>
-      </c>
-      <c r="F1" s="140" t="inlineStr">
-        <is>
-          <t>Shot2</t>
-        </is>
-      </c>
-      <c r="G1" s="140" t="inlineStr">
-        <is>
-          <t>Shot3</t>
-        </is>
-      </c>
-      <c r="H1" s="140" t="inlineStr">
-        <is>
-          <t>Shot4</t>
-        </is>
-      </c>
-      <c r="I1" s="140" t="inlineStr">
-        <is>
-          <t>Shot5</t>
-        </is>
-      </c>
-      <c r="J1" s="140" t="inlineStr">
-        <is>
-          <t>Shot6</t>
-        </is>
-      </c>
-      <c r="K1" s="140" t="inlineStr">
-        <is>
-          <t>Shot7</t>
-        </is>
-      </c>
-      <c r="L1" s="140" t="inlineStr">
-        <is>
-          <t>Shot8</t>
-        </is>
-      </c>
-      <c r="M1" s="140" t="inlineStr">
-        <is>
-          <t>Shot9</t>
-        </is>
-      </c>
-      <c r="N1" s="140" t="inlineStr">
-        <is>
-          <t>Shot10</t>
-        </is>
-      </c>
-      <c r="O1" s="140" t="inlineStr">
-        <is>
-          <t>AvgVel</t>
-        </is>
-      </c>
-      <c r="P1" s="140" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="Q1" s="140" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="R1" s="140" t="inlineStr">
-        <is>
-          <t>BulletWt</t>
-        </is>
-      </c>
-      <c r="S1" s="140" t="inlineStr">
-        <is>
-          <t>AvgKE</t>
-        </is>
-      </c>
-      <c r="T1" s="140" t="inlineStr">
-        <is>
-          <t>SessionTitle</t>
-        </is>
-      </c>
-      <c r="U1" s="140" t="inlineStr">
-        <is>
-          <t>SessionNote</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2710</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2718</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2705</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2715</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2712</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2722</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2708</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2716</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2724</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2715</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19</v>
-      </c>
-      <c r="R2" t="n">
-        <v>140</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2293</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 41.5gr</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2732</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2748</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2725</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2740</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2734</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2742</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2728</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2736</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2747</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2737</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>140</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 41.8gr</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2755</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2762</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2750</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2768</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2758</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2765</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2752</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2770</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q4" t="n">
+    <row r="1" ht="26" customHeight="1" s="141">
+      <c r="A1" s="594" t="inlineStr">
+        <is>
+          <t>POCKET RANGE CARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="141">
+      <c r="A2" s="595" t="inlineStr">
+        <is>
+          <t>Tikka T3X CTR 6.5 CM  •  Hornady 140gr ELD-M  •  42.4gr  •  2780 fps</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="141">
+      <c r="A3" s="596" t="inlineStr">
+        <is>
+          <t>Scope: Leupold Mark 5HD 5-25x56   |   Click: 0.1 Mil   |   Zero: 100 yd   |   Sight Ht: 1.75"   |   Twist: 1:8 RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="141">
+      <c r="A5" s="597" t="inlineStr">
+        <is>
+          <t>Range
+(yd)</t>
+        </is>
+      </c>
+      <c r="B5" s="597" t="inlineStr">
+        <is>
+          <t>Mils
+Elev</t>
+        </is>
+      </c>
+      <c r="C5" s="597" t="inlineStr">
+        <is>
+          <t>Mil
+Clicks</t>
+        </is>
+      </c>
+      <c r="D5" s="597" t="inlineStr">
+        <is>
+          <t>MOA
+Elev</t>
+        </is>
+      </c>
+      <c r="E5" s="597" t="inlineStr">
+        <is>
+          <t>MOA
+Clicks</t>
+        </is>
+      </c>
+      <c r="F5" s="597" t="inlineStr">
+        <is>
+          <t>Wind
+Mils/10</t>
+        </is>
+      </c>
+      <c r="G5" s="597" t="inlineStr">
+        <is>
+          <t>Wind
+Mil Clk</t>
+        </is>
+      </c>
+      <c r="H5" s="597" t="inlineStr">
+        <is>
+          <t>Wind
+MOA/10</t>
+        </is>
+      </c>
+      <c r="I5" s="597" t="inlineStr">
+        <is>
+          <t>Wind
+MOA Clk</t>
+        </is>
+      </c>
+      <c r="J5" s="597" t="inlineStr">
+        <is>
+          <t>TOF
+(sec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="141">
+      <c r="A6" s="598" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="598" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="141">
+      <c r="A7" s="598" t="n">
+        <v>200</v>
+      </c>
+      <c r="B7" s="598" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="598" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="598" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="598" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="598" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="598" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="598" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="598" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="598" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="141">
+      <c r="A8" s="598" t="n">
+        <v>300</v>
+      </c>
+      <c r="B8" s="598" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="598" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="598" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="598" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="598" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="598" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="598" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="598" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="598" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="141">
+      <c r="A9" s="598" t="n">
+        <v>400</v>
+      </c>
+      <c r="B9" s="598" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="598" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="598" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E9" s="598" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="598" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G9" s="598" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="598" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I9" s="598" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="598" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="141">
+      <c r="A10" s="598" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" s="598" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="598" t="n">
         <v>20</v>
       </c>
-      <c r="R4" t="n">
-        <v>140</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2369</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.1gr</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2778</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2782</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2776</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2779</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2778</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2781</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>140</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.4gr (WINNER)</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2798</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2805</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2795</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2812</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2800</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2802</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2806</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2796</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2802</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2810</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2803</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>17</v>
-      </c>
-      <c r="R6" t="n">
-        <v>140</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2443</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.7gr</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2778</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2784</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2781</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="D10" s="598" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E10" s="598" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="598" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="598" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="598" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I10" s="598" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="598" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="141">
+      <c r="A11" s="598" t="n">
+        <v>600</v>
+      </c>
+      <c r="B11" s="598" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C11" s="598" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" s="598" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E11" s="598" t="n">
+        <v>38</v>
+      </c>
+      <c r="F11" s="598" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="598" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" s="598" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I11" s="598" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" s="598" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="141">
+      <c r="A12" s="598" t="n">
+        <v>700</v>
+      </c>
+      <c r="B12" s="598" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C12" s="598" t="n">
+        <v>37</v>
+      </c>
+      <c r="D12" s="598" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E12" s="598" t="n">
+        <v>51</v>
+      </c>
+      <c r="F12" s="598" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="598" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="598" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I12" s="598" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" s="598" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="141">
+      <c r="A13" s="598" t="n">
+        <v>800</v>
+      </c>
+      <c r="B13" s="598" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C13" s="598" t="n">
+        <v>48</v>
+      </c>
+      <c r="D13" s="598" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E13" s="598" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" s="598" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G13" s="598" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" s="598" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I13" s="598" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="598" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="141">
+      <c r="A14" s="598" t="n">
+        <v>900</v>
+      </c>
+      <c r="B14" s="598" t="n">
         <v>6</v>
       </c>
-      <c r="R7" t="n">
-        <v>140</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2404</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Seating depth +0.005 jump</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2778</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2782</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2776</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2784</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2782</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="C14" s="598" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" s="598" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E14" s="598" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" s="598" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G14" s="598" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" s="598" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I14" s="598" t="n">
+        <v>29</v>
+      </c>
+      <c r="J14" s="598" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="141">
+      <c r="A15" s="598" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B15" s="598" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C15" s="598" t="n">
+        <v>73</v>
+      </c>
+      <c r="D15" s="598" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="598" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="598" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>140</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Seating depth +0.020 jump</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2781</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2782</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2781</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2780.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>140</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2403</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Seating depth +0.035 jump (WINNER)</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2784</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2776</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2782</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2784</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2782</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2774</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" t="n">
-        <v>140</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Seating depth +0.050 jump</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2786</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2774</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2776</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2782</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2786</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2776</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2784</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>140</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Seating depth +0.065 jump</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
+      <c r="G15" s="598" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" s="598" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I15" s="598" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" s="598" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="141">
+      <c r="A17" s="599" t="inlineStr">
+        <is>
+          <t>Sample card based on Ballistics tab DOPE values. Click 'Print Pocket Range Card' on the Ballistics tab to generate a printable 4x6 version.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="4">
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1"/>
 </worksheet>
 </file>
--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticX Import" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Library" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballistics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Card" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Range Card" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GarminSessions" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticXGroups" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
@@ -53,7 +53,7 @@
     <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="71">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -488,11 +488,6 @@
     <font>
       <color rgb="FF000000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF888888"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="42">
@@ -2940,8 +2935,8 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -26006,23 +26001,23 @@
   <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="5" customWidth="1" style="140" min="1" max="1"/>
-    <col width="12" customWidth="1" style="140" min="2" max="2"/>
-    <col width="36" customWidth="1" style="140" min="3" max="3"/>
-    <col width="22" customWidth="1" style="140" min="4" max="5"/>
-    <col width="18" customWidth="1" style="141" min="5" max="5"/>
-    <col width="11" customWidth="1" style="140" min="6" max="6"/>
-    <col width="16" customWidth="1" style="140" min="7" max="7"/>
-    <col width="11" customWidth="1" style="140" min="8" max="8"/>
-    <col width="12" customWidth="1" style="140" min="9" max="10"/>
-    <col width="12" customWidth="1" style="141" min="10" max="10"/>
-    <col width="22" customWidth="1" style="140" min="11" max="11"/>
-    <col width="11" customWidth="1" style="140" min="12" max="13"/>
-    <col width="12" customWidth="1" style="141" min="13" max="13"/>
-    <col width="12" customWidth="1" style="140" min="14" max="14"/>
-    <col width="9" customWidth="1" style="140" min="15" max="16"/>
-    <col width="10" customWidth="1" style="141" min="16" max="16"/>
-    <col width="28" customWidth="1" style="140" min="17" max="17"/>
+    <col width="4" customWidth="1" style="140" min="1" max="1"/>
+    <col width="11" customWidth="1" style="140" min="2" max="2"/>
+    <col width="25" customWidth="1" style="140" min="3" max="3"/>
+    <col width="18" customWidth="1" style="140" min="4" max="5"/>
+    <col width="15" customWidth="1" style="141" min="5" max="5"/>
+    <col width="8" customWidth="1" style="140" min="6" max="6"/>
+    <col width="14" customWidth="1" style="140" min="7" max="7"/>
+    <col width="8" customWidth="1" style="140" min="8" max="8"/>
+    <col width="10" customWidth="1" style="140" min="9" max="10"/>
+    <col width="10" customWidth="1" style="141" min="10" max="10"/>
+    <col width="8" customWidth="1" style="140" min="11" max="11"/>
+    <col width="8" customWidth="1" style="140" min="12" max="13"/>
+    <col width="9" customWidth="1" style="141" min="13" max="13"/>
+    <col width="7" customWidth="1" style="140" min="14" max="14"/>
+    <col width="8" customWidth="1" style="140" min="15" max="16"/>
+    <col width="8" customWidth="1" style="141" min="16" max="16"/>
+    <col width="22" customWidth="1" style="140" min="17" max="17"/>
     <col width="8.43" customWidth="1" style="140" min="18" max="29"/>
   </cols>
   <sheetData>
@@ -26841,7 +26836,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Italic"&amp;8 &amp;"Calibri,Italic"&amp;8 &amp;F&amp;C&amp;"Calibri,Bold"&amp;10 &amp;"Calibri,Bold"&amp;10 &amp;A&amp;R&amp;"Calibri,Italic"&amp;8 &amp;"Calibri,Italic"&amp;8 Page &amp;P of &amp;N</oddHeader>
     <oddFooter/>
@@ -29766,10 +29761,10 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="141">
+    <row r="17" ht="36" customHeight="1" s="141">
       <c r="A17" s="599" t="inlineStr">
         <is>
-          <t>Sample card based on Ballistics tab DOPE values. Click 'Print Pocket Range Card' on the Ballistics tab to generate a printable 4x6 version.</t>
+          <t>Click "Print Pocket Range Card" on the Ballistics tab to print this card as a 4×6 page.</t>
         </is>
       </c>
     </row>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -53,7 +53,7 @@
     <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -466,31 +466,41 @@
       <color rgb="FFFFFF00"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="22"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
       <color rgb="FF1F4E78"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <color rgb="FF555555"/>
       <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="FF555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="FF888888"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="44">
     <fill>
       <patternFill/>
     </fill>
@@ -730,8 +740,20 @@
         <bgColor rgb="FFFFE082"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor rgb="FFF7F9FC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1036,17 +1058,22 @@
       </bottom>
     </border>
     <border>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF888888"/>
+        <color rgb="FFBBBBBB"/>
       </left>
       <right style="thin">
-        <color rgb="FF888888"/>
+        <color rgb="FFBBBBBB"/>
       </right>
       <top style="thin">
-        <color rgb="FF888888"/>
+        <color rgb="FFBBBBBB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF888888"/>
+        <color rgb="FFBBBBBB"/>
       </bottom>
     </border>
   </borders>
@@ -1060,7 +1087,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="600">
+  <cellXfs count="603">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2920,22 +2947,27 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="42" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="68" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="26" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="21" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="42" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="70" fillId="43" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -29346,423 +29378,456 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="141" min="1" max="1"/>
+    <col width="11" customWidth="1" style="141" min="1" max="1"/>
     <col width="8" customWidth="1" style="141" min="2" max="2"/>
     <col width="8" customWidth="1" style="141" min="3" max="3"/>
     <col width="8" customWidth="1" style="141" min="4" max="4"/>
     <col width="8" customWidth="1" style="141" min="5" max="5"/>
-    <col width="8" customWidth="1" style="141" min="6" max="6"/>
+    <col width="9" customWidth="1" style="141" min="6" max="6"/>
     <col width="8" customWidth="1" style="141" min="7" max="7"/>
-    <col width="8" customWidth="1" style="141" min="8" max="8"/>
+    <col width="9" customWidth="1" style="141" min="8" max="8"/>
     <col width="8" customWidth="1" style="141" min="9" max="9"/>
-    <col width="8" customWidth="1" style="141" min="10" max="10"/>
+    <col width="9" customWidth="1" style="141" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="141">
+    <row r="1" ht="36" customHeight="1" s="141">
       <c r="A1" s="594" t="inlineStr">
         <is>
           <t>POCKET RANGE CARD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" s="141">
-      <c r="A2" s="595" t="inlineStr">
+      <c r="B1" s="595" t="n"/>
+      <c r="C1" s="595" t="n"/>
+      <c r="D1" s="595" t="n"/>
+      <c r="E1" s="595" t="n"/>
+      <c r="F1" s="595" t="n"/>
+      <c r="G1" s="595" t="n"/>
+      <c r="H1" s="595" t="n"/>
+      <c r="I1" s="595" t="n"/>
+      <c r="J1" s="595" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="141">
+      <c r="A2" s="596" t="inlineStr">
         <is>
           <t>Tikka T3X CTR 6.5 CM  •  Hornady 140gr ELD-M  •  42.4gr  •  2780 fps</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="141">
-      <c r="A3" s="596" t="inlineStr">
-        <is>
-          <t>Scope: Leupold Mark 5HD 5-25x56   |   Click: 0.1 Mil   |   Zero: 100 yd   |   Sight Ht: 1.75"   |   Twist: 1:8 RH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="141">
-      <c r="A5" s="597" t="inlineStr">
+    <row r="3" ht="22" customHeight="1" s="141">
+      <c r="A3" s="597" t="inlineStr">
+        <is>
+          <t>Scope: Leupold Mark 5HD 5-25x56   ·   Click: 0.1 Mil   ·   Zero: 100 yd   ·   Sight Ht: 1.75"   ·   Twist: 1:8 RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1" s="141">
+      <c r="A4" s="598" t="n"/>
+      <c r="B4" s="598" t="n"/>
+      <c r="C4" s="598" t="n"/>
+      <c r="D4" s="598" t="n"/>
+      <c r="E4" s="598" t="n"/>
+      <c r="F4" s="598" t="n"/>
+      <c r="G4" s="598" t="n"/>
+      <c r="H4" s="598" t="n"/>
+      <c r="I4" s="598" t="n"/>
+      <c r="J4" s="598" t="n"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" s="141">
+      <c r="A5" s="599" t="inlineStr">
         <is>
           <t>Range
 (yd)</t>
         </is>
       </c>
-      <c r="B5" s="597" t="inlineStr">
+      <c r="B5" s="599" t="inlineStr">
         <is>
           <t>Mils
 Elev</t>
         </is>
       </c>
-      <c r="C5" s="597" t="inlineStr">
+      <c r="C5" s="599" t="inlineStr">
         <is>
           <t>Mil
 Clicks</t>
         </is>
       </c>
-      <c r="D5" s="597" t="inlineStr">
+      <c r="D5" s="599" t="inlineStr">
         <is>
           <t>MOA
 Elev</t>
         </is>
       </c>
-      <c r="E5" s="597" t="inlineStr">
+      <c r="E5" s="599" t="inlineStr">
         <is>
           <t>MOA
 Clicks</t>
         </is>
       </c>
-      <c r="F5" s="597" t="inlineStr">
+      <c r="F5" s="599" t="inlineStr">
         <is>
           <t>Wind
 Mils/10</t>
         </is>
       </c>
-      <c r="G5" s="597" t="inlineStr">
+      <c r="G5" s="599" t="inlineStr">
         <is>
           <t>Wind
 Mil Clk</t>
         </is>
       </c>
-      <c r="H5" s="597" t="inlineStr">
+      <c r="H5" s="599" t="inlineStr">
         <is>
           <t>Wind
 MOA/10</t>
         </is>
       </c>
-      <c r="I5" s="597" t="inlineStr">
+      <c r="I5" s="599" t="inlineStr">
         <is>
           <t>Wind
 MOA Clk</t>
         </is>
       </c>
-      <c r="J5" s="597" t="inlineStr">
+      <c r="J5" s="599" t="inlineStr">
         <is>
           <t>TOF
 (sec)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="141">
-      <c r="A6" s="598" t="n">
+    <row r="6" ht="20" customHeight="1" s="141">
+      <c r="A6" s="600" t="n">
         <v>100</v>
       </c>
-      <c r="B6" s="598" t="n">
+      <c r="B6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="598" t="n">
+      <c r="C6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="598" t="n">
+      <c r="D6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="598" t="n">
+      <c r="E6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="598" t="n">
+      <c r="F6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="598" t="n">
+      <c r="G6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="598" t="n">
+      <c r="H6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="598" t="n">
+      <c r="I6" s="600" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="598" t="n">
+      <c r="J6" s="600" t="n">
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="141">
-      <c r="A7" s="598" t="n">
+    <row r="7" ht="20" customHeight="1" s="141">
+      <c r="A7" s="601" t="n">
         <v>200</v>
       </c>
-      <c r="B7" s="598" t="n">
+      <c r="B7" s="601" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="598" t="n">
+      <c r="C7" s="601" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="598" t="n">
+      <c r="D7" s="601" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="598" t="n">
+      <c r="E7" s="601" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="598" t="n">
+      <c r="F7" s="601" t="n">
         <v>0.3</v>
       </c>
-      <c r="G7" s="598" t="n">
+      <c r="G7" s="601" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="598" t="n">
+      <c r="H7" s="601" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="598" t="n">
+      <c r="I7" s="601" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="598" t="n">
+      <c r="J7" s="601" t="n">
         <v>0.23</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="141">
-      <c r="A8" s="598" t="n">
+    <row r="8" ht="20" customHeight="1" s="141">
+      <c r="A8" s="600" t="n">
         <v>300</v>
       </c>
-      <c r="B8" s="598" t="n">
+      <c r="B8" s="600" t="n">
         <v>0.6</v>
       </c>
-      <c r="C8" s="598" t="n">
+      <c r="C8" s="600" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="598" t="n">
+      <c r="D8" s="600" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="598" t="n">
+      <c r="E8" s="600" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="598" t="n">
+      <c r="F8" s="600" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="598" t="n">
+      <c r="G8" s="600" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="598" t="n">
+      <c r="H8" s="600" t="n">
         <v>1.7</v>
       </c>
-      <c r="I8" s="598" t="n">
+      <c r="I8" s="600" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="598" t="n">
+      <c r="J8" s="600" t="n">
         <v>0.36</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" s="141">
-      <c r="A9" s="598" t="n">
+    <row r="9" ht="20" customHeight="1" s="141">
+      <c r="A9" s="601" t="n">
         <v>400</v>
       </c>
-      <c r="B9" s="598" t="n">
+      <c r="B9" s="601" t="n">
         <v>1.2</v>
       </c>
-      <c r="C9" s="598" t="n">
+      <c r="C9" s="601" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="598" t="n">
+      <c r="D9" s="601" t="n">
         <v>4.1</v>
       </c>
-      <c r="E9" s="598" t="n">
+      <c r="E9" s="601" t="n">
         <v>16</v>
       </c>
-      <c r="F9" s="598" t="n">
+      <c r="F9" s="601" t="n">
         <v>0.7</v>
       </c>
-      <c r="G9" s="598" t="n">
+      <c r="G9" s="601" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="598" t="n">
+      <c r="H9" s="601" t="n">
         <v>2.4</v>
       </c>
-      <c r="I9" s="598" t="n">
+      <c r="I9" s="601" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="598" t="n">
+      <c r="J9" s="601" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="141">
-      <c r="A10" s="598" t="n">
+    <row r="10" ht="20" customHeight="1" s="141">
+      <c r="A10" s="600" t="n">
         <v>500</v>
       </c>
-      <c r="B10" s="598" t="n">
+      <c r="B10" s="600" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="598" t="n">
+      <c r="C10" s="600" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="598" t="n">
+      <c r="D10" s="600" t="n">
         <v>6.9</v>
       </c>
-      <c r="E10" s="598" t="n">
+      <c r="E10" s="600" t="n">
         <v>28</v>
       </c>
-      <c r="F10" s="598" t="n">
+      <c r="F10" s="600" t="n">
         <v>0.9</v>
       </c>
-      <c r="G10" s="598" t="n">
+      <c r="G10" s="600" t="n">
         <v>9</v>
       </c>
-      <c r="H10" s="598" t="n">
+      <c r="H10" s="600" t="n">
         <v>3.1</v>
       </c>
-      <c r="I10" s="598" t="n">
+      <c r="I10" s="600" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="598" t="n">
+      <c r="J10" s="600" t="n">
         <v>0.66</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" s="141">
-      <c r="A11" s="598" t="n">
+    <row r="11" ht="20" customHeight="1" s="141">
+      <c r="A11" s="601" t="n">
         <v>600</v>
       </c>
-      <c r="B11" s="598" t="n">
+      <c r="B11" s="601" t="n">
         <v>2.8</v>
       </c>
-      <c r="C11" s="598" t="n">
+      <c r="C11" s="601" t="n">
         <v>28</v>
       </c>
-      <c r="D11" s="598" t="n">
+      <c r="D11" s="601" t="n">
         <v>9.6</v>
       </c>
-      <c r="E11" s="598" t="n">
+      <c r="E11" s="601" t="n">
         <v>38</v>
       </c>
-      <c r="F11" s="598" t="n">
+      <c r="F11" s="601" t="n">
         <v>1.2</v>
       </c>
-      <c r="G11" s="598" t="n">
+      <c r="G11" s="601" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="598" t="n">
+      <c r="H11" s="601" t="n">
         <v>4.1</v>
       </c>
-      <c r="I11" s="598" t="n">
+      <c r="I11" s="601" t="n">
         <v>16</v>
       </c>
-      <c r="J11" s="598" t="n">
+      <c r="J11" s="601" t="n">
         <v>0.83</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="141">
-      <c r="A12" s="598" t="n">
+    <row r="12" ht="20" customHeight="1" s="141">
+      <c r="A12" s="600" t="n">
         <v>700</v>
       </c>
-      <c r="B12" s="598" t="n">
+      <c r="B12" s="600" t="n">
         <v>3.7</v>
       </c>
-      <c r="C12" s="598" t="n">
+      <c r="C12" s="600" t="n">
         <v>37</v>
       </c>
-      <c r="D12" s="598" t="n">
+      <c r="D12" s="600" t="n">
         <v>12.7</v>
       </c>
-      <c r="E12" s="598" t="n">
+      <c r="E12" s="600" t="n">
         <v>51</v>
       </c>
-      <c r="F12" s="598" t="n">
+      <c r="F12" s="600" t="n">
         <v>1.5</v>
       </c>
-      <c r="G12" s="598" t="n">
+      <c r="G12" s="600" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="598" t="n">
+      <c r="H12" s="600" t="n">
         <v>5.1</v>
       </c>
-      <c r="I12" s="598" t="n">
+      <c r="I12" s="600" t="n">
         <v>20</v>
       </c>
-      <c r="J12" s="598" t="n">
+      <c r="J12" s="600" t="n">
         <v>1.02</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="141">
-      <c r="A13" s="598" t="n">
+    <row r="13" ht="20" customHeight="1" s="141">
+      <c r="A13" s="601" t="n">
         <v>800</v>
       </c>
-      <c r="B13" s="598" t="n">
+      <c r="B13" s="601" t="n">
         <v>4.8</v>
       </c>
-      <c r="C13" s="598" t="n">
+      <c r="C13" s="601" t="n">
         <v>48</v>
       </c>
-      <c r="D13" s="598" t="n">
+      <c r="D13" s="601" t="n">
         <v>16.5</v>
       </c>
-      <c r="E13" s="598" t="n">
+      <c r="E13" s="601" t="n">
         <v>66</v>
       </c>
-      <c r="F13" s="598" t="n">
+      <c r="F13" s="601" t="n">
         <v>1.8</v>
       </c>
-      <c r="G13" s="598" t="n">
+      <c r="G13" s="601" t="n">
         <v>18</v>
       </c>
-      <c r="H13" s="598" t="n">
+      <c r="H13" s="601" t="n">
         <v>6.2</v>
       </c>
-      <c r="I13" s="598" t="n">
+      <c r="I13" s="601" t="n">
         <v>25</v>
       </c>
-      <c r="J13" s="598" t="n">
+      <c r="J13" s="601" t="n">
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="141">
-      <c r="A14" s="598" t="n">
+    <row r="14" ht="20" customHeight="1" s="141">
+      <c r="A14" s="600" t="n">
         <v>900</v>
       </c>
-      <c r="B14" s="598" t="n">
+      <c r="B14" s="600" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="598" t="n">
+      <c r="C14" s="600" t="n">
         <v>60</v>
       </c>
-      <c r="D14" s="598" t="n">
+      <c r="D14" s="600" t="n">
         <v>20.6</v>
       </c>
-      <c r="E14" s="598" t="n">
+      <c r="E14" s="600" t="n">
         <v>82</v>
       </c>
-      <c r="F14" s="598" t="n">
+      <c r="F14" s="600" t="n">
         <v>2.1</v>
       </c>
-      <c r="G14" s="598" t="n">
+      <c r="G14" s="600" t="n">
         <v>21</v>
       </c>
-      <c r="H14" s="598" t="n">
+      <c r="H14" s="600" t="n">
         <v>7.2</v>
       </c>
-      <c r="I14" s="598" t="n">
+      <c r="I14" s="600" t="n">
         <v>29</v>
       </c>
-      <c r="J14" s="598" t="n">
+      <c r="J14" s="600" t="n">
         <v>1.46</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="141">
-      <c r="A15" s="598" t="n">
+    <row r="15" ht="20" customHeight="1" s="141">
+      <c r="A15" s="601" t="n">
         <v>1000</v>
       </c>
-      <c r="B15" s="598" t="n">
+      <c r="B15" s="601" t="n">
         <v>7.3</v>
       </c>
-      <c r="C15" s="598" t="n">
+      <c r="C15" s="601" t="n">
         <v>73</v>
       </c>
-      <c r="D15" s="598" t="n">
+      <c r="D15" s="601" t="n">
         <v>25</v>
       </c>
-      <c r="E15" s="598" t="n">
+      <c r="E15" s="601" t="n">
         <v>100</v>
       </c>
-      <c r="F15" s="598" t="n">
+      <c r="F15" s="601" t="n">
         <v>2.4</v>
       </c>
-      <c r="G15" s="598" t="n">
+      <c r="G15" s="601" t="n">
         <v>24</v>
       </c>
-      <c r="H15" s="598" t="n">
+      <c r="H15" s="601" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I15" s="598" t="n">
+      <c r="I15" s="601" t="n">
         <v>33</v>
       </c>
-      <c r="J15" s="598" t="n">
+      <c r="J15" s="601" t="n">
         <v>1.71</v>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" s="141">
-      <c r="A17" s="599" t="inlineStr">
+    <row r="16" ht="8" customHeight="1" s="141">
+      <c r="A16" s="598" t="n"/>
+      <c r="B16" s="598" t="n"/>
+      <c r="C16" s="598" t="n"/>
+      <c r="D16" s="598" t="n"/>
+      <c r="E16" s="598" t="n"/>
+      <c r="F16" s="598" t="n"/>
+      <c r="G16" s="598" t="n"/>
+      <c r="H16" s="598" t="n"/>
+      <c r="I16" s="598" t="n"/>
+      <c r="J16" s="598" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1" s="141">
+      <c r="A17" s="602" t="inlineStr">
         <is>
           <t>Click "Print Pocket Range Card" on the Ballistics tab to print this card as a 4×6 page.</t>
         </is>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -15,9 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticX Import" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Library" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballistics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Range Card" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GarminSessions" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticXGroups" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GarminSessions" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BallisticXGroups" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'After Range Day'!$A$1:$H$17</definedName>
@@ -53,7 +52,7 @@
     <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="181" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="66">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -465,42 +464,8 @@
       <b val="1"/>
       <color rgb="FFFFFF00"/>
     </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="FF1F4E78"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="FF1F4E78"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="FF555555"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <i val="1"/>
-      <color rgb="FF888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="44">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -740,20 +705,8 @@
         <bgColor rgb="FFFFE082"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor rgb="FFF7F9FC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1057,25 +1010,6 @@
         <color rgb="FFB0B0B0"/>
       </bottom>
     </border>
-    <border>
-      <bottom style="medium">
-        <color rgb="FF1F4E78"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1087,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="603">
+  <cellXfs count="594">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2946,29 +2880,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="42" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="21" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="42" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="43" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8587,877 +8498,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="140" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="B1" s="140" t="inlineStr">
-        <is>
-          <t>ChargeOrJump</t>
-        </is>
-      </c>
-      <c r="C1" s="140" t="inlineStr">
-        <is>
-          <t>Powder</t>
-        </is>
-      </c>
-      <c r="D1" s="140" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" s="140" t="inlineStr">
-        <is>
-          <t>Shot1</t>
-        </is>
-      </c>
-      <c r="F1" s="140" t="inlineStr">
-        <is>
-          <t>Shot2</t>
-        </is>
-      </c>
-      <c r="G1" s="140" t="inlineStr">
-        <is>
-          <t>Shot3</t>
-        </is>
-      </c>
-      <c r="H1" s="140" t="inlineStr">
-        <is>
-          <t>Shot4</t>
-        </is>
-      </c>
-      <c r="I1" s="140" t="inlineStr">
-        <is>
-          <t>Shot5</t>
-        </is>
-      </c>
-      <c r="J1" s="140" t="inlineStr">
-        <is>
-          <t>Shot6</t>
-        </is>
-      </c>
-      <c r="K1" s="140" t="inlineStr">
-        <is>
-          <t>Shot7</t>
-        </is>
-      </c>
-      <c r="L1" s="140" t="inlineStr">
-        <is>
-          <t>Shot8</t>
-        </is>
-      </c>
-      <c r="M1" s="140" t="inlineStr">
-        <is>
-          <t>Shot9</t>
-        </is>
-      </c>
-      <c r="N1" s="140" t="inlineStr">
-        <is>
-          <t>Shot10</t>
-        </is>
-      </c>
-      <c r="O1" s="140" t="inlineStr">
-        <is>
-          <t>AvgVel</t>
-        </is>
-      </c>
-      <c r="P1" s="140" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="Q1" s="140" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="R1" s="140" t="inlineStr">
-        <is>
-          <t>BulletWt</t>
-        </is>
-      </c>
-      <c r="S1" s="140" t="inlineStr">
-        <is>
-          <t>AvgKE</t>
-        </is>
-      </c>
-      <c r="T1" s="140" t="inlineStr">
-        <is>
-          <t>SessionTitle</t>
-        </is>
-      </c>
-      <c r="U1" s="140" t="inlineStr">
-        <is>
-          <t>SessionNote</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2710</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2718</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2705</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2715</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2712</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2722</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2708</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2716</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2724</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2715</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19</v>
-      </c>
-      <c r="R2" t="n">
-        <v>140</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2293</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 41.5gr</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2732</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2748</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2725</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2740</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2734</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2742</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2728</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2736</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2747</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2737</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>140</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 41.8gr</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2755</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2762</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2750</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2768</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2758</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2765</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2752</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2770</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2760</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R4" t="n">
-        <v>140</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2369</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.1gr</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2778</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2782</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2776</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2779</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2778</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2781</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>140</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.4gr (WINNER)</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2798</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2805</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2795</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2812</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2800</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2802</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2806</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2796</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2802</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2810</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2803</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>17</v>
-      </c>
-      <c r="R6" t="n">
-        <v>140</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2443</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>6.5 CM H4350 42.7gr</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2778</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2784</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2782</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2781</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>140</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2404</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Seating depth +0.005 jump</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2778</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2782</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2776</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2784</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2782</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>140</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Seating depth +0.020 jump</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2781</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2782</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2782</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2780</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2781</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2780.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>140</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2403</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Seating depth +0.035 jump (WINNER)</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2784</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2776</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2782</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2778</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2784</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2782</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2774</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" t="n">
-        <v>140</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Seating depth +0.050 jump</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>H4350</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2786</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2774</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2776</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2782</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2786</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2776</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2784</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>140</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2402</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Seating depth +0.065 jump</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>42.4gr H4350, same brass/primer as PL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -29375,472 +28415,867 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" style="141" min="1" max="1"/>
-    <col width="8" customWidth="1" style="141" min="2" max="2"/>
-    <col width="8" customWidth="1" style="141" min="3" max="3"/>
-    <col width="8" customWidth="1" style="141" min="4" max="4"/>
-    <col width="8" customWidth="1" style="141" min="5" max="5"/>
-    <col width="9" customWidth="1" style="141" min="6" max="6"/>
-    <col width="8" customWidth="1" style="141" min="7" max="7"/>
-    <col width="9" customWidth="1" style="141" min="8" max="8"/>
-    <col width="8" customWidth="1" style="141" min="9" max="9"/>
-    <col width="9" customWidth="1" style="141" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="141">
-      <c r="A1" s="594" t="inlineStr">
-        <is>
-          <t>POCKET RANGE CARD</t>
-        </is>
-      </c>
-      <c r="B1" s="595" t="n"/>
-      <c r="C1" s="595" t="n"/>
-      <c r="D1" s="595" t="n"/>
-      <c r="E1" s="595" t="n"/>
-      <c r="F1" s="595" t="n"/>
-      <c r="G1" s="595" t="n"/>
-      <c r="H1" s="595" t="n"/>
-      <c r="I1" s="595" t="n"/>
-      <c r="J1" s="595" t="n"/>
-    </row>
-    <row r="2" ht="26" customHeight="1" s="141">
-      <c r="A2" s="596" t="inlineStr">
-        <is>
-          <t>Tikka T3X CTR 6.5 CM  •  Hornady 140gr ELD-M  •  42.4gr  •  2780 fps</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" s="141">
-      <c r="A3" s="597" t="inlineStr">
-        <is>
-          <t>Scope: Leupold Mark 5HD 5-25x56   ·   Click: 0.1 Mil   ·   Zero: 100 yd   ·   Sight Ht: 1.75"   ·   Twist: 1:8 RH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="8" customHeight="1" s="141">
-      <c r="A4" s="598" t="n"/>
-      <c r="B4" s="598" t="n"/>
-      <c r="C4" s="598" t="n"/>
-      <c r="D4" s="598" t="n"/>
-      <c r="E4" s="598" t="n"/>
-      <c r="F4" s="598" t="n"/>
-      <c r="G4" s="598" t="n"/>
-      <c r="H4" s="598" t="n"/>
-      <c r="I4" s="598" t="n"/>
-      <c r="J4" s="598" t="n"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" s="141">
-      <c r="A5" s="599" t="inlineStr">
-        <is>
-          <t>Range
-(yd)</t>
-        </is>
-      </c>
-      <c r="B5" s="599" t="inlineStr">
-        <is>
-          <t>Mils
-Elev</t>
-        </is>
-      </c>
-      <c r="C5" s="599" t="inlineStr">
-        <is>
-          <t>Mil
-Clicks</t>
-        </is>
-      </c>
-      <c r="D5" s="599" t="inlineStr">
-        <is>
-          <t>MOA
-Elev</t>
-        </is>
-      </c>
-      <c r="E5" s="599" t="inlineStr">
-        <is>
-          <t>MOA
-Clicks</t>
-        </is>
-      </c>
-      <c r="F5" s="599" t="inlineStr">
-        <is>
-          <t>Wind
-Mils/10</t>
-        </is>
-      </c>
-      <c r="G5" s="599" t="inlineStr">
-        <is>
-          <t>Wind
-Mil Clk</t>
-        </is>
-      </c>
-      <c r="H5" s="599" t="inlineStr">
-        <is>
-          <t>Wind
-MOA/10</t>
-        </is>
-      </c>
-      <c r="I5" s="599" t="inlineStr">
-        <is>
-          <t>Wind
-MOA Clk</t>
-        </is>
-      </c>
-      <c r="J5" s="599" t="inlineStr">
-        <is>
-          <t>TOF
-(sec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="141">
-      <c r="A6" s="600" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="600" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="600" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="141">
-      <c r="A7" s="601" t="n">
-        <v>200</v>
-      </c>
-      <c r="B7" s="601" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="601" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="601" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="601" t="n">
+    <row r="1">
+      <c r="A1" s="140" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" s="140" t="inlineStr">
+        <is>
+          <t>ChargeOrJump</t>
+        </is>
+      </c>
+      <c r="C1" s="140" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="D1" s="140" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="140" t="inlineStr">
+        <is>
+          <t>Shot1</t>
+        </is>
+      </c>
+      <c r="F1" s="140" t="inlineStr">
+        <is>
+          <t>Shot2</t>
+        </is>
+      </c>
+      <c r="G1" s="140" t="inlineStr">
+        <is>
+          <t>Shot3</t>
+        </is>
+      </c>
+      <c r="H1" s="140" t="inlineStr">
+        <is>
+          <t>Shot4</t>
+        </is>
+      </c>
+      <c r="I1" s="140" t="inlineStr">
+        <is>
+          <t>Shot5</t>
+        </is>
+      </c>
+      <c r="J1" s="140" t="inlineStr">
+        <is>
+          <t>Shot6</t>
+        </is>
+      </c>
+      <c r="K1" s="140" t="inlineStr">
+        <is>
+          <t>Shot7</t>
+        </is>
+      </c>
+      <c r="L1" s="140" t="inlineStr">
+        <is>
+          <t>Shot8</t>
+        </is>
+      </c>
+      <c r="M1" s="140" t="inlineStr">
+        <is>
+          <t>Shot9</t>
+        </is>
+      </c>
+      <c r="N1" s="140" t="inlineStr">
+        <is>
+          <t>Shot10</t>
+        </is>
+      </c>
+      <c r="O1" s="140" t="inlineStr">
+        <is>
+          <t>AvgVel</t>
+        </is>
+      </c>
+      <c r="P1" s="140" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="Q1" s="140" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="R1" s="140" t="inlineStr">
+        <is>
+          <t>BulletWt</t>
+        </is>
+      </c>
+      <c r="S1" s="140" t="inlineStr">
+        <is>
+          <t>AvgKE</t>
+        </is>
+      </c>
+      <c r="T1" s="140" t="inlineStr">
+        <is>
+          <t>SessionTitle</t>
+        </is>
+      </c>
+      <c r="U1" s="140" t="inlineStr">
+        <is>
+          <t>SessionNote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2718</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2705</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2715</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2712</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2722</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2708</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2716</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2724</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2715</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R2" t="n">
+        <v>140</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2293</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 41.5gr</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2732</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2748</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2725</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2740</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2734</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2742</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2728</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2736</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2747</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2737</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>140</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 41.8gr</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2762</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2768</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2758</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2765</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2752</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2770</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2760</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>140</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2369</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.1gr</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2778</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2782</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2776</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2779</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2778</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2781</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>140</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.4gr (WINNER)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2798</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2805</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2795</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2800</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2802</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2806</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2796</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2802</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2803</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>17</v>
+      </c>
+      <c r="R6" t="n">
+        <v>140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2443</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6.5 CM H4350 42.7gr</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hornady brass, CCI BR-2 primer, 2.875 OAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2784</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2781</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>140</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2404</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Seating depth +0.005 jump</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2782</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2776</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2784</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2782</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>140</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Seating depth +0.020 jump</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2781</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2782</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2782</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2780</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2781</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2780.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="601" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="601" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="601" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="601" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="601" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="141">
-      <c r="A8" s="600" t="n">
-        <v>300</v>
-      </c>
-      <c r="B8" s="600" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C8" s="600" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="600" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="600" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="600" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="600" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="600" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I8" s="600" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="600" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="141">
-      <c r="A9" s="601" t="n">
-        <v>400</v>
-      </c>
-      <c r="B9" s="601" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C9" s="601" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="601" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E9" s="601" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" s="601" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G9" s="601" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="601" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I9" s="601" t="n">
+      <c r="R9" t="n">
+        <v>140</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2403</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Seating depth +0.035 jump (WINNER)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2784</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2776</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2782</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2784</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2782</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2774</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="601" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="141">
-      <c r="A10" s="600" t="n">
-        <v>500</v>
-      </c>
-      <c r="B10" s="600" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="600" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="600" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E10" s="600" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" s="600" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G10" s="600" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="600" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I10" s="600" t="n">
-        <v>12</v>
-      </c>
-      <c r="J10" s="600" t="n">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="141">
-      <c r="A11" s="601" t="n">
-        <v>600</v>
-      </c>
-      <c r="B11" s="601" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C11" s="601" t="n">
-        <v>28</v>
-      </c>
-      <c r="D11" s="601" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E11" s="601" t="n">
-        <v>38</v>
-      </c>
-      <c r="F11" s="601" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G11" s="601" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" s="601" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I11" s="601" t="n">
-        <v>16</v>
-      </c>
-      <c r="J11" s="601" t="n">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="141">
-      <c r="A12" s="600" t="n">
-        <v>700</v>
-      </c>
-      <c r="B12" s="600" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C12" s="600" t="n">
-        <v>37</v>
-      </c>
-      <c r="D12" s="600" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="E12" s="600" t="n">
-        <v>51</v>
-      </c>
-      <c r="F12" s="600" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="600" t="n">
-        <v>15</v>
-      </c>
-      <c r="H12" s="600" t="n">
+      <c r="R10" t="n">
+        <v>140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Seating depth +0.050 jump</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>H4350</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2786</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2784</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2776</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2782</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2772</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2786</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2776</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2784</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2780</v>
+      </c>
+      <c r="P11" t="n">
         <v>5.1</v>
       </c>
-      <c r="I12" s="600" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="600" t="n">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="141">
-      <c r="A13" s="601" t="n">
-        <v>800</v>
-      </c>
-      <c r="B13" s="601" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="C13" s="601" t="n">
-        <v>48</v>
-      </c>
-      <c r="D13" s="601" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E13" s="601" t="n">
-        <v>66</v>
-      </c>
-      <c r="F13" s="601" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G13" s="601" t="n">
-        <v>18</v>
-      </c>
-      <c r="H13" s="601" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I13" s="601" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" s="601" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="141">
-      <c r="A14" s="600" t="n">
-        <v>900</v>
-      </c>
-      <c r="B14" s="600" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="600" t="n">
-        <v>60</v>
-      </c>
-      <c r="D14" s="600" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E14" s="600" t="n">
-        <v>82</v>
-      </c>
-      <c r="F14" s="600" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G14" s="600" t="n">
-        <v>21</v>
-      </c>
-      <c r="H14" s="600" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I14" s="600" t="n">
-        <v>29</v>
-      </c>
-      <c r="J14" s="600" t="n">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="141">
-      <c r="A15" s="601" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B15" s="601" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C15" s="601" t="n">
-        <v>73</v>
-      </c>
-      <c r="D15" s="601" t="n">
-        <v>25</v>
-      </c>
-      <c r="E15" s="601" t="n">
-        <v>100</v>
-      </c>
-      <c r="F15" s="601" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G15" s="601" t="n">
-        <v>24</v>
-      </c>
-      <c r="H15" s="601" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I15" s="601" t="n">
-        <v>33</v>
-      </c>
-      <c r="J15" s="601" t="n">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1" s="141">
-      <c r="A16" s="598" t="n"/>
-      <c r="B16" s="598" t="n"/>
-      <c r="C16" s="598" t="n"/>
-      <c r="D16" s="598" t="n"/>
-      <c r="E16" s="598" t="n"/>
-      <c r="F16" s="598" t="n"/>
-      <c r="G16" s="598" t="n"/>
-      <c r="H16" s="598" t="n"/>
-      <c r="I16" s="598" t="n"/>
-      <c r="J16" s="598" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1" s="141">
-      <c r="A17" s="602" t="inlineStr">
-        <is>
-          <t>Click "Print Pocket Range Card" on the Ballistics tab to print this card as a 4×6 page.</t>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>140</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2402</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Seating depth +0.065 jump</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>42.4gr H4350, same brass/primer as PL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -1021,7 +1021,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="594">
+  <cellXfs count="596">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2879,6 +2879,13 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -26011,12 +26018,12 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B5" s="270" t="inlineStr">
+      <c r="B5" s="594" t="inlineStr">
         <is>
           <t>Tikka T3X CTR 6.5 CM</t>
         </is>
       </c>
-      <c r="C5" s="382" t="n"/>
+      <c r="C5" s="166" t="n"/>
       <c r="D5" s="381" t="inlineStr">
         <is>
           <t>Bullet:</t>
@@ -26052,12 +26059,12 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B6" s="363" t="inlineStr">
+      <c r="B6" s="595" t="inlineStr">
         <is>
           <t>Leupold Mark 5HD 5-25x56</t>
         </is>
       </c>
-      <c r="C6" s="384" t="n"/>
+      <c r="C6" s="323" t="n"/>
       <c r="D6" s="383" t="inlineStr">
         <is>
           <t>Zero (yd):</t>
@@ -28382,10 +28389,12 @@
     <row r="91" ht="12" customHeight="1" s="141"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A76:K76"/>
     <mergeCell ref="A1:K1"/>

--- a/app/resources/Loadscope - Demo Workbook.xlsx
+++ b/app/resources/Loadscope - Demo Workbook.xlsx
@@ -1138,7 +1138,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="713">
+  <cellXfs count="714">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -3109,6 +3109,9 @@
     </xf>
     <xf numFmtId="176" fontId="24" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="41" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="51" fillId="40" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13182,83 +13185,89 @@
         </is>
       </c>
     </row>
-    <row r="14" hidden="1" s="141"/>
+    <row r="14" hidden="1" ht="22" customHeight="1" s="141">
+      <c r="A14" s="635" t="inlineStr">
+        <is>
+          <t>→  Print This Workbook  ←</t>
+        </is>
+      </c>
+    </row>
     <row r="15" hidden="1" s="141"/>
     <row r="16" hidden="1" s="141"/>
     <row r="17" ht="42" customHeight="1" s="141">
-      <c r="A17" s="635" t="inlineStr">
+      <c r="A17" s="636" t="inlineStr">
         <is>
           <t>Charge</t>
         </is>
       </c>
       <c r="B17" s="261" t="n"/>
       <c r="C17" s="261" t="n"/>
-      <c r="D17" s="635" t="inlineStr">
+      <c r="D17" s="636" t="inlineStr">
         <is>
           <t>Avg Vel (fps)</t>
         </is>
       </c>
-      <c r="E17" s="636" t="inlineStr">
+      <c r="E17" s="637" t="inlineStr">
         <is>
           <t>SD (fps)</t>
         </is>
       </c>
-      <c r="F17" s="636" t="inlineStr">
+      <c r="F17" s="637" t="inlineStr">
         <is>
           <t>Mean Radius (MOA)</t>
         </is>
       </c>
-      <c r="G17" s="636" t="inlineStr">
+      <c r="G17" s="637" t="inlineStr">
         <is>
           <t>SD-Vert (MOA)</t>
         </is>
       </c>
-      <c r="H17" s="636" t="inlineStr">
+      <c r="H17" s="637" t="inlineStr">
         <is>
           <t>Norm Vel</t>
         </is>
       </c>
-      <c r="I17" s="636" t="inlineStr">
+      <c r="I17" s="637" t="inlineStr">
         <is>
           <t>Norm SD</t>
         </is>
       </c>
-      <c r="J17" s="636" t="inlineStr">
+      <c r="J17" s="637" t="inlineStr">
         <is>
           <t>Norm MR</t>
         </is>
       </c>
-      <c r="K17" s="636" t="inlineStr">
+      <c r="K17" s="637" t="inlineStr">
         <is>
           <t>Norm SD-Vert</t>
         </is>
       </c>
-      <c r="L17" s="636" t="inlineStr">
+      <c r="L17" s="637" t="inlineStr">
         <is>
           <t>Composite Score</t>
         </is>
       </c>
-      <c r="M17" s="637" t="inlineStr">
+      <c r="M17" s="638" t="inlineStr">
         <is>
           <t>Chart: Vel Spread</t>
         </is>
       </c>
-      <c r="N17" s="638" t="inlineStr">
+      <c r="N17" s="639" t="inlineStr">
         <is>
           <t>Chart: SD</t>
         </is>
       </c>
-      <c r="O17" s="638" t="inlineStr">
+      <c r="O17" s="639" t="inlineStr">
         <is>
           <t>Chart: MR</t>
         </is>
       </c>
-      <c r="P17" s="638" t="inlineStr">
+      <c r="P17" s="639" t="inlineStr">
         <is>
           <t>Chart: Vert</t>
         </is>
       </c>
-      <c r="Q17" s="638" t="inlineStr">
+      <c r="Q17" s="639" t="inlineStr">
         <is>
           <t>Chart: Composite</t>
         </is>
@@ -13280,251 +13289,251 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="141">
-      <c r="A18" s="639">
+      <c r="A18" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B17,IF('Load Log'!B16="","",'Load Log'!B16)),"")</f>
         <v/>
       </c>
       <c r="B18" s="558" t="n"/>
       <c r="C18" s="558" t="n"/>
-      <c r="D18" s="640" t="n">
+      <c r="D18" s="641" t="n">
         <v>2715</v>
       </c>
-      <c r="E18" s="639" t="n">
+      <c r="E18" s="640" t="n">
         <v>6.7</v>
       </c>
-      <c r="F18" s="641" t="n">
+      <c r="F18" s="642" t="n">
         <v>0.31</v>
       </c>
-      <c r="G18" s="641" t="n">
+      <c r="G18" s="642" t="n">
         <v>0.2</v>
       </c>
-      <c r="H18" s="642" t="n">
+      <c r="H18" s="643" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="I18" s="642" t="n">
+      <c r="I18" s="643" t="n">
         <v>0.792</v>
       </c>
-      <c r="J18" s="642" t="n">
+      <c r="J18" s="643" t="n">
         <v>0.542</v>
       </c>
-      <c r="K18" s="642" t="n">
+      <c r="K18" s="643" t="n">
         <v>0.571</v>
       </c>
-      <c r="L18" s="642" t="n">
+      <c r="L18" s="643" t="n">
         <v>0.606</v>
       </c>
-      <c r="M18" s="643">
+      <c r="M18" s="644">
         <f>IF(D18="",NA(),H18)</f>
         <v/>
       </c>
-      <c r="N18" s="644">
+      <c r="N18" s="645">
         <f>IF(D18="",NA(),I18)</f>
         <v/>
       </c>
-      <c r="O18" s="644">
+      <c r="O18" s="645">
         <f>IF(D18="",NA(),J18)</f>
         <v/>
       </c>
-      <c r="P18" s="644">
+      <c r="P18" s="645">
         <f>IF(D18="",NA(),K18)</f>
         <v/>
       </c>
-      <c r="Q18" s="644">
+      <c r="Q18" s="645">
         <f>IF(D18="",NA(),L18)</f>
         <v/>
       </c>
-      <c r="R18" s="645">
+      <c r="R18" s="646">
         <f>IFERROR(IF(D18=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E18=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F18=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G18=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T18" s="645" t="n">
+      <c r="T18" s="646" t="n">
         <v>41.5</v>
       </c>
-      <c r="U18" s="645" t="n">
+      <c r="U18" s="646" t="n">
         <v>2715</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="141">
-      <c r="A19" s="646">
+      <c r="A19" s="647">
         <f>IFERROR(IF($B$100="window",'Load Log'!B18,IF('Load Log'!B17="","",'Load Log'!B17)),"")</f>
         <v/>
       </c>
       <c r="B19" s="562" t="n"/>
       <c r="C19" s="562" t="n"/>
-      <c r="D19" s="647" t="n">
+      <c r="D19" s="648" t="n">
         <v>2737</v>
       </c>
-      <c r="E19" s="646" t="n">
+      <c r="E19" s="647" t="n">
         <v>7.8</v>
       </c>
-      <c r="F19" s="648" t="n">
+      <c r="F19" s="649" t="n">
         <v>0.42</v>
       </c>
-      <c r="G19" s="641" t="n">
+      <c r="G19" s="642" t="n">
         <v>0.26</v>
       </c>
-      <c r="H19" s="642" t="n">
+      <c r="H19" s="643" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="642" t="n">
+      <c r="I19" s="643" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="642" t="n">
+      <c r="J19" s="643" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="642" t="n">
+      <c r="K19" s="643" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="642" t="n">
+      <c r="L19" s="643" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="643">
+      <c r="M19" s="644">
         <f>IF(D19="",NA(),H19)</f>
         <v/>
       </c>
-      <c r="N19" s="644">
+      <c r="N19" s="645">
         <f>IF(D19="",NA(),I19)</f>
         <v/>
       </c>
-      <c r="O19" s="644">
+      <c r="O19" s="645">
         <f>IF(D19="",NA(),J19)</f>
         <v/>
       </c>
-      <c r="P19" s="644">
+      <c r="P19" s="645">
         <f>IF(D19="",NA(),K19)</f>
         <v/>
       </c>
-      <c r="Q19" s="644">
+      <c r="Q19" s="645">
         <f>IF(D19="",NA(),L19)</f>
         <v/>
       </c>
-      <c r="R19" s="645">
+      <c r="R19" s="646">
         <f>IFERROR(IF(D19=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E19=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F19=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G19=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T19" s="645" t="n">
+      <c r="T19" s="646" t="n">
         <v>41.8</v>
       </c>
-      <c r="U19" s="645" t="n">
+      <c r="U19" s="646" t="n">
         <v>2737</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="141">
-      <c r="A20" s="639">
+      <c r="A20" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B19,IF('Load Log'!B18="","",'Load Log'!B18)),"")</f>
         <v/>
       </c>
       <c r="B20" s="558" t="n"/>
       <c r="C20" s="558" t="n"/>
-      <c r="D20" s="640" t="n">
+      <c r="D20" s="641" t="n">
         <v>2760</v>
       </c>
-      <c r="E20" s="639" t="n">
+      <c r="E20" s="640" t="n">
         <v>6.4</v>
       </c>
-      <c r="F20" s="641" t="n">
+      <c r="F20" s="642" t="n">
         <v>0.22</v>
       </c>
-      <c r="G20" s="641" t="n">
+      <c r="G20" s="642" t="n">
         <v>0.14</v>
       </c>
-      <c r="H20" s="642" t="n">
+      <c r="H20" s="643" t="n">
         <v>0.163</v>
       </c>
-      <c r="I20" s="642" t="n">
+      <c r="I20" s="643" t="n">
         <v>0.736</v>
       </c>
-      <c r="J20" s="642" t="n">
+      <c r="J20" s="643" t="n">
         <v>0.167</v>
       </c>
-      <c r="K20" s="642" t="n">
+      <c r="K20" s="643" t="n">
         <v>0.143</v>
       </c>
-      <c r="L20" s="642" t="n">
+      <c r="L20" s="643" t="n">
         <v>0.272</v>
       </c>
-      <c r="M20" s="643">
+      <c r="M20" s="644">
         <f>IF(D20="",NA(),H20)</f>
         <v/>
       </c>
-      <c r="N20" s="644">
+      <c r="N20" s="645">
         <f>IF(D20="",NA(),I20)</f>
         <v/>
       </c>
-      <c r="O20" s="644">
+      <c r="O20" s="645">
         <f>IF(D20="",NA(),J20)</f>
         <v/>
       </c>
-      <c r="P20" s="644">
+      <c r="P20" s="645">
         <f>IF(D20="",NA(),K20)</f>
         <v/>
       </c>
-      <c r="Q20" s="644">
+      <c r="Q20" s="645">
         <f>IF(D20="",NA(),L20)</f>
         <v/>
       </c>
-      <c r="R20" s="645">
+      <c r="R20" s="646">
         <f>IFERROR(IF(D20=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E20=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F20=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G20=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T20" s="645" t="n">
+      <c r="T20" s="646" t="n">
         <v>42.1</v>
       </c>
-      <c r="U20" s="645" t="n">
+      <c r="U20" s="646" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="141">
-      <c r="A21" s="646">
+      <c r="A21" s="647">
         <f>IFERROR(IF($B$100="window",'Load Log'!B20,IF('Load Log'!B19="","",'Load Log'!B19)),"")</f>
         <v/>
       </c>
       <c r="B21" s="562" t="n"/>
       <c r="C21" s="562" t="n"/>
-      <c r="D21" s="647" t="n">
+      <c r="D21" s="648" t="n">
         <v>2780</v>
       </c>
-      <c r="E21" s="646" t="n">
+      <c r="E21" s="647" t="n">
         <v>2.5</v>
       </c>
-      <c r="F21" s="648" t="n">
+      <c r="F21" s="649" t="n">
         <v>0.18</v>
       </c>
-      <c r="G21" s="641" t="n">
+      <c r="G21" s="642" t="n">
         <v>0.12</v>
       </c>
-      <c r="H21" s="642" t="n">
+      <c r="H21" s="643" t="n">
         <v>0.001</v>
       </c>
-      <c r="I21" s="642" t="n">
+      <c r="I21" s="643" t="n">
         <v>0.001</v>
       </c>
-      <c r="J21" s="642" t="n">
+      <c r="J21" s="643" t="n">
         <v>0.001</v>
       </c>
-      <c r="K21" s="642" t="n">
+      <c r="K21" s="643" t="n">
         <v>0.001</v>
       </c>
-      <c r="L21" s="642" t="n">
+      <c r="L21" s="643" t="n">
         <v>0.001</v>
       </c>
-      <c r="M21" s="643">
+      <c r="M21" s="644">
         <f>IF(D21="",NA(),H21)</f>
         <v/>
       </c>
-      <c r="N21" s="644">
+      <c r="N21" s="645">
         <f>IF(D21="",NA(),I21)</f>
         <v/>
       </c>
-      <c r="O21" s="644">
+      <c r="O21" s="645">
         <f>IF(D21="",NA(),J21)</f>
         <v/>
       </c>
-      <c r="P21" s="644">
+      <c r="P21" s="645">
         <f>IF(D21="",NA(),K21)</f>
         <v/>
       </c>
-      <c r="Q21" s="644">
+      <c r="Q21" s="645">
         <f>IF(D21="",NA(),L21)</f>
         <v/>
       </c>
@@ -13533,321 +13542,321 @@
           <t>All metrics ✓</t>
         </is>
       </c>
-      <c r="T21" s="645" t="n">
+      <c r="T21" s="646" t="n">
         <v>42.4</v>
       </c>
-      <c r="U21" s="645" t="n">
+      <c r="U21" s="646" t="n">
         <v>2780</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="141">
-      <c r="A22" s="639">
+      <c r="A22" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B21,IF('Load Log'!B20="","",'Load Log'!B20)),"")</f>
         <v/>
       </c>
       <c r="B22" s="558" t="n"/>
       <c r="C22" s="558" t="n"/>
-      <c r="D22" s="640" t="n">
+      <c r="D22" s="641" t="n">
         <v>2803</v>
       </c>
-      <c r="E22" s="639" t="n">
+      <c r="E22" s="640" t="n">
         <v>5.6</v>
       </c>
-      <c r="F22" s="641" t="n">
+      <c r="F22" s="642" t="n">
         <v>0.29</v>
       </c>
-      <c r="G22" s="641" t="n">
+      <c r="G22" s="642" t="n">
         <v>0.18</v>
       </c>
-      <c r="H22" s="642" t="n">
+      <c r="H22" s="643" t="n">
         <v>0.465</v>
       </c>
-      <c r="I22" s="642" t="n">
+      <c r="I22" s="643" t="n">
         <v>0.585</v>
       </c>
-      <c r="J22" s="642" t="n">
+      <c r="J22" s="643" t="n">
         <v>0.458</v>
       </c>
-      <c r="K22" s="642" t="n">
+      <c r="K22" s="643" t="n">
         <v>0.429</v>
       </c>
-      <c r="L22" s="642" t="n">
+      <c r="L22" s="643" t="n">
         <v>0.477</v>
       </c>
-      <c r="M22" s="643">
+      <c r="M22" s="644">
         <f>IF(D22="",NA(),H22)</f>
         <v/>
       </c>
-      <c r="N22" s="644">
+      <c r="N22" s="645">
         <f>IF(D22="",NA(),I22)</f>
         <v/>
       </c>
-      <c r="O22" s="644">
+      <c r="O22" s="645">
         <f>IF(D22="",NA(),J22)</f>
         <v/>
       </c>
-      <c r="P22" s="644">
+      <c r="P22" s="645">
         <f>IF(D22="",NA(),K22)</f>
         <v/>
       </c>
-      <c r="Q22" s="644">
+      <c r="Q22" s="645">
         <f>IF(D22="",NA(),L22)</f>
         <v/>
       </c>
-      <c r="R22" s="645">
+      <c r="R22" s="646">
         <f>IFERROR(IF(D22=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E22=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F22=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G22=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T22" s="645" t="n">
+      <c r="T22" s="646" t="n">
         <v>42.7</v>
       </c>
-      <c r="U22" s="645" t="n">
+      <c r="U22" s="646" t="n">
         <v>2803</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="141">
-      <c r="A23" s="639">
+      <c r="A23" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B22,IF('Load Log'!B21="","",'Load Log'!B21)),"")</f>
         <v/>
       </c>
-      <c r="B23" s="639">
+      <c r="B23" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B21,""),"")</f>
         <v/>
       </c>
-      <c r="C23" s="639">
+      <c r="C23" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B23,""),"")</f>
         <v/>
       </c>
-      <c r="D23" s="640">
+      <c r="D23" s="641">
         <f>IF($B$100="window",IF(OR(A23="",B23="",C23=""),"",MAX('Load Log'!H21:H23)-MIN('Load Log'!H21:H23)),IF('Load Log'!H21="","",'Load Log'!H21))</f>
         <v/>
       </c>
-      <c r="E23" s="639">
+      <c r="E23" s="640">
         <f>IF($B$100="window",IF(OR(A23="",B23="",C23=""),"",'Load Log'!J22),IF('Load Log'!J21="","",'Load Log'!J21))</f>
         <v/>
       </c>
-      <c r="F23" s="641">
+      <c r="F23" s="642">
         <f>IF($B$100="window",IF(OR(A23="",B23="",C23=""),"",IFERROR(IF('Load Log'!N22="",'Load Log'!K22,'Load Log'!N22)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N21="",'Load Log'!K21,'Load Log'!N21)/('Load Log'!$L$10/100)/1.047,""))</f>
         <v/>
       </c>
-      <c r="G23" s="641">
+      <c r="G23" s="642">
         <f>IF($B$100="window",IF(OR(A23="",B23="",C23=""),"",IF('Load Log'!M22="",IF('Load Log'!L22="",F23,'Load Log'!L22/('Load Log'!$L$10/100)/1.047),'Load Log'!M22/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M21="",IF('Load Log'!L21="",F23,'Load Log'!L21/('Load Log'!$L$10/100)/1.047),'Load Log'!M21/('Load Log'!$L$10/100)/1.047))</f>
         <v/>
       </c>
-      <c r="H23" s="642">
+      <c r="H23" s="643">
         <f>IF(D23="","",IFERROR((D23-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
         <v/>
       </c>
-      <c r="I23" s="642">
+      <c r="I23" s="643">
         <f>IF(E23="","",IFERROR((E23-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
         <v/>
       </c>
-      <c r="J23" s="642">
+      <c r="J23" s="643">
         <f>IF(F23="","",IFERROR((F23-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
         <v/>
       </c>
-      <c r="K23" s="642">
+      <c r="K23" s="643">
         <f>IF(G23="","",IFERROR((G23-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
         <v/>
       </c>
-      <c r="L23" s="642">
+      <c r="L23" s="643">
         <f>IF(A23="","",H23*$B$11+I23*$D$11+J23*$F$11+K23*$H$11)</f>
         <v/>
       </c>
-      <c r="M23" s="643">
+      <c r="M23" s="644">
         <f>IF(D23="",NA(),H23)</f>
         <v/>
       </c>
-      <c r="N23" s="644">
+      <c r="N23" s="645">
         <f>IF(D23="",NA(),I23)</f>
         <v/>
       </c>
-      <c r="O23" s="644">
+      <c r="O23" s="645">
         <f>IF(D23="",NA(),J23)</f>
         <v/>
       </c>
-      <c r="P23" s="644">
+      <c r="P23" s="645">
         <f>IF(D23="",NA(),K23)</f>
         <v/>
       </c>
-      <c r="Q23" s="644">
+      <c r="Q23" s="645">
         <f>IF(D23="",NA(),L23)</f>
         <v/>
       </c>
-      <c r="R23" s="645">
+      <c r="R23" s="646">
         <f>IFERROR(IF(D23=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E23=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F23=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G23=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T23" s="645">
+      <c r="T23" s="646">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="U23" s="645">
+      <c r="U23" s="646">
         <f>NA()</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="141">
-      <c r="A24" s="639">
+      <c r="A24" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B23,IF('Load Log'!B22="","",'Load Log'!B22)),"")</f>
         <v/>
       </c>
-      <c r="B24" s="639">
+      <c r="B24" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B22,""),"")</f>
         <v/>
       </c>
-      <c r="C24" s="639">
+      <c r="C24" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B24,""),"")</f>
         <v/>
       </c>
-      <c r="D24" s="640">
+      <c r="D24" s="641">
         <f>IF($B$100="window",IF(OR(A24="",B24="",C24=""),"",MAX('Load Log'!H22:H24)-MIN('Load Log'!H22:H24)),IF('Load Log'!H22="","",'Load Log'!H22))</f>
         <v/>
       </c>
-      <c r="E24" s="639">
+      <c r="E24" s="640">
         <f>IF($B$100="window",IF(OR(A24="",B24="",C24=""),"",'Load Log'!J23),IF('Load Log'!J22="","",'Load Log'!J22))</f>
         <v/>
       </c>
-      <c r="F24" s="641">
+      <c r="F24" s="642">
         <f>IF($B$100="window",IF(OR(A24="",B24="",C24=""),"",IFERROR(IF('Load Log'!N23="",'Load Log'!K23,'Load Log'!N23)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N22="",'Load Log'!K22,'Load Log'!N22)/('Load Log'!$L$10/100)/1.047,""))</f>
         <v/>
       </c>
-      <c r="G24" s="641">
+      <c r="G24" s="642">
         <f>IF($B$100="window",IF(OR(A24="",B24="",C24=""),"",IF('Load Log'!M23="",IF('Load Log'!L23="",F24,'Load Log'!L23/('Load Log'!$L$10/100)/1.047),'Load Log'!M23/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M22="",IF('Load Log'!L22="",F24,'Load Log'!L22/('Load Log'!$L$10/100)/1.047),'Load Log'!M22/('Load Log'!$L$10/100)/1.047))</f>
         <v/>
       </c>
-      <c r="H24" s="642">
+      <c r="H24" s="643">
         <f>IF(D24="","",IFERROR((D24-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
         <v/>
       </c>
-      <c r="I24" s="642">
+      <c r="I24" s="643">
         <f>IF(E24="","",IFERROR((E24-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
         <v/>
       </c>
-      <c r="J24" s="642">
+      <c r="J24" s="643">
         <f>IF(F24="","",IFERROR((F24-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
         <v/>
       </c>
-      <c r="K24" s="642">
+      <c r="K24" s="643">
         <f>IF(G24="","",IFERROR((G24-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
         <v/>
       </c>
-      <c r="L24" s="642">
+      <c r="L24" s="643">
         <f>IF(A24="","",H24*$B$11+I24*$D$11+J24*$F$11+K24*$H$11)</f>
         <v/>
       </c>
-      <c r="M24" s="643">
+      <c r="M24" s="644">
         <f>IF(D24="",NA(),H24)</f>
         <v/>
       </c>
-      <c r="N24" s="649">
+      <c r="N24" s="650">
         <f>IF(D24="",NA(),I24)</f>
         <v/>
       </c>
-      <c r="O24" s="649">
+      <c r="O24" s="650">
         <f>IF(D24="",NA(),J24)</f>
         <v/>
       </c>
-      <c r="P24" s="649">
+      <c r="P24" s="650">
         <f>IF(D24="",NA(),K24)</f>
         <v/>
       </c>
-      <c r="Q24" s="649">
+      <c r="Q24" s="650">
         <f>IF(D24="",NA(),L24)</f>
         <v/>
       </c>
-      <c r="R24" s="645">
+      <c r="R24" s="646">
         <f>IFERROR(IF(D24=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E24=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F24=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G24=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
       <c r="S24" s="221" t="n"/>
-      <c r="T24" s="645">
+      <c r="T24" s="646">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="U24" s="645">
+      <c r="U24" s="646">
         <f>NA()</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="141">
-      <c r="A25" s="639">
+      <c r="A25" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B24,IF('Load Log'!B23="","",'Load Log'!B23)),"")</f>
         <v/>
       </c>
-      <c r="B25" s="639">
+      <c r="B25" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B23,""),"")</f>
         <v/>
       </c>
-      <c r="C25" s="639">
+      <c r="C25" s="640">
         <f>IFERROR(IF($B$100="window",'Load Log'!B25,""),"")</f>
         <v/>
       </c>
-      <c r="D25" s="640">
+      <c r="D25" s="641">
         <f>IF($B$100="window",IF(OR(A25="",B25="",C25=""),"",MAX('Load Log'!H23:H25)-MIN('Load Log'!H23:H25)),IF('Load Log'!H23="","",'Load Log'!H23))</f>
         <v/>
       </c>
-      <c r="E25" s="639">
+      <c r="E25" s="640">
         <f>IF($B$100="window",IF(OR(A25="",B25="",C25=""),"",'Load Log'!J24),IF('Load Log'!J23="","",'Load Log'!J23))</f>
         <v/>
       </c>
-      <c r="F25" s="641">
+      <c r="F25" s="642">
         <f>IF($B$100="window",IF(OR(A25="",B25="",C25=""),"",IFERROR(IF('Load Log'!N24="",'Load Log'!K24,'Load Log'!N24)/('Load Log'!$L$10/100)/1.047,"")),IFERROR(IF('Load Log'!N23="",'Load Log'!K23,'Load Log'!N23)/('Load Log'!$L$10/100)/1.047,""))</f>
         <v/>
       </c>
-      <c r="G25" s="641">
+      <c r="G25" s="642">
         <f>IF($B$100="window",IF(OR(A25="",B25="",C25=""),"",IF('Load Log'!M24="",IF('Load Log'!L24="",F25,'Load Log'!L24/('Load Log'!$L$10/100)/1.047),'Load Log'!M24/('Load Log'!$L$10/100)/1.047)),IF('Load Log'!M23="",IF('Load Log'!L23="",F25,'Load Log'!L23/('Load Log'!$L$10/100)/1.047),'Load Log'!M23/('Load Log'!$L$10/100)/1.047))</f>
         <v/>
       </c>
-      <c r="H25" s="642">
+      <c r="H25" s="643">
         <f>IF(D25="","",IFERROR((D25-AGGREGATE(5,6,$D$18:$D$25))/(AGGREGATE(4,6,$D$18:$D$25)-AGGREGATE(5,6,$D$18:$D$25)),0))</f>
         <v/>
       </c>
-      <c r="I25" s="642">
+      <c r="I25" s="643">
         <f>IF(E25="","",IFERROR((E25-AGGREGATE(5,6,$E$18:$E$25))/(AGGREGATE(4,6,$E$18:$E$25)-AGGREGATE(5,6,$E$18:$E$25)),0))</f>
         <v/>
       </c>
-      <c r="J25" s="642">
+      <c r="J25" s="643">
         <f>IF(F25="","",IFERROR((F25-AGGREGATE(5,6,$F$18:$F$25))/(AGGREGATE(4,6,$F$18:$F$25)-AGGREGATE(5,6,$F$18:$F$25)),0))</f>
         <v/>
       </c>
-      <c r="K25" s="642">
+      <c r="K25" s="643">
         <f>IF(G25="","",IFERROR((G25-AGGREGATE(5,6,$G$18:$G$25))/(AGGREGATE(4,6,$G$18:$G$25)-AGGREGATE(5,6,$G$18:$G$25)),0))</f>
         <v/>
       </c>
-      <c r="L25" s="642">
+      <c r="L25" s="643">
         <f>IF(A25="","",H25*$B$11+I25*$D$11+J25*$F$11+K25*$H$11)</f>
         <v/>
       </c>
-      <c r="M25" s="643">
+      <c r="M25" s="644">
         <f>IF(D25="",NA(),H25)</f>
         <v/>
       </c>
-      <c r="N25" s="644">
+      <c r="N25" s="645">
         <f>IF(D25="",NA(),I25)</f>
         <v/>
       </c>
-      <c r="O25" s="644">
+      <c r="O25" s="645">
         <f>IF(D25="",NA(),J25)</f>
         <v/>
       </c>
-      <c r="P25" s="644">
+      <c r="P25" s="645">
         <f>IF(D25="",NA(),K25)</f>
         <v/>
       </c>
-      <c r="Q25" s="644">
+      <c r="Q25" s="645">
         <f>IF(D25="",NA(),L25)</f>
         <v/>
       </c>
-      <c r="R25" s="645">
+      <c r="R25" s="646">
         <f>IFERROR(IF(D25=AGGREGATE(5,6,$D$18:$D$25),"Vel ✓ ","")&amp;IF(E25=AGGREGATE(5,6,$E$18:$E$25),"SD ✓ ","")&amp;IF(F25=AGGREGATE(5,6,$F$18:$F$25),"MR ✓ ","")&amp;IF(G25=AGGREGATE(5,6,$G$18:$G$25),"Vert ✓ ",""),"")</f>
         <v/>
       </c>
-      <c r="T25" s="645">
+      <c r="T25" s="646">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="U25" s="645">
+      <c r="U25" s="646">
         <f>NA()</f>
         <v/>
       </c>
@@ -14978,6 +14987,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" display="Save Suggested Load to Library" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" display="Click to reset to Loadscope defaults" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId3"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
@@ -14990,7 +15000,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -15085,7 +15095,7 @@
       <c r="L2" s="598" t="n">
         <v>0.16</v>
       </c>
-      <c r="M2" s="650" t="inlineStr">
+      <c r="M2" s="651" t="inlineStr">
         <is>
           <t>Vert:</t>
         </is>
@@ -15794,7 +15804,7 @@
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S1"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C16" s="651">
+      <c r="C16" s="652">
         <f>IFERROR($G$10-B16,"")</f>
         <v/>
       </c>
@@ -15822,7 +15832,7 @@
         <f>IF(OR('Garmin Xero Import'!O17="",'Garmin Xero Import'!O17=0),"",'Garmin Xero Import'!O17)</f>
         <v/>
       </c>
-      <c r="J16" s="652">
+      <c r="J16" s="653">
         <f>IF(OR('Garmin Xero Import'!Q17="",'Garmin Xero Import'!Q17=0),"",'Garmin Xero Import'!Q17)</f>
         <v/>
       </c>
@@ -15873,11 +15883,11 @@
       <c r="A17" s="612" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="653">
+      <c r="B17" s="654">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S2"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C17" s="654">
+      <c r="C17" s="655">
         <f>IFERROR($G$10-B17,"")</f>
         <v/>
       </c>
@@ -15905,7 +15915,7 @@
         <f>IF(OR('Garmin Xero Import'!O18="",'Garmin Xero Import'!O18=0),"",'Garmin Xero Import'!O18)</f>
         <v/>
       </c>
-      <c r="J17" s="655">
+      <c r="J17" s="656">
         <f>IF(OR('Garmin Xero Import'!Q18="",'Garmin Xero Import'!Q18=0),"",'Garmin Xero Import'!Q18)</f>
         <v/>
       </c>
@@ -15964,7 +15974,7 @@
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S3"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C18" s="651">
+      <c r="C18" s="652">
         <f>IFERROR($G$10-B18,"")</f>
         <v/>
       </c>
@@ -15992,7 +16002,7 @@
         <f>IF(OR('Garmin Xero Import'!O19="",'Garmin Xero Import'!O19=0),"",'Garmin Xero Import'!O19)</f>
         <v/>
       </c>
-      <c r="J18" s="652">
+      <c r="J18" s="653">
         <f>IF(OR('Garmin Xero Import'!Q19="",'Garmin Xero Import'!Q19=0),"",'Garmin Xero Import'!Q19)</f>
         <v/>
       </c>
@@ -16047,11 +16057,11 @@
       <c r="A19" s="612" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="653">
+      <c r="B19" s="654">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S4"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C19" s="654">
+      <c r="C19" s="655">
         <f>IFERROR($G$10-B19,"")</f>
         <v/>
       </c>
@@ -16079,7 +16089,7 @@
         <f>IF(OR('Garmin Xero Import'!O20="",'Garmin Xero Import'!O20=0),"",'Garmin Xero Import'!O20)</f>
         <v/>
       </c>
-      <c r="J19" s="655">
+      <c r="J19" s="656">
         <f>IF(OR('Garmin Xero Import'!Q20="",'Garmin Xero Import'!Q20=0),"",'Garmin Xero Import'!Q20)</f>
         <v/>
       </c>
@@ -16138,7 +16148,7 @@
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S5"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C20" s="651">
+      <c r="C20" s="652">
         <f>IFERROR($G$10-B20,"")</f>
         <v/>
       </c>
@@ -16166,7 +16176,7 @@
         <f>IF(OR('Garmin Xero Import'!O21="",'Garmin Xero Import'!O21=0),"",'Garmin Xero Import'!O21)</f>
         <v/>
       </c>
-      <c r="J20" s="652">
+      <c r="J20" s="653">
         <f>IF(OR('Garmin Xero Import'!Q21="",'Garmin Xero Import'!Q21=0),"",'Garmin Xero Import'!Q21)</f>
         <v/>
       </c>
@@ -16217,11 +16227,11 @@
       <c r="A21" s="612" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="653">
+      <c r="B21" s="654">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S6"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C21" s="654">
+      <c r="C21" s="655">
         <f>IFERROR($G$10-B21,"")</f>
         <v/>
       </c>
@@ -16249,7 +16259,7 @@
         <f>IF(OR('Garmin Xero Import'!O22="",'Garmin Xero Import'!O22=0),"",'Garmin Xero Import'!O22)</f>
         <v/>
       </c>
-      <c r="J21" s="655">
+      <c r="J21" s="656">
         <f>IF(OR('Garmin Xero Import'!Q22="",'Garmin Xero Import'!Q22=0),"",'Garmin Xero Import'!Q22)</f>
         <v/>
       </c>
@@ -16305,7 +16315,7 @@
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S7"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C22" s="651">
+      <c r="C22" s="652">
         <f>IFERROR($G$10-B22,"")</f>
         <v/>
       </c>
@@ -16333,7 +16343,7 @@
         <f>IF(OR('Garmin Xero Import'!O23="",'Garmin Xero Import'!O23=0),"",'Garmin Xero Import'!O23)</f>
         <v/>
       </c>
-      <c r="J22" s="652">
+      <c r="J22" s="653">
         <f>IF(OR('Garmin Xero Import'!Q23="",'Garmin Xero Import'!Q23=0),"",'Garmin Xero Import'!Q23)</f>
         <v/>
       </c>
@@ -16385,11 +16395,11 @@
       <c r="A23" s="612" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="653">
+      <c r="B23" s="654">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S8"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C23" s="654">
+      <c r="C23" s="655">
         <f>IFERROR($G$10-B23,"")</f>
         <v/>
       </c>
@@ -16417,7 +16427,7 @@
         <f>IF(OR('Garmin Xero Import'!O24="",'Garmin Xero Import'!O24=0),"",'Garmin Xero Import'!O24)</f>
         <v/>
       </c>
-      <c r="J23" s="655">
+      <c r="J23" s="656">
         <f>IF(OR('Garmin Xero Import'!Q24="",'Garmin Xero Import'!Q24=0),"",'Garmin Xero Import'!Q24)</f>
         <v/>
       </c>
@@ -16473,7 +16483,7 @@
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S9"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C24" s="651">
+      <c r="C24" s="652">
         <f>IFERROR($G$10-B24,"")</f>
         <v/>
       </c>
@@ -16501,7 +16511,7 @@
         <f>IF(OR('Garmin Xero Import'!O25="",'Garmin Xero Import'!O25=0),"",'Garmin Xero Import'!O25)</f>
         <v/>
       </c>
-      <c r="J24" s="652">
+      <c r="J24" s="653">
         <f>IF(OR('Garmin Xero Import'!Q25="",'Garmin Xero Import'!Q25=0),"",'Garmin Xero Import'!Q25)</f>
         <v/>
       </c>
@@ -16553,11 +16563,11 @@
       <c r="A25" s="612" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="653">
+      <c r="B25" s="654">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200="S10"),GarminSessions!$B$2:$B$200),NA())</f>
         <v/>
       </c>
-      <c r="C25" s="654">
+      <c r="C25" s="655">
         <f>IFERROR($G$10-B25,"")</f>
         <v/>
       </c>
@@ -16585,7 +16595,7 @@
         <f>IF(OR('Garmin Xero Import'!O26="",'Garmin Xero Import'!O26=0),"",'Garmin Xero Import'!O26)</f>
         <v/>
       </c>
-      <c r="J25" s="655">
+      <c r="J25" s="656">
         <f>IF(OR('Garmin Xero Import'!Q26="",'Garmin Xero Import'!Q26=0),"",'Garmin Xero Import'!Q26)</f>
         <v/>
       </c>
@@ -16707,57 +16717,57 @@
       <c r="AL27" s="155" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1" s="141">
-      <c r="A28" s="656" t="inlineStr">
+      <c r="A28" s="657" t="inlineStr">
         <is>
           <t>Reset weights</t>
         </is>
       </c>
-      <c r="B28" s="657" t="inlineStr">
+      <c r="B28" s="658" t="inlineStr">
         <is>
           <t>Velocity</t>
         </is>
       </c>
-      <c r="C28" s="658" t="n">
+      <c r="C28" s="659" t="n">
         <v>0.15</v>
       </c>
-      <c r="D28" s="659" t="n"/>
-      <c r="E28" s="657" t="inlineStr">
+      <c r="D28" s="660" t="n"/>
+      <c r="E28" s="658" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="F28" s="658" t="n">
+      <c r="F28" s="659" t="n">
         <v>0.25</v>
       </c>
-      <c r="G28" s="659" t="n"/>
-      <c r="H28" s="657" t="inlineStr">
+      <c r="G28" s="660" t="n"/>
+      <c r="H28" s="658" t="inlineStr">
         <is>
           <t>MR</t>
         </is>
       </c>
-      <c r="I28" s="658" t="n">
+      <c r="I28" s="659" t="n">
         <v>0.25</v>
       </c>
-      <c r="J28" s="659" t="n"/>
-      <c r="K28" s="657" t="inlineStr">
+      <c r="J28" s="660" t="n"/>
+      <c r="K28" s="658" t="inlineStr">
         <is>
           <t>SD-Vert</t>
         </is>
       </c>
-      <c r="L28" s="658" t="n">
+      <c r="L28" s="659" t="n">
         <v>0.35</v>
       </c>
-      <c r="M28" s="659" t="n"/>
-      <c r="N28" s="657" t="inlineStr">
+      <c r="M28" s="660" t="n"/>
+      <c r="N28" s="658" t="inlineStr">
         <is>
           <t>Sum:</t>
         </is>
       </c>
-      <c r="O28" s="660">
+      <c r="O28" s="661">
         <f>SUM(C28,F28,I28,L28)</f>
         <v/>
       </c>
-      <c r="P28" s="659" t="n"/>
+      <c r="P28" s="660" t="n"/>
       <c r="Q28" s="155" t="n"/>
       <c r="R28" s="155" t="n"/>
       <c r="S28" s="155" t="n"/>
@@ -16782,70 +16792,70 @@
       <c r="AL28" s="155" t="n"/>
     </row>
     <row r="29" ht="42" customHeight="1" s="141">
-      <c r="A29" s="661" t="inlineStr">
+      <c r="A29" s="662" t="inlineStr">
         <is>
           <t>Jump</t>
         </is>
       </c>
-      <c r="B29" s="661" t="n"/>
-      <c r="C29" s="661" t="n"/>
-      <c r="D29" s="661" t="inlineStr">
+      <c r="B29" s="662" t="n"/>
+      <c r="C29" s="662" t="n"/>
+      <c r="D29" s="662" t="inlineStr">
         <is>
           <t>Avg Vel (fps)</t>
         </is>
       </c>
-      <c r="E29" s="661" t="inlineStr">
+      <c r="E29" s="662" t="inlineStr">
         <is>
           <t>SD (fps)</t>
         </is>
       </c>
-      <c r="F29" s="661" t="inlineStr">
+      <c r="F29" s="662" t="inlineStr">
         <is>
           <t>Mean Radius (MOA)</t>
         </is>
       </c>
-      <c r="G29" s="661" t="inlineStr">
+      <c r="G29" s="662" t="inlineStr">
         <is>
           <t>SD-Vert (MOA)</t>
         </is>
       </c>
-      <c r="H29" s="661" t="inlineStr">
+      <c r="H29" s="662" t="inlineStr">
         <is>
           <t>Norm Vel</t>
         </is>
       </c>
-      <c r="I29" s="661" t="inlineStr">
+      <c r="I29" s="662" t="inlineStr">
         <is>
           <t>Norm SD</t>
         </is>
       </c>
-      <c r="J29" s="661" t="inlineStr">
+      <c r="J29" s="662" t="inlineStr">
         <is>
           <t>Norm MR</t>
         </is>
       </c>
-      <c r="K29" s="661" t="inlineStr">
+      <c r="K29" s="662" t="inlineStr">
         <is>
           <t>Norm SD-Vert</t>
         </is>
       </c>
-      <c r="L29" s="661" t="inlineStr">
+      <c r="L29" s="662" t="inlineStr">
         <is>
           <t>Composite Score</t>
         </is>
       </c>
-      <c r="M29" s="661" t="inlineStr">
+      <c r="M29" s="662" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="N29" s="661" t="inlineStr">
+      <c r="N29" s="662" t="inlineStr">
         <is>
           <t>Best in</t>
         </is>
       </c>
       <c r="O29" s="176" t="n"/>
-      <c r="P29" s="662" t="n"/>
+      <c r="P29" s="663" t="n"/>
       <c r="Q29" s="155" t="n"/>
       <c r="R29" s="155" t="n"/>
       <c r="S29" s="155" t="n"/>
@@ -16870,44 +16880,44 @@
       <c r="AL29" s="155" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" s="141">
-      <c r="A30" s="663" t="n">
+      <c r="A30" s="664" t="n">
         <v>0.005</v>
       </c>
       <c r="B30" s="451" t="n"/>
       <c r="C30" s="451" t="n"/>
-      <c r="D30" s="664" t="n">
+      <c r="D30" s="665" t="n">
         <v>2781</v>
       </c>
-      <c r="E30" s="665" t="n">
+      <c r="E30" s="666" t="n">
         <v>2.2</v>
       </c>
-      <c r="F30" s="666" t="n">
+      <c r="F30" s="667" t="n">
         <v>0.27</v>
       </c>
-      <c r="G30" s="666" t="n">
+      <c r="G30" s="667" t="n">
         <v>0.17</v>
       </c>
-      <c r="H30" s="663" t="n">
+      <c r="H30" s="664" t="n">
         <v>0.767</v>
       </c>
-      <c r="I30" s="663" t="n">
+      <c r="I30" s="664" t="n">
         <v>0.326</v>
       </c>
-      <c r="J30" s="663" t="n">
+      <c r="J30" s="664" t="n">
         <v>0.733</v>
       </c>
-      <c r="K30" s="663" t="n">
+      <c r="K30" s="664" t="n">
         <v>0.778</v>
       </c>
-      <c r="L30" s="663" t="n">
+      <c r="L30" s="664" t="n">
         <v>0.652</v>
       </c>
-      <c r="M30" s="664" t="n">
+      <c r="M30" s="665" t="n">
         <v>4</v>
       </c>
-      <c r="N30" s="667" t="inlineStr"/>
+      <c r="N30" s="668" t="inlineStr"/>
       <c r="O30" s="233" t="n"/>
-      <c r="P30" s="659" t="n"/>
+      <c r="P30" s="660" t="n"/>
       <c r="Q30" s="155" t="n"/>
       <c r="R30" s="155" t="n"/>
       <c r="S30" s="155" t="n"/>
@@ -16932,44 +16942,44 @@
       <c r="AL30" s="155" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" s="141">
-      <c r="A31" s="668" t="n">
+      <c r="A31" s="669" t="n">
         <v>0.02</v>
       </c>
       <c r="B31" s="453" t="n"/>
       <c r="C31" s="453" t="n"/>
-      <c r="D31" s="669" t="n">
+      <c r="D31" s="670" t="n">
         <v>2780</v>
       </c>
-      <c r="E31" s="670" t="n">
+      <c r="E31" s="671" t="n">
         <v>2.4</v>
       </c>
-      <c r="F31" s="671" t="n">
+      <c r="F31" s="672" t="n">
         <v>0.21</v>
       </c>
-      <c r="G31" s="671" t="n">
+      <c r="G31" s="672" t="n">
         <v>0.13</v>
       </c>
-      <c r="H31" s="668" t="n">
+      <c r="H31" s="669" t="n">
         <v>0.3</v>
       </c>
-      <c r="I31" s="668" t="n">
+      <c r="I31" s="669" t="n">
         <v>0.372</v>
       </c>
-      <c r="J31" s="668" t="n">
+      <c r="J31" s="669" t="n">
         <v>0.333</v>
       </c>
-      <c r="K31" s="668" t="n">
+      <c r="K31" s="669" t="n">
         <v>0.333</v>
       </c>
-      <c r="L31" s="668" t="n">
+      <c r="L31" s="669" t="n">
         <v>0.338</v>
       </c>
-      <c r="M31" s="669" t="n">
+      <c r="M31" s="670" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="672" t="inlineStr"/>
+      <c r="N31" s="673" t="inlineStr"/>
       <c r="O31" s="236" t="n"/>
-      <c r="P31" s="673" t="n"/>
+      <c r="P31" s="674" t="n"/>
       <c r="Q31" s="155" t="n"/>
       <c r="R31" s="155" t="n"/>
       <c r="S31" s="155" t="n"/>
@@ -16994,48 +17004,48 @@
       <c r="AL31" s="155" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" s="141">
-      <c r="A32" s="663" t="n">
+      <c r="A32" s="664" t="n">
         <v>0.035</v>
       </c>
       <c r="B32" s="451" t="n"/>
       <c r="C32" s="451" t="n"/>
-      <c r="D32" s="664" t="n">
+      <c r="D32" s="665" t="n">
         <v>2780.6</v>
       </c>
-      <c r="E32" s="665" t="n">
+      <c r="E32" s="666" t="n">
         <v>0.8</v>
       </c>
-      <c r="F32" s="666" t="n">
+      <c r="F32" s="667" t="n">
         <v>0.16</v>
       </c>
-      <c r="G32" s="666" t="n">
+      <c r="G32" s="667" t="n">
         <v>0.1</v>
       </c>
-      <c r="H32" s="663" t="n">
+      <c r="H32" s="664" t="n">
         <v>0.001</v>
       </c>
-      <c r="I32" s="663" t="n">
+      <c r="I32" s="664" t="n">
         <v>0.001</v>
       </c>
-      <c r="J32" s="663" t="n">
+      <c r="J32" s="664" t="n">
         <v>0.001</v>
       </c>
-      <c r="K32" s="663" t="n">
+      <c r="K32" s="664" t="n">
         <v>0.001</v>
       </c>
-      <c r="L32" s="663" t="n">
+      <c r="L32" s="664" t="n">
         <v>0.001</v>
       </c>
-      <c r="M32" s="664" t="n">
+      <c r="M32" s="665" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="667" t="inlineStr">
+      <c r="N32" s="668" t="inlineStr">
         <is>
           <t>All metrics ✓</t>
         </is>
       </c>
       <c r="O32" s="233" t="n"/>
-      <c r="P32" s="659" t="n"/>
+      <c r="P32" s="660" t="n"/>
       <c r="Q32" s="155" t="n"/>
       <c r="R32" s="155" t="n"/>
       <c r="S32" s="155" t="n"/>
@@ -17060,44 +17070,44 @@
       <c r="AL32" s="155" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" s="141">
-      <c r="A33" s="668" t="n">
+      <c r="A33" s="669" t="n">
         <v>0.05</v>
       </c>
       <c r="B33" s="453" t="n"/>
       <c r="C33" s="453" t="n"/>
-      <c r="D33" s="669" t="n">
+      <c r="D33" s="670" t="n">
         <v>2780</v>
       </c>
-      <c r="E33" s="670" t="n">
+      <c r="E33" s="671" t="n">
         <v>3.4</v>
       </c>
-      <c r="F33" s="671" t="n">
+      <c r="F33" s="672" t="n">
         <v>0.24</v>
       </c>
-      <c r="G33" s="671" t="n">
+      <c r="G33" s="672" t="n">
         <v>0.15</v>
       </c>
-      <c r="H33" s="668" t="n">
+      <c r="H33" s="669" t="n">
         <v>0.533</v>
       </c>
-      <c r="I33" s="668" t="n">
+      <c r="I33" s="669" t="n">
         <v>0.605</v>
       </c>
-      <c r="J33" s="668" t="n">
+      <c r="J33" s="669" t="n">
         <v>0.533</v>
       </c>
-      <c r="K33" s="668" t="n">
+      <c r="K33" s="669" t="n">
         <v>0.556</v>
       </c>
-      <c r="L33" s="668" t="n">
+      <c r="L33" s="669" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="M33" s="669" t="n">
+      <c r="M33" s="670" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="672" t="inlineStr"/>
+      <c r="N33" s="673" t="inlineStr"/>
       <c r="O33" s="236" t="n"/>
-      <c r="P33" s="673" t="n"/>
+      <c r="P33" s="674" t="n"/>
       <c r="Q33" s="155" t="n"/>
       <c r="R33" s="155" t="n"/>
       <c r="S33" s="155" t="n"/>
@@ -17122,44 +17132,44 @@
       <c r="AL33" s="155" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" s="141">
-      <c r="A34" s="663" t="n">
+      <c r="A34" s="664" t="n">
         <v>0.065</v>
       </c>
       <c r="B34" s="451" t="n"/>
       <c r="C34" s="451" t="n"/>
-      <c r="D34" s="664" t="n">
+      <c r="D34" s="665" t="n">
         <v>2780</v>
       </c>
-      <c r="E34" s="665" t="n">
+      <c r="E34" s="666" t="n">
         <v>5.1</v>
       </c>
-      <c r="F34" s="666" t="n">
+      <c r="F34" s="667" t="n">
         <v>0.31</v>
       </c>
-      <c r="G34" s="666" t="n">
+      <c r="G34" s="667" t="n">
         <v>0.19</v>
       </c>
-      <c r="H34" s="663" t="n">
+      <c r="H34" s="664" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="663" t="n">
+      <c r="I34" s="664" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="663" t="n">
+      <c r="J34" s="664" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="663" t="n">
+      <c r="K34" s="664" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="663" t="n">
+      <c r="L34" s="664" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="664" t="n">
+      <c r="M34" s="665" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="667" t="inlineStr"/>
+      <c r="N34" s="668" t="inlineStr"/>
       <c r="O34" s="233" t="n"/>
-      <c r="P34" s="659" t="n"/>
+      <c r="P34" s="660" t="n"/>
       <c r="Q34" s="155" t="n"/>
       <c r="R34" s="155" t="n"/>
       <c r="S34" s="155" t="n"/>
@@ -17184,64 +17194,64 @@
       <c r="AL34" s="155" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" s="141">
-      <c r="A35" s="668">
+      <c r="A35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="B35" s="668">
+      <c r="B35" s="669">
         <f>IFERROR(IF($B$100="window",B21,""),"")</f>
         <v/>
       </c>
-      <c r="C35" s="668">
+      <c r="C35" s="669">
         <f>IFERROR(IF($B$100="window",B23,""),"")</f>
         <v/>
       </c>
-      <c r="D35" s="669">
+      <c r="D35" s="670">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="E35" s="670">
+      <c r="E35" s="671">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="F35" s="671">
+      <c r="F35" s="672">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="G35" s="671">
+      <c r="G35" s="672">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="H35" s="668">
+      <c r="H35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="I35" s="668">
+      <c r="I35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="J35" s="668">
+      <c r="J35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="K35" s="668">
+      <c r="K35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="L35" s="668">
+      <c r="L35" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="M35" s="669">
+      <c r="M35" s="670">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="N35" s="674">
+      <c r="N35" s="675">
         <f>NA()</f>
         <v/>
       </c>
       <c r="O35" s="236" t="n"/>
-      <c r="P35" s="673" t="n"/>
+      <c r="P35" s="674" t="n"/>
       <c r="Q35" s="155" t="n"/>
       <c r="R35" s="155" t="n"/>
       <c r="S35" s="155" t="n"/>
@@ -17266,64 +17276,64 @@
       <c r="AL35" s="155" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" s="141">
-      <c r="A36" s="663">
+      <c r="A36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="B36" s="663">
+      <c r="B36" s="664">
         <f>IFERROR(IF($B$100="window",B22,""),"")</f>
         <v/>
       </c>
-      <c r="C36" s="663">
+      <c r="C36" s="664">
         <f>IFERROR(IF($B$100="window",B24,""),"")</f>
         <v/>
       </c>
-      <c r="D36" s="664">
+      <c r="D36" s="665">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="E36" s="665">
+      <c r="E36" s="666">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="F36" s="666">
+      <c r="F36" s="667">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="G36" s="666">
+      <c r="G36" s="667">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="H36" s="663">
+      <c r="H36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="I36" s="663">
+      <c r="I36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="J36" s="663">
+      <c r="J36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="K36" s="663">
+      <c r="K36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="L36" s="663">
+      <c r="L36" s="664">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="M36" s="664">
+      <c r="M36" s="665">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="N36" s="675">
+      <c r="N36" s="676">
         <f>NA()</f>
         <v/>
       </c>
       <c r="O36" s="233" t="n"/>
-      <c r="P36" s="659" t="n"/>
+      <c r="P36" s="660" t="n"/>
       <c r="Q36" s="155" t="n"/>
       <c r="R36" s="155" t="n"/>
       <c r="S36" s="155" t="n"/>
@@ -17348,64 +17358,64 @@
       <c r="AL36" s="155" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" s="141">
-      <c r="A37" s="668">
+      <c r="A37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="B37" s="668">
+      <c r="B37" s="669">
         <f>IFERROR(IF($B$100="window",B23,""),"")</f>
         <v/>
       </c>
-      <c r="C37" s="668">
+      <c r="C37" s="669">
         <f>IFERROR(IF($B$100="window",B25,""),"")</f>
         <v/>
       </c>
-      <c r="D37" s="669">
+      <c r="D37" s="670">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="E37" s="670">
+      <c r="E37" s="671">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="F37" s="671">
+      <c r="F37" s="672">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="G37" s="671">
+      <c r="G37" s="672">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="H37" s="668">
+      <c r="H37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="I37" s="668">
+      <c r="I37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="J37" s="668">
+      <c r="J37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="K37" s="668">
+      <c r="K37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="L37" s="668">
+      <c r="L37" s="669">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="M37" s="669">
+      <c r="M37" s="670">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="N37" s="674">
+      <c r="N37" s="675">
         <f>NA()</f>
         <v/>
       </c>
       <c r="O37" s="236" t="n"/>
-      <c r="P37" s="673" t="n"/>
+      <c r="P37" s="674" t="n"/>
       <c r="Q37" s="155" t="n"/>
       <c r="R37" s="155" t="n"/>
       <c r="S37" s="155" t="n"/>
@@ -18784,7 +18794,7 @@
           <t>Mode:</t>
         </is>
       </c>
-      <c r="B100" s="676">
+      <c r="B100" s="677">
         <f>IF(COUNT(B16:B25)&gt;=5,"window","test")</f>
         <v/>
       </c>
@@ -19977,7 +19987,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" s="141">
-      <c r="A3" s="677" t="inlineStr">
+      <c r="A3" s="678" t="inlineStr">
         <is>
           <t>POWDER LADDER  (Load Log P1–P10  →  rows 6–15)</t>
         </is>
@@ -20004,939 +20014,939 @@
     </row>
     <row r="4" ht="6" customHeight="1" s="141"/>
     <row r="5" ht="32" customHeight="1" s="141">
-      <c r="A5" s="678" t="inlineStr">
+      <c r="A5" s="679" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="B5" s="678" t="inlineStr">
+      <c r="B5" s="679" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C5" s="678" t="inlineStr">
+      <c r="C5" s="679" t="inlineStr">
         <is>
           <t>Session Title</t>
         </is>
       </c>
-      <c r="D5" s="678" t="inlineStr">
+      <c r="D5" s="679" t="inlineStr">
         <is>
           <t># Shots</t>
         </is>
       </c>
-      <c r="E5" s="678" t="inlineStr">
+      <c r="E5" s="679" t="inlineStr">
         <is>
           <t>Shot 1 (fps)</t>
         </is>
       </c>
-      <c r="F5" s="678" t="inlineStr">
+      <c r="F5" s="679" t="inlineStr">
         <is>
           <t>Shot 2 (fps)</t>
         </is>
       </c>
-      <c r="G5" s="678" t="inlineStr">
+      <c r="G5" s="679" t="inlineStr">
         <is>
           <t>Shot 3 (fps)</t>
         </is>
       </c>
-      <c r="H5" s="678" t="inlineStr">
+      <c r="H5" s="679" t="inlineStr">
         <is>
           <t>Shot 4 (fps)</t>
         </is>
       </c>
-      <c r="I5" s="678" t="inlineStr">
+      <c r="I5" s="679" t="inlineStr">
         <is>
           <t>Shot 5 (fps)</t>
         </is>
       </c>
-      <c r="J5" s="678" t="inlineStr">
+      <c r="J5" s="679" t="inlineStr">
         <is>
           <t>Shot 6 (fps)</t>
         </is>
       </c>
-      <c r="K5" s="678" t="inlineStr">
+      <c r="K5" s="679" t="inlineStr">
         <is>
           <t>Shot 7 (fps)</t>
         </is>
       </c>
-      <c r="L5" s="679" t="inlineStr">
+      <c r="L5" s="680" t="inlineStr">
         <is>
           <t>Shot 8 (fps)</t>
         </is>
       </c>
-      <c r="M5" s="679" t="inlineStr">
+      <c r="M5" s="680" t="inlineStr">
         <is>
           <t>Shot 9 (fps)</t>
         </is>
       </c>
-      <c r="N5" s="679" t="inlineStr">
+      <c r="N5" s="680" t="inlineStr">
         <is>
           <t>Shot 10 (fps)</t>
         </is>
       </c>
-      <c r="O5" s="679" t="inlineStr">
+      <c r="O5" s="680" t="inlineStr">
         <is>
           <t>Avg Vel (fps)</t>
         </is>
       </c>
-      <c r="P5" s="679" t="inlineStr">
+      <c r="P5" s="680" t="inlineStr">
         <is>
           <t>SD (fps)</t>
         </is>
       </c>
-      <c r="Q5" s="679" t="inlineStr">
+      <c r="Q5" s="680" t="inlineStr">
         <is>
           <t>ES (fps)</t>
         </is>
       </c>
-      <c r="R5" s="679" t="inlineStr">
+      <c r="R5" s="680" t="inlineStr">
         <is>
           <t>Bullet Wt (gr)</t>
         </is>
       </c>
-      <c r="S5" s="679" t="inlineStr">
+      <c r="S5" s="680" t="inlineStr">
         <is>
           <t>Avg KE (ft·lb)</t>
         </is>
       </c>
-      <c r="T5" s="679" t="inlineStr">
+      <c r="T5" s="680" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" s="141">
-      <c r="A6" s="680" t="inlineStr">
+      <c r="A6" s="681" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B6" s="681">
+      <c r="B6" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C6" s="682">
+      <c r="C6" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D6" s="683">
+      <c r="D6" s="684">
         <f>COUNT(E6:N6)</f>
         <v/>
       </c>
-      <c r="E6" s="684">
+      <c r="E6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F6" s="684">
+      <c r="F6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G6" s="684">
+      <c r="G6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H6" s="684">
+      <c r="H6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I6" s="684">
+      <c r="I6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J6" s="684">
+      <c r="J6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K6" s="684">
+      <c r="K6" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L6" s="683">
+      <c r="L6" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M6" s="683">
+      <c r="M6" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N6" s="683">
+      <c r="N6" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O6" s="685">
+      <c r="O6" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P6" s="681">
+      <c r="P6" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q6" s="685">
+      <c r="Q6" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R6" s="681">
+      <c r="R6" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S6" s="681">
+      <c r="S6" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T6" s="682">
+      <c r="T6" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A6),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" s="141">
-      <c r="A7" s="686" t="inlineStr">
+      <c r="A7" s="687" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B7" s="687">
+      <c r="B7" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C7" s="688">
+      <c r="C7" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="689">
+      <c r="D7" s="690">
         <f>COUNT(E7:N7)</f>
         <v/>
       </c>
-      <c r="E7" s="690">
+      <c r="E7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F7" s="690">
+      <c r="F7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G7" s="690">
+      <c r="G7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H7" s="690">
+      <c r="H7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I7" s="690">
+      <c r="I7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J7" s="690">
+      <c r="J7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K7" s="690">
+      <c r="K7" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L7" s="687">
+      <c r="L7" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M7" s="687">
+      <c r="M7" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N7" s="687">
+      <c r="N7" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O7" s="690">
+      <c r="O7" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P7" s="687">
+      <c r="P7" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q7" s="690">
+      <c r="Q7" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R7" s="687">
+      <c r="R7" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S7" s="687">
+      <c r="S7" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T7" s="688">
+      <c r="T7" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A7),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" s="141">
-      <c r="A8" s="680" t="inlineStr">
+      <c r="A8" s="681" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B8" s="681">
+      <c r="B8" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C8" s="682">
+      <c r="C8" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="683">
+      <c r="D8" s="684">
         <f>COUNT(E8:N8)</f>
         <v/>
       </c>
-      <c r="E8" s="684">
+      <c r="E8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F8" s="684">
+      <c r="F8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G8" s="684">
+      <c r="G8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H8" s="684">
+      <c r="H8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I8" s="684">
+      <c r="I8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J8" s="684">
+      <c r="J8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K8" s="684">
+      <c r="K8" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L8" s="683">
+      <c r="L8" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M8" s="683">
+      <c r="M8" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N8" s="683">
+      <c r="N8" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O8" s="685">
+      <c r="O8" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P8" s="681">
+      <c r="P8" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q8" s="685">
+      <c r="Q8" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R8" s="681">
+      <c r="R8" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S8" s="681">
+      <c r="S8" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T8" s="682">
+      <c r="T8" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A8),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" s="141">
-      <c r="A9" s="686" t="inlineStr">
+      <c r="A9" s="687" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B9" s="687">
+      <c r="B9" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C9" s="688">
+      <c r="C9" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="689">
+      <c r="D9" s="690">
         <f>COUNT(E9:N9)</f>
         <v/>
       </c>
-      <c r="E9" s="690">
+      <c r="E9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F9" s="690">
+      <c r="F9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G9" s="690">
+      <c r="G9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H9" s="690">
+      <c r="H9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I9" s="690">
+      <c r="I9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J9" s="690">
+      <c r="J9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K9" s="690">
+      <c r="K9" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L9" s="687">
+      <c r="L9" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M9" s="687">
+      <c r="M9" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N9" s="687">
+      <c r="N9" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O9" s="690">
+      <c r="O9" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P9" s="687">
+      <c r="P9" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q9" s="690">
+      <c r="Q9" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R9" s="687">
+      <c r="R9" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S9" s="687">
+      <c r="S9" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T9" s="688">
+      <c r="T9" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A9),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" s="141">
-      <c r="A10" s="680" t="inlineStr">
+      <c r="A10" s="681" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B10" s="681">
+      <c r="B10" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C10" s="682">
+      <c r="C10" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="683">
+      <c r="D10" s="684">
         <f>COUNT(E10:N10)</f>
         <v/>
       </c>
-      <c r="E10" s="684">
+      <c r="E10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F10" s="684">
+      <c r="F10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G10" s="684">
+      <c r="G10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H10" s="684">
+      <c r="H10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I10" s="684">
+      <c r="I10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J10" s="684">
+      <c r="J10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K10" s="684">
+      <c r="K10" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L10" s="683">
+      <c r="L10" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M10" s="683">
+      <c r="M10" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N10" s="683">
+      <c r="N10" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O10" s="685">
+      <c r="O10" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P10" s="681">
+      <c r="P10" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q10" s="685">
+      <c r="Q10" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R10" s="681">
+      <c r="R10" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S10" s="681">
+      <c r="S10" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T10" s="682">
+      <c r="T10" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A10),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" s="141">
-      <c r="A11" s="686" t="inlineStr">
+      <c r="A11" s="687" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B11" s="687">
+      <c r="B11" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C11" s="688">
+      <c r="C11" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="689">
+      <c r="D11" s="690">
         <f>COUNT(E11:N11)</f>
         <v/>
       </c>
-      <c r="E11" s="690">
+      <c r="E11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F11" s="690">
+      <c r="F11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G11" s="690">
+      <c r="G11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H11" s="690">
+      <c r="H11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I11" s="690">
+      <c r="I11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J11" s="690">
+      <c r="J11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K11" s="690">
+      <c r="K11" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L11" s="687">
+      <c r="L11" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M11" s="687">
+      <c r="M11" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N11" s="687">
+      <c r="N11" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O11" s="690">
+      <c r="O11" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P11" s="687">
+      <c r="P11" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q11" s="690">
+      <c r="Q11" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R11" s="687">
+      <c r="R11" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S11" s="687">
+      <c r="S11" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T11" s="688">
+      <c r="T11" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A11),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" s="141">
-      <c r="A12" s="680" t="inlineStr">
+      <c r="A12" s="681" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B12" s="681">
+      <c r="B12" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C12" s="682">
+      <c r="C12" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D12" s="683">
+      <c r="D12" s="684">
         <f>COUNT(E12:N12)</f>
         <v/>
       </c>
-      <c r="E12" s="684">
+      <c r="E12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F12" s="684">
+      <c r="F12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G12" s="684">
+      <c r="G12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H12" s="684">
+      <c r="H12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I12" s="684">
+      <c r="I12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J12" s="684">
+      <c r="J12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K12" s="684">
+      <c r="K12" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L12" s="683">
+      <c r="L12" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M12" s="683">
+      <c r="M12" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N12" s="683">
+      <c r="N12" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O12" s="685">
+      <c r="O12" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P12" s="681">
+      <c r="P12" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q12" s="685">
+      <c r="Q12" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R12" s="681">
+      <c r="R12" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S12" s="681">
+      <c r="S12" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T12" s="682">
+      <c r="T12" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A12),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" s="141">
-      <c r="A13" s="686" t="inlineStr">
+      <c r="A13" s="687" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B13" s="687">
+      <c r="B13" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C13" s="688">
+      <c r="C13" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="689">
+      <c r="D13" s="690">
         <f>COUNT(E13:N13)</f>
         <v/>
       </c>
-      <c r="E13" s="690">
+      <c r="E13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F13" s="690">
+      <c r="F13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G13" s="690">
+      <c r="G13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H13" s="690">
+      <c r="H13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I13" s="690">
+      <c r="I13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J13" s="690">
+      <c r="J13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K13" s="690">
+      <c r="K13" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L13" s="687">
+      <c r="L13" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M13" s="687">
+      <c r="M13" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N13" s="687">
+      <c r="N13" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O13" s="690">
+      <c r="O13" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P13" s="687">
+      <c r="P13" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q13" s="690">
+      <c r="Q13" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R13" s="687">
+      <c r="R13" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S13" s="687">
+      <c r="S13" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T13" s="688">
+      <c r="T13" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A13),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" s="141">
-      <c r="A14" s="680" t="inlineStr">
+      <c r="A14" s="681" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B14" s="681">
+      <c r="B14" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C14" s="682">
+      <c r="C14" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="683">
+      <c r="D14" s="684">
         <f>COUNT(E14:N14)</f>
         <v/>
       </c>
-      <c r="E14" s="684">
+      <c r="E14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F14" s="684">
+      <c r="F14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G14" s="684">
+      <c r="G14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H14" s="684">
+      <c r="H14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I14" s="684">
+      <c r="I14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J14" s="684">
+      <c r="J14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K14" s="684">
+      <c r="K14" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L14" s="683">
+      <c r="L14" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M14" s="683">
+      <c r="M14" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N14" s="683">
+      <c r="N14" s="684">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O14" s="685">
+      <c r="O14" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P14" s="681">
+      <c r="P14" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q14" s="685">
+      <c r="Q14" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R14" s="681">
+      <c r="R14" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S14" s="681">
+      <c r="S14" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T14" s="682">
+      <c r="T14" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A14),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1" s="141">
-      <c r="A15" s="686" t="inlineStr">
+      <c r="A15" s="687" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B15" s="687">
+      <c r="B15" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C15" s="688">
+      <c r="C15" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="689">
+      <c r="D15" s="690">
         <f>COUNT(E15:N15)</f>
         <v/>
       </c>
-      <c r="E15" s="690">
+      <c r="E15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F15" s="690">
+      <c r="F15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G15" s="690">
+      <c r="G15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H15" s="690">
+      <c r="H15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I15" s="690">
+      <c r="I15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J15" s="690">
+      <c r="J15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K15" s="690">
+      <c r="K15" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L15" s="687">
+      <c r="L15" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M15" s="687">
+      <c r="M15" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N15" s="687">
+      <c r="N15" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O15" s="690">
+      <c r="O15" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P15" s="687">
+      <c r="P15" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q15" s="690">
+      <c r="Q15" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R15" s="687">
+      <c r="R15" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S15" s="687">
+      <c r="S15" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T15" s="688">
+      <c r="T15" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A15),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" s="141">
-      <c r="A16" s="677" t="inlineStr">
+      <c r="A16" s="678" t="inlineStr">
         <is>
           <t>SEATING DEPTH  (Seating Depth Tests 1–10  →  rows 17–26)</t>
         </is>
@@ -20962,838 +20972,838 @@
       <c r="T16" s="279" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" s="141">
-      <c r="A17" s="680" t="inlineStr">
+      <c r="A17" s="681" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B17" s="681">
+      <c r="B17" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C17" s="682">
+      <c r="C17" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="683">
+      <c r="D17" s="684">
         <f>COUNT(E17:N17)</f>
         <v/>
       </c>
-      <c r="E17" s="684">
+      <c r="E17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F17" s="684">
+      <c r="F17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G17" s="684">
+      <c r="G17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H17" s="684">
+      <c r="H17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I17" s="684">
+      <c r="I17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J17" s="684">
+      <c r="J17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K17" s="684">
+      <c r="K17" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L17" s="681">
+      <c r="L17" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M17" s="681">
+      <c r="M17" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N17" s="681">
+      <c r="N17" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O17" s="681">
+      <c r="O17" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P17" s="691">
+      <c r="P17" s="692">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q17" s="681">
+      <c r="Q17" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R17" s="692">
+      <c r="R17" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S17" s="692">
+      <c r="S17" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T17" s="693">
+      <c r="T17" s="694">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A17),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1" s="141">
-      <c r="A18" s="686" t="inlineStr">
+      <c r="A18" s="687" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B18" s="687">
+      <c r="B18" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C18" s="688">
+      <c r="C18" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="689">
+      <c r="D18" s="690">
         <f>COUNT(E18:N18)</f>
         <v/>
       </c>
-      <c r="E18" s="690">
+      <c r="E18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F18" s="690">
+      <c r="F18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G18" s="690">
+      <c r="G18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H18" s="690">
+      <c r="H18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I18" s="690">
+      <c r="I18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J18" s="690">
+      <c r="J18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K18" s="690">
+      <c r="K18" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L18" s="687">
+      <c r="L18" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M18" s="687">
+      <c r="M18" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N18" s="687">
+      <c r="N18" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O18" s="690">
+      <c r="O18" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P18" s="687">
+      <c r="P18" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q18" s="690">
+      <c r="Q18" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R18" s="687">
+      <c r="R18" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S18" s="687">
+      <c r="S18" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T18" s="688">
+      <c r="T18" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A18),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1" s="141">
-      <c r="A19" s="680" t="inlineStr">
+      <c r="A19" s="681" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B19" s="681">
+      <c r="B19" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C19" s="682">
+      <c r="C19" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="683">
+      <c r="D19" s="684">
         <f>COUNT(E19:N19)</f>
         <v/>
       </c>
-      <c r="E19" s="684">
+      <c r="E19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F19" s="684">
+      <c r="F19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G19" s="684">
+      <c r="G19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H19" s="684">
+      <c r="H19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I19" s="684">
+      <c r="I19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J19" s="684">
+      <c r="J19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K19" s="684">
+      <c r="K19" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L19" s="681">
+      <c r="L19" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M19" s="681">
+      <c r="M19" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N19" s="681">
+      <c r="N19" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O19" s="681">
+      <c r="O19" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P19" s="691">
+      <c r="P19" s="692">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q19" s="681">
+      <c r="Q19" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R19" s="692">
+      <c r="R19" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S19" s="692">
+      <c r="S19" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T19" s="693">
+      <c r="T19" s="694">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A19),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1" s="141">
-      <c r="A20" s="686" t="inlineStr">
+      <c r="A20" s="687" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B20" s="687">
+      <c r="B20" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C20" s="688">
+      <c r="C20" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="689">
+      <c r="D20" s="690">
         <f>COUNT(E20:N20)</f>
         <v/>
       </c>
-      <c r="E20" s="690">
+      <c r="E20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F20" s="690">
+      <c r="F20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G20" s="690">
+      <c r="G20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H20" s="690">
+      <c r="H20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I20" s="690">
+      <c r="I20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J20" s="690">
+      <c r="J20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K20" s="690">
+      <c r="K20" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L20" s="687">
+      <c r="L20" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M20" s="687">
+      <c r="M20" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N20" s="687">
+      <c r="N20" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O20" s="690">
+      <c r="O20" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P20" s="687">
+      <c r="P20" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q20" s="690">
+      <c r="Q20" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R20" s="687">
+      <c r="R20" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S20" s="687">
+      <c r="S20" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T20" s="688">
+      <c r="T20" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A20),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1" s="141">
-      <c r="A21" s="680" t="inlineStr">
+      <c r="A21" s="681" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B21" s="681">
+      <c r="B21" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C21" s="682">
+      <c r="C21" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="683">
+      <c r="D21" s="684">
         <f>COUNT(E21:N21)</f>
         <v/>
       </c>
-      <c r="E21" s="684">
+      <c r="E21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F21" s="684">
+      <c r="F21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G21" s="684">
+      <c r="G21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H21" s="684">
+      <c r="H21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I21" s="684">
+      <c r="I21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J21" s="684">
+      <c r="J21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K21" s="684">
+      <c r="K21" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L21" s="681">
+      <c r="L21" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M21" s="681">
+      <c r="M21" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N21" s="681">
+      <c r="N21" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O21" s="681">
+      <c r="O21" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P21" s="691">
+      <c r="P21" s="692">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q21" s="681">
+      <c r="Q21" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R21" s="692">
+      <c r="R21" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S21" s="692">
+      <c r="S21" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T21" s="693">
+      <c r="T21" s="694">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A21),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1" s="141">
-      <c r="A22" s="686" t="inlineStr">
+      <c r="A22" s="687" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="B22" s="687">
+      <c r="B22" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C22" s="688">
+      <c r="C22" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="689">
+      <c r="D22" s="690">
         <f>COUNT(E22:N22)</f>
         <v/>
       </c>
-      <c r="E22" s="690">
+      <c r="E22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F22" s="690">
+      <c r="F22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G22" s="690">
+      <c r="G22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H22" s="690">
+      <c r="H22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I22" s="690">
+      <c r="I22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J22" s="690">
+      <c r="J22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K22" s="690">
+      <c r="K22" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L22" s="687">
+      <c r="L22" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M22" s="687">
+      <c r="M22" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N22" s="687">
+      <c r="N22" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O22" s="690">
+      <c r="O22" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P22" s="687">
+      <c r="P22" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="690">
+      <c r="Q22" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R22" s="687">
+      <c r="R22" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S22" s="687">
+      <c r="S22" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T22" s="688">
+      <c r="T22" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A22),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" s="141">
-      <c r="A23" s="680" t="inlineStr">
+      <c r="A23" s="681" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="B23" s="681">
+      <c r="B23" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C23" s="682">
+      <c r="C23" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="683">
+      <c r="D23" s="684">
         <f>COUNT(E23:N23)</f>
         <v/>
       </c>
-      <c r="E23" s="684">
+      <c r="E23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F23" s="684">
+      <c r="F23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G23" s="684">
+      <c r="G23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H23" s="684">
+      <c r="H23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I23" s="684">
+      <c r="I23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J23" s="684">
+      <c r="J23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K23" s="684">
+      <c r="K23" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L23" s="681">
+      <c r="L23" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M23" s="681">
+      <c r="M23" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N23" s="681">
+      <c r="N23" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O23" s="681">
+      <c r="O23" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P23" s="691">
+      <c r="P23" s="692">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q23" s="681">
+      <c r="Q23" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R23" s="692">
+      <c r="R23" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S23" s="692">
+      <c r="S23" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T23" s="693">
+      <c r="T23" s="694">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A23),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" s="141">
-      <c r="A24" s="686" t="inlineStr">
+      <c r="A24" s="687" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="B24" s="687">
+      <c r="B24" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C24" s="688">
+      <c r="C24" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="689">
+      <c r="D24" s="690">
         <f>COUNT(E24:N24)</f>
         <v/>
       </c>
-      <c r="E24" s="690">
+      <c r="E24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F24" s="690">
+      <c r="F24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G24" s="690">
+      <c r="G24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H24" s="690">
+      <c r="H24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I24" s="690">
+      <c r="I24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J24" s="690">
+      <c r="J24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K24" s="690">
+      <c r="K24" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L24" s="687">
+      <c r="L24" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M24" s="687">
+      <c r="M24" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N24" s="687">
+      <c r="N24" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O24" s="690">
+      <c r="O24" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P24" s="687">
+      <c r="P24" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q24" s="690">
+      <c r="Q24" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R24" s="687">
+      <c r="R24" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S24" s="687">
+      <c r="S24" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T24" s="688">
+      <c r="T24" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A24),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1" s="141">
-      <c r="A25" s="680" t="inlineStr">
+      <c r="A25" s="681" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="B25" s="681">
+      <c r="B25" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C25" s="682">
+      <c r="C25" s="683">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="683">
+      <c r="D25" s="684">
         <f>COUNT(E25:N25)</f>
         <v/>
       </c>
-      <c r="E25" s="684">
+      <c r="E25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F25" s="684">
+      <c r="F25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G25" s="684">
+      <c r="G25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H25" s="684">
+      <c r="H25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I25" s="684">
+      <c r="I25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J25" s="684">
+      <c r="J25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K25" s="684">
+      <c r="K25" s="685">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L25" s="681">
+      <c r="L25" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M25" s="681">
+      <c r="M25" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N25" s="681">
+      <c r="N25" s="682">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O25" s="681">
+      <c r="O25" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P25" s="691">
+      <c r="P25" s="692">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q25" s="681">
+      <c r="Q25" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R25" s="692">
+      <c r="R25" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S25" s="692">
+      <c r="S25" s="693">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T25" s="693">
+      <c r="T25" s="694">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A25),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1" s="141">
-      <c r="A26" s="686" t="inlineStr">
+      <c r="A26" s="687" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="B26" s="687">
+      <c r="B26" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C26" s="688">
+      <c r="C26" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$T$2:$T$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$T$2:$T$200)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="689">
+      <c r="D26" s="690">
         <f>COUNT(E26:N26)</f>
         <v/>
       </c>
-      <c r="E26" s="690">
+      <c r="E26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$E$2:$E$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$E$2:$E$200),""),"")</f>
         <v/>
       </c>
-      <c r="F26" s="690">
+      <c r="F26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$F$2:$F$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$F$2:$F$200),""),"")</f>
         <v/>
       </c>
-      <c r="G26" s="690">
+      <c r="G26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$G$2:$G$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$G$2:$G$200),""),"")</f>
         <v/>
       </c>
-      <c r="H26" s="690">
+      <c r="H26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$H$2:$H$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$H$2:$H$200),""),"")</f>
         <v/>
       </c>
-      <c r="I26" s="690">
+      <c r="I26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$I$2:$I$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$I$2:$I$200),""),"")</f>
         <v/>
       </c>
-      <c r="J26" s="690">
+      <c r="J26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$J$2:$J$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$J$2:$J$200),""),"")</f>
         <v/>
       </c>
-      <c r="K26" s="690">
+      <c r="K26" s="691">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$K$2:$K$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$K$2:$K$200),""),"")</f>
         <v/>
       </c>
-      <c r="L26" s="687">
+      <c r="L26" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$L$2:$L$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$L$2:$L$200),""),"")</f>
         <v/>
       </c>
-      <c r="M26" s="687">
+      <c r="M26" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$M$2:$M$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$M$2:$M$200),""),"")</f>
         <v/>
       </c>
-      <c r="N26" s="687">
+      <c r="N26" s="688">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$N$2:$N$200)&gt;0,LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$N$2:$N$200),""),"")</f>
         <v/>
       </c>
-      <c r="O26" s="690">
+      <c r="O26" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P26" s="687">
+      <c r="P26" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q26" s="690">
+      <c r="Q26" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="R26" s="687">
+      <c r="R26" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="S26" s="687">
+      <c r="S26" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$S$2:$S$200),"")</f>
         <v/>
       </c>
-      <c r="T26" s="688">
+      <c r="T26" s="689">
         <f>IFERROR(IF(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$U$2:$U$200)="","",LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A26),GarminSessions!$U$2:$U$200)),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="7.5" customHeight="1" s="141"/>
     <row r="28" ht="26" customHeight="1" s="141">
-      <c r="A28" s="677" t="inlineStr">
+      <c r="A28" s="678" t="inlineStr">
         <is>
           <t>FREE-FORM SESSION LOG  (extra Garmin sessions — confirmation groups, calibration shoots, etc.)</t>
         </is>
@@ -21819,1058 +21829,1058 @@
       <c r="T28" s="279" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" s="141">
-      <c r="A29" s="680" t="n"/>
-      <c r="B29" s="681">
+      <c r="A29" s="681" t="n"/>
+      <c r="B29" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C29" s="682">
+      <c r="C29" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D29" s="683">
+      <c r="D29" s="684">
         <f>COUNT(E29:K29)</f>
         <v/>
       </c>
-      <c r="E29" s="684">
+      <c r="E29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F29" s="684">
+      <c r="F29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G29" s="684">
+      <c r="G29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H29" s="684">
+      <c r="H29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I29" s="684">
+      <c r="I29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J29" s="684">
+      <c r="J29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K29" s="684">
+      <c r="K29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L29" s="684">
+      <c r="L29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M29" s="685">
+      <c r="M29" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N29" s="684">
+      <c r="N29" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O29" s="683">
+      <c r="O29" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P29" s="683">
+      <c r="P29" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q29" s="681">
+      <c r="Q29" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A29),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R29" s="680" t="n"/>
-      <c r="S29" s="680" t="n"/>
-      <c r="T29" s="682" t="n"/>
+      <c r="R29" s="681" t="n"/>
+      <c r="S29" s="681" t="n"/>
+      <c r="T29" s="683" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" s="141">
-      <c r="A30" s="686" t="n"/>
-      <c r="B30" s="687">
+      <c r="A30" s="687" t="n"/>
+      <c r="B30" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C30" s="688">
+      <c r="C30" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D30" s="689">
+      <c r="D30" s="690">
         <f>COUNT(E30:K30)</f>
         <v/>
       </c>
-      <c r="E30" s="690">
+      <c r="E30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F30" s="690">
+      <c r="F30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G30" s="690">
+      <c r="G30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H30" s="690">
+      <c r="H30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I30" s="690">
+      <c r="I30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J30" s="690">
+      <c r="J30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K30" s="690">
+      <c r="K30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L30" s="690">
+      <c r="L30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M30" s="694">
+      <c r="M30" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N30" s="690">
+      <c r="N30" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O30" s="689">
+      <c r="O30" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P30" s="689">
+      <c r="P30" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q30" s="687">
+      <c r="Q30" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A30),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R30" s="686" t="n"/>
-      <c r="S30" s="686" t="n"/>
-      <c r="T30" s="688" t="n"/>
+      <c r="R30" s="687" t="n"/>
+      <c r="S30" s="687" t="n"/>
+      <c r="T30" s="689" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" s="141">
-      <c r="A31" s="680" t="n"/>
-      <c r="B31" s="681">
+      <c r="A31" s="681" t="n"/>
+      <c r="B31" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C31" s="682">
+      <c r="C31" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D31" s="683">
+      <c r="D31" s="684">
         <f>COUNT(E31:K31)</f>
         <v/>
       </c>
-      <c r="E31" s="684">
+      <c r="E31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F31" s="684">
+      <c r="F31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G31" s="684">
+      <c r="G31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H31" s="684">
+      <c r="H31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I31" s="684">
+      <c r="I31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J31" s="684">
+      <c r="J31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K31" s="684">
+      <c r="K31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L31" s="684">
+      <c r="L31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M31" s="685">
+      <c r="M31" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N31" s="684">
+      <c r="N31" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O31" s="683">
+      <c r="O31" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P31" s="683">
+      <c r="P31" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q31" s="681">
+      <c r="Q31" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A31),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R31" s="680" t="n"/>
-      <c r="S31" s="680" t="n"/>
-      <c r="T31" s="682" t="n"/>
+      <c r="R31" s="681" t="n"/>
+      <c r="S31" s="681" t="n"/>
+      <c r="T31" s="683" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" s="141">
-      <c r="A32" s="686" t="n"/>
-      <c r="B32" s="687">
+      <c r="A32" s="687" t="n"/>
+      <c r="B32" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C32" s="688">
+      <c r="C32" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D32" s="689">
+      <c r="D32" s="690">
         <f>COUNT(E32:K32)</f>
         <v/>
       </c>
-      <c r="E32" s="690">
+      <c r="E32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F32" s="690">
+      <c r="F32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G32" s="690">
+      <c r="G32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H32" s="690">
+      <c r="H32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I32" s="690">
+      <c r="I32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J32" s="690">
+      <c r="J32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K32" s="690">
+      <c r="K32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L32" s="690">
+      <c r="L32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M32" s="694">
+      <c r="M32" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N32" s="690">
+      <c r="N32" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O32" s="689">
+      <c r="O32" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P32" s="689">
+      <c r="P32" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q32" s="687">
+      <c r="Q32" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A32),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R32" s="686" t="n"/>
-      <c r="S32" s="686" t="n"/>
-      <c r="T32" s="688" t="n"/>
+      <c r="R32" s="687" t="n"/>
+      <c r="S32" s="687" t="n"/>
+      <c r="T32" s="689" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" s="141">
-      <c r="A33" s="680" t="n"/>
-      <c r="B33" s="681">
+      <c r="A33" s="681" t="n"/>
+      <c r="B33" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C33" s="682">
+      <c r="C33" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D33" s="683">
+      <c r="D33" s="684">
         <f>COUNT(E33:K33)</f>
         <v/>
       </c>
-      <c r="E33" s="684">
+      <c r="E33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F33" s="684">
+      <c r="F33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G33" s="684">
+      <c r="G33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H33" s="684">
+      <c r="H33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I33" s="684">
+      <c r="I33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J33" s="684">
+      <c r="J33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K33" s="684">
+      <c r="K33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L33" s="684">
+      <c r="L33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M33" s="685">
+      <c r="M33" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N33" s="684">
+      <c r="N33" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O33" s="683">
+      <c r="O33" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P33" s="683">
+      <c r="P33" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="681">
+      <c r="Q33" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A33),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R33" s="680" t="n"/>
-      <c r="S33" s="680" t="n"/>
-      <c r="T33" s="682" t="n"/>
+      <c r="R33" s="681" t="n"/>
+      <c r="S33" s="681" t="n"/>
+      <c r="T33" s="683" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" s="141">
-      <c r="A34" s="686" t="n"/>
-      <c r="B34" s="687">
+      <c r="A34" s="687" t="n"/>
+      <c r="B34" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C34" s="688">
+      <c r="C34" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D34" s="689">
+      <c r="D34" s="690">
         <f>COUNT(E34:K34)</f>
         <v/>
       </c>
-      <c r="E34" s="690">
+      <c r="E34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F34" s="690">
+      <c r="F34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G34" s="690">
+      <c r="G34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H34" s="690">
+      <c r="H34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I34" s="690">
+      <c r="I34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J34" s="690">
+      <c r="J34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K34" s="690">
+      <c r="K34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L34" s="690">
+      <c r="L34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M34" s="694">
+      <c r="M34" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N34" s="690">
+      <c r="N34" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O34" s="689">
+      <c r="O34" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P34" s="689">
+      <c r="P34" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q34" s="687">
+      <c r="Q34" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A34),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R34" s="686" t="n"/>
-      <c r="S34" s="686" t="n"/>
-      <c r="T34" s="688" t="n"/>
+      <c r="R34" s="687" t="n"/>
+      <c r="S34" s="687" t="n"/>
+      <c r="T34" s="689" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" s="141">
-      <c r="A35" s="680" t="n"/>
-      <c r="B35" s="681">
+      <c r="A35" s="681" t="n"/>
+      <c r="B35" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C35" s="682">
+      <c r="C35" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D35" s="683">
+      <c r="D35" s="684">
         <f>COUNT(E35:K35)</f>
         <v/>
       </c>
-      <c r="E35" s="684">
+      <c r="E35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F35" s="684">
+      <c r="F35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G35" s="684">
+      <c r="G35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H35" s="684">
+      <c r="H35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I35" s="684">
+      <c r="I35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J35" s="684">
+      <c r="J35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K35" s="684">
+      <c r="K35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L35" s="684">
+      <c r="L35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M35" s="685">
+      <c r="M35" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N35" s="684">
+      <c r="N35" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O35" s="683">
+      <c r="O35" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P35" s="683">
+      <c r="P35" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q35" s="681">
+      <c r="Q35" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A35),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R35" s="680" t="n"/>
-      <c r="S35" s="680" t="n"/>
-      <c r="T35" s="682" t="n"/>
+      <c r="R35" s="681" t="n"/>
+      <c r="S35" s="681" t="n"/>
+      <c r="T35" s="683" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" s="141">
-      <c r="A36" s="686" t="n"/>
-      <c r="B36" s="687">
+      <c r="A36" s="687" t="n"/>
+      <c r="B36" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C36" s="688">
+      <c r="C36" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D36" s="689">
+      <c r="D36" s="690">
         <f>COUNT(E36:K36)</f>
         <v/>
       </c>
-      <c r="E36" s="690">
+      <c r="E36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F36" s="690">
+      <c r="F36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G36" s="690">
+      <c r="G36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H36" s="690">
+      <c r="H36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I36" s="690">
+      <c r="I36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J36" s="690">
+      <c r="J36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K36" s="690">
+      <c r="K36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L36" s="690">
+      <c r="L36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M36" s="694">
+      <c r="M36" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N36" s="690">
+      <c r="N36" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O36" s="689">
+      <c r="O36" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P36" s="689">
+      <c r="P36" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q36" s="687">
+      <c r="Q36" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A36),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R36" s="686" t="n"/>
-      <c r="S36" s="686" t="n"/>
-      <c r="T36" s="688" t="n"/>
+      <c r="R36" s="687" t="n"/>
+      <c r="S36" s="687" t="n"/>
+      <c r="T36" s="689" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" s="141">
-      <c r="A37" s="680" t="n"/>
-      <c r="B37" s="681">
+      <c r="A37" s="681" t="n"/>
+      <c r="B37" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C37" s="682">
+      <c r="C37" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D37" s="683">
+      <c r="D37" s="684">
         <f>COUNT(E37:K37)</f>
         <v/>
       </c>
-      <c r="E37" s="684">
+      <c r="E37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F37" s="684">
+      <c r="F37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G37" s="684">
+      <c r="G37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H37" s="684">
+      <c r="H37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I37" s="684">
+      <c r="I37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J37" s="684">
+      <c r="J37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K37" s="684">
+      <c r="K37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L37" s="684">
+      <c r="L37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M37" s="685">
+      <c r="M37" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N37" s="684">
+      <c r="N37" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O37" s="683">
+      <c r="O37" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P37" s="683">
+      <c r="P37" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q37" s="681">
+      <c r="Q37" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A37),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R37" s="680" t="n"/>
-      <c r="S37" s="680" t="n"/>
-      <c r="T37" s="682" t="n"/>
+      <c r="R37" s="681" t="n"/>
+      <c r="S37" s="681" t="n"/>
+      <c r="T37" s="683" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1" s="141">
-      <c r="A38" s="686" t="n"/>
-      <c r="B38" s="687">
+      <c r="A38" s="687" t="n"/>
+      <c r="B38" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C38" s="688">
+      <c r="C38" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D38" s="689">
+      <c r="D38" s="690">
         <f>COUNT(E38:K38)</f>
         <v/>
       </c>
-      <c r="E38" s="690">
+      <c r="E38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F38" s="690">
+      <c r="F38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G38" s="690">
+      <c r="G38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H38" s="690">
+      <c r="H38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I38" s="690">
+      <c r="I38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J38" s="690">
+      <c r="J38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K38" s="690">
+      <c r="K38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L38" s="690">
+      <c r="L38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M38" s="694">
+      <c r="M38" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N38" s="690">
+      <c r="N38" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O38" s="689">
+      <c r="O38" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P38" s="689">
+      <c r="P38" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="687">
+      <c r="Q38" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A38),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R38" s="686" t="n"/>
-      <c r="S38" s="686" t="n"/>
-      <c r="T38" s="688" t="n"/>
+      <c r="R38" s="687" t="n"/>
+      <c r="S38" s="687" t="n"/>
+      <c r="T38" s="689" t="n"/>
     </row>
     <row r="39" ht="18.75" customHeight="1" s="141">
-      <c r="A39" s="680" t="n"/>
-      <c r="B39" s="681">
+      <c r="A39" s="681" t="n"/>
+      <c r="B39" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C39" s="682">
+      <c r="C39" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D39" s="683">
+      <c r="D39" s="684">
         <f>COUNT(E39:K39)</f>
         <v/>
       </c>
-      <c r="E39" s="684">
+      <c r="E39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F39" s="684">
+      <c r="F39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G39" s="684">
+      <c r="G39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H39" s="684">
+      <c r="H39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I39" s="684">
+      <c r="I39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J39" s="684">
+      <c r="J39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K39" s="684">
+      <c r="K39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L39" s="684">
+      <c r="L39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M39" s="685">
+      <c r="M39" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N39" s="684">
+      <c r="N39" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O39" s="683">
+      <c r="O39" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P39" s="683">
+      <c r="P39" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q39" s="681">
+      <c r="Q39" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A39),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R39" s="680" t="n"/>
-      <c r="S39" s="680" t="n"/>
-      <c r="T39" s="682" t="n"/>
+      <c r="R39" s="681" t="n"/>
+      <c r="S39" s="681" t="n"/>
+      <c r="T39" s="683" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" s="141">
-      <c r="A40" s="686" t="n"/>
-      <c r="B40" s="687">
+      <c r="A40" s="687" t="n"/>
+      <c r="B40" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C40" s="688">
+      <c r="C40" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D40" s="689">
+      <c r="D40" s="690">
         <f>COUNT(E40:K40)</f>
         <v/>
       </c>
-      <c r="E40" s="690">
+      <c r="E40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F40" s="690">
+      <c r="F40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G40" s="690">
+      <c r="G40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H40" s="690">
+      <c r="H40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I40" s="690">
+      <c r="I40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J40" s="690">
+      <c r="J40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K40" s="690">
+      <c r="K40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L40" s="690">
+      <c r="L40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M40" s="694">
+      <c r="M40" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N40" s="690">
+      <c r="N40" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O40" s="689">
+      <c r="O40" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P40" s="689">
+      <c r="P40" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q40" s="687">
+      <c r="Q40" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A40),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R40" s="686" t="n"/>
-      <c r="S40" s="686" t="n"/>
-      <c r="T40" s="688" t="n"/>
+      <c r="R40" s="687" t="n"/>
+      <c r="S40" s="687" t="n"/>
+      <c r="T40" s="689" t="n"/>
     </row>
     <row r="41" ht="18.75" customHeight="1" s="141">
-      <c r="A41" s="680" t="n"/>
-      <c r="B41" s="681">
+      <c r="A41" s="681" t="n"/>
+      <c r="B41" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C41" s="682">
+      <c r="C41" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D41" s="683">
+      <c r="D41" s="684">
         <f>COUNT(E41:K41)</f>
         <v/>
       </c>
-      <c r="E41" s="684">
+      <c r="E41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F41" s="684">
+      <c r="F41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G41" s="684">
+      <c r="G41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H41" s="684">
+      <c r="H41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I41" s="684">
+      <c r="I41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J41" s="684">
+      <c r="J41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K41" s="684">
+      <c r="K41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L41" s="684">
+      <c r="L41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M41" s="685">
+      <c r="M41" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N41" s="684">
+      <c r="N41" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O41" s="683">
+      <c r="O41" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P41" s="683">
+      <c r="P41" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q41" s="681">
+      <c r="Q41" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A41),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R41" s="680" t="n"/>
-      <c r="S41" s="680" t="n"/>
-      <c r="T41" s="682" t="n"/>
+      <c r="R41" s="681" t="n"/>
+      <c r="S41" s="681" t="n"/>
+      <c r="T41" s="683" t="n"/>
     </row>
     <row r="42" ht="18.75" customHeight="1" s="141">
-      <c r="A42" s="686" t="n"/>
-      <c r="B42" s="687">
+      <c r="A42" s="687" t="n"/>
+      <c r="B42" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C42" s="688">
+      <c r="C42" s="689">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D42" s="689">
+      <c r="D42" s="690">
         <f>COUNT(E42:K42)</f>
         <v/>
       </c>
-      <c r="E42" s="690">
+      <c r="E42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F42" s="690">
+      <c r="F42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G42" s="690">
+      <c r="G42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H42" s="690">
+      <c r="H42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I42" s="690">
+      <c r="I42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J42" s="690">
+      <c r="J42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K42" s="690">
+      <c r="K42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L42" s="690">
+      <c r="L42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M42" s="694">
+      <c r="M42" s="695">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N42" s="690">
+      <c r="N42" s="691">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O42" s="689">
+      <c r="O42" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P42" s="689">
+      <c r="P42" s="690">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q42" s="687">
+      <c r="Q42" s="688">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A42),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R42" s="686" t="n"/>
-      <c r="S42" s="686" t="n"/>
-      <c r="T42" s="688" t="n"/>
+      <c r="R42" s="687" t="n"/>
+      <c r="S42" s="687" t="n"/>
+      <c r="T42" s="689" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" s="141">
-      <c r="A43" s="680" t="n"/>
-      <c r="B43" s="681">
+      <c r="A43" s="681" t="n"/>
+      <c r="B43" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C43" s="682">
+      <c r="C43" s="683">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$Q$2:$Q$200),"")</f>
         <v/>
       </c>
-      <c r="D43" s="683">
+      <c r="D43" s="684">
         <f>COUNT(E43:K43)</f>
         <v/>
       </c>
-      <c r="E43" s="684">
+      <c r="E43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="F43" s="684">
+      <c r="F43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="G43" s="684">
+      <c r="G43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="H43" s="684">
+      <c r="H43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="I43" s="684">
+      <c r="I43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="J43" s="684">
+      <c r="J43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="K43" s="684">
+      <c r="K43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="L43" s="684">
+      <c r="L43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="M43" s="685">
+      <c r="M43" s="686">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="N43" s="684">
+      <c r="N43" s="685">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="O43" s="683">
+      <c r="O43" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$O$2:$O$200),"")</f>
         <v/>
       </c>
-      <c r="P43" s="683">
+      <c r="P43" s="684">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$P$2:$P$200),"")</f>
         <v/>
       </c>
-      <c r="Q43" s="681">
+      <c r="Q43" s="682">
         <f>IFERROR(LOOKUP(2,1/(GarminSessions!$A$2:$A$200=$A43),GarminSessions!$R$2:$R$200),"")</f>
         <v/>
       </c>
-      <c r="R43" s="680" t="n"/>
-      <c r="S43" s="680" t="n"/>
-      <c r="T43" s="682" t="n"/>
+      <c r="R43" s="681" t="n"/>
+      <c r="S43" s="681" t="n"/>
+      <c r="T43" s="683" t="n"/>
     </row>
     <row r="44"/>
     <row r="45" ht="26" customHeight="1" s="141">
-      <c r="A45" s="677" t="inlineStr">
+      <c r="A45" s="678" t="inlineStr">
         <is>
           <t>HOW THE WIRING WORKS</t>
         </is>
@@ -23031,7 +23041,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" s="141">
-      <c r="A3" s="677" t="inlineStr">
+      <c r="A3" s="678" t="inlineStr">
         <is>
           <t>POWDER LADDER  (Load Log P1–P10  →  rows 6–15)</t>
         </is>
@@ -23051,594 +23061,594 @@
     </row>
     <row r="4" ht="6" customHeight="1" s="141"/>
     <row r="5" ht="32" customHeight="1" s="141">
-      <c r="A5" s="678" t="inlineStr">
+      <c r="A5" s="679" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="B5" s="678" t="inlineStr">
+      <c r="B5" s="679" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C5" s="678" t="inlineStr">
+      <c r="C5" s="679" t="inlineStr">
         <is>
           <t>Distance (yd)</t>
         </is>
       </c>
-      <c r="D5" s="678" t="inlineStr">
+      <c r="D5" s="679" t="inlineStr">
         <is>
           <t>Group (in)</t>
         </is>
       </c>
-      <c r="E5" s="678" t="inlineStr">
+      <c r="E5" s="679" t="inlineStr">
         <is>
           <t>Width (in)</t>
         </is>
       </c>
-      <c r="F5" s="678" t="inlineStr">
+      <c r="F5" s="679" t="inlineStr">
         <is>
           <t>Height (in)</t>
         </is>
       </c>
-      <c r="G5" s="678" t="inlineStr">
+      <c r="G5" s="679" t="inlineStr">
         <is>
           <t>MR (in)</t>
         </is>
       </c>
-      <c r="H5" s="678" t="inlineStr">
+      <c r="H5" s="679" t="inlineStr">
         <is>
           <t>CEP (in)</t>
         </is>
       </c>
-      <c r="I5" s="678" t="inlineStr">
+      <c r="I5" s="679" t="inlineStr">
         <is>
           <t>SD Radial (in)</t>
         </is>
       </c>
-      <c r="J5" s="678" t="inlineStr">
+      <c r="J5" s="679" t="inlineStr">
         <is>
           <t>SD Vert (in)</t>
         </is>
       </c>
-      <c r="K5" s="678" t="inlineStr">
+      <c r="K5" s="679" t="inlineStr">
         <is>
           <t>SD Horiz (in)</t>
         </is>
       </c>
-      <c r="L5" s="678" t="inlineStr">
+      <c r="L5" s="679" t="inlineStr">
         <is>
           <t>Caliber</t>
         </is>
       </c>
-      <c r="M5" s="678" t="inlineStr">
+      <c r="M5" s="679" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" s="141">
-      <c r="A6" s="680" t="inlineStr">
+      <c r="A6" s="681" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B6" s="681">
+      <c r="B6" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C6" s="683">
+      <c r="C6" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D6" s="695">
+      <c r="D6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E6" s="695">
+      <c r="E6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F6" s="695">
+      <c r="F6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G6" s="695">
+      <c r="G6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H6" s="695">
+      <c r="H6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I6" s="695">
+      <c r="I6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J6" s="695">
+      <c r="J6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K6" s="695">
+      <c r="K6" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L6" s="681">
+      <c r="L6" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A6),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M6" s="682" t="n"/>
+      <c r="M6" s="683" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" s="141">
-      <c r="A7" s="686" t="inlineStr">
+      <c r="A7" s="687" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B7" s="687">
+      <c r="B7" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C7" s="689">
+      <c r="C7" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D7" s="696">
+      <c r="D7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E7" s="696">
+      <c r="E7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F7" s="696">
+      <c r="F7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G7" s="696">
+      <c r="G7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H7" s="696">
+      <c r="H7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I7" s="696">
+      <c r="I7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J7" s="696">
+      <c r="J7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K7" s="696">
+      <c r="K7" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L7" s="687">
+      <c r="L7" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A7),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M7" s="688" t="n"/>
+      <c r="M7" s="689" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" s="141">
-      <c r="A8" s="680" t="inlineStr">
+      <c r="A8" s="681" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B8" s="681">
+      <c r="B8" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C8" s="683">
+      <c r="C8" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D8" s="695">
+      <c r="D8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E8" s="695">
+      <c r="E8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F8" s="695">
+      <c r="F8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G8" s="695">
+      <c r="G8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H8" s="695">
+      <c r="H8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I8" s="695">
+      <c r="I8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J8" s="695">
+      <c r="J8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K8" s="695">
+      <c r="K8" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L8" s="681">
+      <c r="L8" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A8),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M8" s="682" t="n"/>
+      <c r="M8" s="683" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" s="141">
-      <c r="A9" s="686" t="inlineStr">
+      <c r="A9" s="687" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B9" s="687">
+      <c r="B9" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C9" s="689">
+      <c r="C9" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D9" s="696">
+      <c r="D9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E9" s="696">
+      <c r="E9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F9" s="696">
+      <c r="F9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G9" s="696">
+      <c r="G9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H9" s="696">
+      <c r="H9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I9" s="696">
+      <c r="I9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J9" s="696">
+      <c r="J9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K9" s="696">
+      <c r="K9" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L9" s="687">
+      <c r="L9" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A9),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M9" s="688" t="n"/>
+      <c r="M9" s="689" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" s="141">
-      <c r="A10" s="680" t="inlineStr">
+      <c r="A10" s="681" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B10" s="681">
+      <c r="B10" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C10" s="683">
+      <c r="C10" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D10" s="695">
+      <c r="D10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E10" s="695">
+      <c r="E10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F10" s="695">
+      <c r="F10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G10" s="695">
+      <c r="G10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H10" s="695">
+      <c r="H10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I10" s="695">
+      <c r="I10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J10" s="695">
+      <c r="J10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K10" s="695">
+      <c r="K10" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L10" s="681">
+      <c r="L10" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A10),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M10" s="682" t="n"/>
+      <c r="M10" s="683" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" s="141">
-      <c r="A11" s="686" t="inlineStr">
+      <c r="A11" s="687" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B11" s="687">
+      <c r="B11" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C11" s="689">
+      <c r="C11" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D11" s="696">
+      <c r="D11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E11" s="696">
+      <c r="E11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F11" s="696">
+      <c r="F11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G11" s="696">
+      <c r="G11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H11" s="696">
+      <c r="H11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I11" s="696">
+      <c r="I11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J11" s="696">
+      <c r="J11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K11" s="696">
+      <c r="K11" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L11" s="687">
+      <c r="L11" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A11),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M11" s="688" t="n"/>
+      <c r="M11" s="689" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" s="141">
-      <c r="A12" s="680" t="inlineStr">
+      <c r="A12" s="681" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B12" s="681">
+      <c r="B12" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C12" s="683">
+      <c r="C12" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D12" s="695">
+      <c r="D12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E12" s="695">
+      <c r="E12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F12" s="695">
+      <c r="F12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G12" s="695">
+      <c r="G12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H12" s="695">
+      <c r="H12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I12" s="695">
+      <c r="I12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J12" s="695">
+      <c r="J12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K12" s="695">
+      <c r="K12" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L12" s="681">
+      <c r="L12" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A12),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M12" s="682" t="n"/>
+      <c r="M12" s="683" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" s="141">
-      <c r="A13" s="686" t="inlineStr">
+      <c r="A13" s="687" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B13" s="687">
+      <c r="B13" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C13" s="689">
+      <c r="C13" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D13" s="696">
+      <c r="D13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E13" s="696">
+      <c r="E13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F13" s="696">
+      <c r="F13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G13" s="696">
+      <c r="G13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H13" s="696">
+      <c r="H13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I13" s="696">
+      <c r="I13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J13" s="696">
+      <c r="J13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K13" s="696">
+      <c r="K13" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L13" s="687">
+      <c r="L13" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A13),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M13" s="688" t="n"/>
+      <c r="M13" s="689" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" s="141">
-      <c r="A14" s="680" t="inlineStr">
+      <c r="A14" s="681" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B14" s="681">
+      <c r="B14" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C14" s="683">
+      <c r="C14" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D14" s="695">
+      <c r="D14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E14" s="695">
+      <c r="E14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F14" s="695">
+      <c r="F14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G14" s="695">
+      <c r="G14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H14" s="695">
+      <c r="H14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I14" s="695">
+      <c r="I14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J14" s="695">
+      <c r="J14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K14" s="695">
+      <c r="K14" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L14" s="681">
+      <c r="L14" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A14),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M14" s="682" t="n"/>
+      <c r="M14" s="683" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" s="141">
-      <c r="A15" s="686" t="inlineStr">
+      <c r="A15" s="687" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B15" s="687">
+      <c r="B15" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C15" s="689">
+      <c r="C15" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D15" s="696">
+      <c r="D15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E15" s="696">
+      <c r="E15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F15" s="696">
+      <c r="F15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G15" s="696">
+      <c r="G15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H15" s="696">
+      <c r="H15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I15" s="696">
+      <c r="I15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J15" s="696">
+      <c r="J15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K15" s="696">
+      <c r="K15" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L15" s="687">
+      <c r="L15" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A15),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M15" s="688" t="n"/>
+      <c r="M15" s="689" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1" s="141">
-      <c r="A16" s="677" t="inlineStr">
+      <c r="A16" s="678" t="inlineStr">
         <is>
           <t>SEATING DEPTH  (Seating Depth Tests 1–10  →  rows 17–26)</t>
         </is>
@@ -23657,528 +23667,528 @@
       <c r="M16" s="279" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" s="141">
-      <c r="A17" s="680" t="inlineStr">
+      <c r="A17" s="681" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B17" s="681">
+      <c r="B17" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C17" s="683">
+      <c r="C17" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D17" s="695">
+      <c r="D17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E17" s="695">
+      <c r="E17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F17" s="695">
+      <c r="F17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G17" s="695">
+      <c r="G17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H17" s="695">
+      <c r="H17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I17" s="695">
+      <c r="I17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J17" s="695">
+      <c r="J17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K17" s="695">
+      <c r="K17" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L17" s="681">
+      <c r="L17" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A17),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M17" s="682" t="n"/>
+      <c r="M17" s="683" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" s="141">
-      <c r="A18" s="686" t="inlineStr">
+      <c r="A18" s="687" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B18" s="687">
+      <c r="B18" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C18" s="689">
+      <c r="C18" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D18" s="696">
+      <c r="D18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E18" s="696">
+      <c r="E18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F18" s="696">
+      <c r="F18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G18" s="696">
+      <c r="G18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H18" s="696">
+      <c r="H18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I18" s="696">
+      <c r="I18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J18" s="696">
+      <c r="J18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K18" s="696">
+      <c r="K18" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L18" s="687">
+      <c r="L18" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A18),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M18" s="688" t="n"/>
+      <c r="M18" s="689" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" s="141">
-      <c r="A19" s="680" t="inlineStr">
+      <c r="A19" s="681" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B19" s="681">
+      <c r="B19" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C19" s="683">
+      <c r="C19" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D19" s="695">
+      <c r="D19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E19" s="695">
+      <c r="E19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F19" s="695">
+      <c r="F19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G19" s="695">
+      <c r="G19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H19" s="695">
+      <c r="H19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I19" s="695">
+      <c r="I19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J19" s="695">
+      <c r="J19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K19" s="695">
+      <c r="K19" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L19" s="681">
+      <c r="L19" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A19),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M19" s="682" t="n"/>
+      <c r="M19" s="683" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" s="141">
-      <c r="A20" s="686" t="inlineStr">
+      <c r="A20" s="687" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B20" s="687">
+      <c r="B20" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C20" s="689">
+      <c r="C20" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D20" s="696">
+      <c r="D20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E20" s="696">
+      <c r="E20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F20" s="696">
+      <c r="F20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G20" s="696">
+      <c r="G20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H20" s="696">
+      <c r="H20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I20" s="696">
+      <c r="I20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J20" s="696">
+      <c r="J20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K20" s="696">
+      <c r="K20" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L20" s="687">
+      <c r="L20" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A20),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M20" s="688" t="n"/>
+      <c r="M20" s="689" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" s="141">
-      <c r="A21" s="680" t="inlineStr">
+      <c r="A21" s="681" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B21" s="681">
+      <c r="B21" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C21" s="683">
+      <c r="C21" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D21" s="695">
+      <c r="D21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E21" s="695">
+      <c r="E21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F21" s="695">
+      <c r="F21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G21" s="695">
+      <c r="G21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H21" s="695">
+      <c r="H21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I21" s="695">
+      <c r="I21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J21" s="695">
+      <c r="J21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K21" s="695">
+      <c r="K21" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L21" s="681">
+      <c r="L21" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A21),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M21" s="682" t="n"/>
+      <c r="M21" s="683" t="n"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" s="141">
-      <c r="A22" s="686" t="inlineStr">
+      <c r="A22" s="687" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="B22" s="687">
+      <c r="B22" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C22" s="689">
+      <c r="C22" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D22" s="696">
+      <c r="D22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E22" s="696">
+      <c r="E22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F22" s="696">
+      <c r="F22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G22" s="696">
+      <c r="G22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H22" s="696">
+      <c r="H22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I22" s="696">
+      <c r="I22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J22" s="696">
+      <c r="J22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K22" s="696">
+      <c r="K22" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L22" s="687">
+      <c r="L22" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A22),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M22" s="688" t="n"/>
+      <c r="M22" s="689" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" s="141">
-      <c r="A23" s="680" t="inlineStr">
+      <c r="A23" s="681" t="inlineStr">
         <is>
           <t>S7</t>
         </is>
       </c>
-      <c r="B23" s="681">
+      <c r="B23" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C23" s="683">
+      <c r="C23" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D23" s="695">
+      <c r="D23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E23" s="695">
+      <c r="E23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F23" s="695">
+      <c r="F23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G23" s="695">
+      <c r="G23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H23" s="695">
+      <c r="H23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I23" s="695">
+      <c r="I23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J23" s="695">
+      <c r="J23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K23" s="695">
+      <c r="K23" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L23" s="681">
+      <c r="L23" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A23),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M23" s="682" t="n"/>
+      <c r="M23" s="683" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1" s="141">
-      <c r="A24" s="686" t="inlineStr">
+      <c r="A24" s="687" t="inlineStr">
         <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="B24" s="687">
+      <c r="B24" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C24" s="689">
+      <c r="C24" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D24" s="696">
+      <c r="D24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E24" s="696">
+      <c r="E24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F24" s="696">
+      <c r="F24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G24" s="696">
+      <c r="G24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H24" s="696">
+      <c r="H24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I24" s="696">
+      <c r="I24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J24" s="696">
+      <c r="J24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K24" s="696">
+      <c r="K24" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L24" s="687">
+      <c r="L24" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A24),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M24" s="688" t="n"/>
+      <c r="M24" s="689" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1" s="141">
-      <c r="A25" s="680" t="inlineStr">
+      <c r="A25" s="681" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="B25" s="681">
+      <c r="B25" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C25" s="683">
+      <c r="C25" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D25" s="695">
+      <c r="D25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E25" s="695">
+      <c r="E25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F25" s="695">
+      <c r="F25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G25" s="695">
+      <c r="G25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H25" s="695">
+      <c r="H25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I25" s="695">
+      <c r="I25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J25" s="695">
+      <c r="J25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K25" s="695">
+      <c r="K25" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L25" s="681">
+      <c r="L25" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A25),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M25" s="682" t="n"/>
+      <c r="M25" s="683" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1" s="141">
-      <c r="A26" s="686" t="inlineStr">
+      <c r="A26" s="687" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="B26" s="687">
+      <c r="B26" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C26" s="689">
+      <c r="C26" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D26" s="696">
+      <c r="D26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E26" s="696">
+      <c r="E26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F26" s="696">
+      <c r="F26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G26" s="696">
+      <c r="G26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H26" s="696">
+      <c r="H26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I26" s="696">
+      <c r="I26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J26" s="696">
+      <c r="J26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K26" s="696">
+      <c r="K26" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L26" s="687">
+      <c r="L26" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A26),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M26" s="688" t="n"/>
+      <c r="M26" s="689" t="n"/>
     </row>
     <row r="27" ht="7.5" customHeight="1" s="141"/>
     <row r="28" ht="26" customHeight="1" s="141">
-      <c r="A28" s="677" t="inlineStr">
+      <c r="A28" s="678" t="inlineStr">
         <is>
           <t>FREE-FORM GROUP LOG  (confirmation groups, calibration, etc.)</t>
         </is>
@@ -24197,728 +24207,728 @@
       <c r="M28" s="279" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" s="141">
-      <c r="A29" s="680" t="n"/>
-      <c r="B29" s="681">
+      <c r="A29" s="681" t="n"/>
+      <c r="B29" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C29" s="683">
+      <c r="C29" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D29" s="695">
+      <c r="D29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E29" s="695">
+      <c r="E29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F29" s="695">
+      <c r="F29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G29" s="695">
+      <c r="G29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H29" s="695">
+      <c r="H29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I29" s="695">
+      <c r="I29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J29" s="695">
+      <c r="J29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K29" s="695">
+      <c r="K29" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L29" s="681">
+      <c r="L29" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A29),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M29" s="682" t="n"/>
+      <c r="M29" s="683" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" s="141">
-      <c r="A30" s="686" t="n"/>
-      <c r="B30" s="687">
+      <c r="A30" s="687" t="n"/>
+      <c r="B30" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C30" s="689">
+      <c r="C30" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D30" s="696">
+      <c r="D30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E30" s="696">
+      <c r="E30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F30" s="696">
+      <c r="F30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G30" s="696">
+      <c r="G30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H30" s="696">
+      <c r="H30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I30" s="696">
+      <c r="I30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J30" s="696">
+      <c r="J30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K30" s="696">
+      <c r="K30" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L30" s="687">
+      <c r="L30" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A30),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M30" s="688" t="n"/>
+      <c r="M30" s="689" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" s="141">
-      <c r="A31" s="680" t="n"/>
-      <c r="B31" s="681">
+      <c r="A31" s="681" t="n"/>
+      <c r="B31" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C31" s="683">
+      <c r="C31" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D31" s="695">
+      <c r="D31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E31" s="695">
+      <c r="E31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F31" s="695">
+      <c r="F31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G31" s="695">
+      <c r="G31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H31" s="695">
+      <c r="H31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I31" s="695">
+      <c r="I31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J31" s="695">
+      <c r="J31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K31" s="695">
+      <c r="K31" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L31" s="681">
+      <c r="L31" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A31),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M31" s="682" t="n"/>
+      <c r="M31" s="683" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" s="141">
-      <c r="A32" s="686" t="n"/>
-      <c r="B32" s="687">
+      <c r="A32" s="687" t="n"/>
+      <c r="B32" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C32" s="689">
+      <c r="C32" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D32" s="696">
+      <c r="D32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E32" s="696">
+      <c r="E32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F32" s="696">
+      <c r="F32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G32" s="696">
+      <c r="G32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H32" s="696">
+      <c r="H32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I32" s="696">
+      <c r="I32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J32" s="696">
+      <c r="J32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K32" s="696">
+      <c r="K32" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L32" s="687">
+      <c r="L32" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A32),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M32" s="688" t="n"/>
+      <c r="M32" s="689" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" s="141">
-      <c r="A33" s="680" t="n"/>
-      <c r="B33" s="681">
+      <c r="A33" s="681" t="n"/>
+      <c r="B33" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C33" s="683">
+      <c r="C33" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D33" s="695">
+      <c r="D33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E33" s="695">
+      <c r="E33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F33" s="695">
+      <c r="F33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G33" s="695">
+      <c r="G33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H33" s="695">
+      <c r="H33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I33" s="695">
+      <c r="I33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J33" s="695">
+      <c r="J33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K33" s="695">
+      <c r="K33" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L33" s="681">
+      <c r="L33" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A33),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M33" s="682" t="n"/>
+      <c r="M33" s="683" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" s="141">
-      <c r="A34" s="686" t="n"/>
-      <c r="B34" s="687">
+      <c r="A34" s="687" t="n"/>
+      <c r="B34" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C34" s="689">
+      <c r="C34" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D34" s="696">
+      <c r="D34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E34" s="696">
+      <c r="E34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F34" s="696">
+      <c r="F34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G34" s="696">
+      <c r="G34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H34" s="696">
+      <c r="H34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I34" s="696">
+      <c r="I34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J34" s="696">
+      <c r="J34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K34" s="696">
+      <c r="K34" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L34" s="687">
+      <c r="L34" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A34),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M34" s="688" t="n"/>
+      <c r="M34" s="689" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" s="141">
-      <c r="A35" s="680" t="n"/>
-      <c r="B35" s="681">
+      <c r="A35" s="681" t="n"/>
+      <c r="B35" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C35" s="683">
+      <c r="C35" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D35" s="695">
+      <c r="D35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E35" s="695">
+      <c r="E35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F35" s="695">
+      <c r="F35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G35" s="695">
+      <c r="G35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H35" s="695">
+      <c r="H35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I35" s="695">
+      <c r="I35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J35" s="695">
+      <c r="J35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K35" s="695">
+      <c r="K35" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L35" s="681">
+      <c r="L35" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A35),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M35" s="682" t="n"/>
+      <c r="M35" s="683" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" s="141">
-      <c r="A36" s="686" t="n"/>
-      <c r="B36" s="687">
+      <c r="A36" s="687" t="n"/>
+      <c r="B36" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C36" s="689">
+      <c r="C36" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D36" s="696">
+      <c r="D36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E36" s="696">
+      <c r="E36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F36" s="696">
+      <c r="F36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G36" s="696">
+      <c r="G36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H36" s="696">
+      <c r="H36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I36" s="696">
+      <c r="I36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J36" s="696">
+      <c r="J36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K36" s="696">
+      <c r="K36" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L36" s="687">
+      <c r="L36" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A36),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M36" s="688" t="n"/>
+      <c r="M36" s="689" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" s="141">
-      <c r="A37" s="680" t="n"/>
-      <c r="B37" s="681">
+      <c r="A37" s="681" t="n"/>
+      <c r="B37" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C37" s="683">
+      <c r="C37" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D37" s="695">
+      <c r="D37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E37" s="695">
+      <c r="E37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F37" s="695">
+      <c r="F37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G37" s="695">
+      <c r="G37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H37" s="695">
+      <c r="H37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I37" s="695">
+      <c r="I37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J37" s="695">
+      <c r="J37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K37" s="695">
+      <c r="K37" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L37" s="681">
+      <c r="L37" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A37),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M37" s="682" t="n"/>
+      <c r="M37" s="683" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1" s="141">
-      <c r="A38" s="686" t="n"/>
-      <c r="B38" s="687">
+      <c r="A38" s="687" t="n"/>
+      <c r="B38" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C38" s="689">
+      <c r="C38" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D38" s="696">
+      <c r="D38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E38" s="696">
+      <c r="E38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F38" s="696">
+      <c r="F38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G38" s="696">
+      <c r="G38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H38" s="696">
+      <c r="H38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I38" s="696">
+      <c r="I38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J38" s="696">
+      <c r="J38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K38" s="696">
+      <c r="K38" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L38" s="687">
+      <c r="L38" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A38),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M38" s="688" t="n"/>
+      <c r="M38" s="689" t="n"/>
     </row>
     <row r="39" ht="18.75" customHeight="1" s="141">
-      <c r="A39" s="680" t="n"/>
-      <c r="B39" s="681">
+      <c r="A39" s="681" t="n"/>
+      <c r="B39" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C39" s="683">
+      <c r="C39" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D39" s="695">
+      <c r="D39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E39" s="695">
+      <c r="E39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F39" s="695">
+      <c r="F39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G39" s="695">
+      <c r="G39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H39" s="695">
+      <c r="H39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I39" s="695">
+      <c r="I39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J39" s="695">
+      <c r="J39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K39" s="695">
+      <c r="K39" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L39" s="681">
+      <c r="L39" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A39),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M39" s="682" t="n"/>
+      <c r="M39" s="683" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" s="141">
-      <c r="A40" s="686" t="n"/>
-      <c r="B40" s="687">
+      <c r="A40" s="687" t="n"/>
+      <c r="B40" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C40" s="689">
+      <c r="C40" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D40" s="696">
+      <c r="D40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E40" s="696">
+      <c r="E40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F40" s="696">
+      <c r="F40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G40" s="696">
+      <c r="G40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H40" s="696">
+      <c r="H40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I40" s="696">
+      <c r="I40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J40" s="696">
+      <c r="J40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K40" s="696">
+      <c r="K40" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L40" s="687">
+      <c r="L40" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A40),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M40" s="688" t="n"/>
+      <c r="M40" s="689" t="n"/>
     </row>
     <row r="41" ht="18.75" customHeight="1" s="141">
-      <c r="A41" s="680" t="n"/>
-      <c r="B41" s="681">
+      <c r="A41" s="681" t="n"/>
+      <c r="B41" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C41" s="683">
+      <c r="C41" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D41" s="695">
+      <c r="D41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E41" s="695">
+      <c r="E41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F41" s="695">
+      <c r="F41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G41" s="695">
+      <c r="G41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H41" s="695">
+      <c r="H41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I41" s="695">
+      <c r="I41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J41" s="695">
+      <c r="J41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K41" s="695">
+      <c r="K41" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L41" s="681">
+      <c r="L41" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A41),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M41" s="682" t="n"/>
+      <c r="M41" s="683" t="n"/>
     </row>
     <row r="42" ht="18.75" customHeight="1" s="141">
-      <c r="A42" s="686" t="n"/>
-      <c r="B42" s="687">
+      <c r="A42" s="687" t="n"/>
+      <c r="B42" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C42" s="689">
+      <c r="C42" s="690">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D42" s="696">
+      <c r="D42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E42" s="696">
+      <c r="E42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F42" s="696">
+      <c r="F42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G42" s="696">
+      <c r="G42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H42" s="696">
+      <c r="H42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I42" s="696">
+      <c r="I42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J42" s="696">
+      <c r="J42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K42" s="696">
+      <c r="K42" s="697">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L42" s="687">
+      <c r="L42" s="688">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A42),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M42" s="688" t="n"/>
+      <c r="M42" s="689" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" s="141">
-      <c r="A43" s="680" t="n"/>
-      <c r="B43" s="681">
+      <c r="A43" s="681" t="n"/>
+      <c r="B43" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$D$2:$D$200),"")</f>
         <v/>
       </c>
-      <c r="C43" s="683">
+      <c r="C43" s="684">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$E$2:$E$200),"")</f>
         <v/>
       </c>
-      <c r="D43" s="695">
+      <c r="D43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$G$2:$G$200),"")</f>
         <v/>
       </c>
-      <c r="E43" s="695">
+      <c r="E43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$H$2:$H$200),"")</f>
         <v/>
       </c>
-      <c r="F43" s="695">
+      <c r="F43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$I$2:$I$200),"")</f>
         <v/>
       </c>
-      <c r="G43" s="695">
+      <c r="G43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$J$2:$J$200),"")</f>
         <v/>
       </c>
-      <c r="H43" s="695">
+      <c r="H43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$K$2:$K$200),"")</f>
         <v/>
       </c>
-      <c r="I43" s="695">
+      <c r="I43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$L$2:$L$200),"")</f>
         <v/>
       </c>
-      <c r="J43" s="695">
+      <c r="J43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$M$2:$M$200),"")</f>
         <v/>
       </c>
-      <c r="K43" s="695">
+      <c r="K43" s="696">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$N$2:$N$200),"")</f>
         <v/>
       </c>
-      <c r="L43" s="681">
+      <c r="L43" s="682">
         <f>IFERROR(LOOKUP(2,1/(BallisticXGroups!$A$2:$A$200=$A43),BallisticXGroups!$F$2:$F$200),"")</f>
         <v/>
       </c>
-      <c r="M43" s="682" t="n"/>
+      <c r="M43" s="683" t="n"/>
     </row>
     <row r="44"/>
     <row r="45" ht="26" customHeight="1" s="141">
-      <c r="A45" s="677" t="inlineStr">
+      <c r="A45" s="678" t="inlineStr">
         <is>
           <t>HOW THE WIRING WORKS</t>
         </is>
@@ -25169,10 +25179,10 @@
       <c r="A5" s="247" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="697" t="n">
+      <c r="B5" s="698" t="n">
         <v>46143</v>
       </c>
-      <c r="C5" s="698" t="inlineStr">
+      <c r="C5" s="699" t="inlineStr">
         <is>
           <t>6.5 CM 140 ELD-M / H4350 42.4 / 0.035 jump</t>
         </is>
@@ -25226,7 +25236,7 @@
       <c r="P5" s="268" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q5" s="699" t="inlineStr">
+      <c r="Q5" s="700" t="inlineStr">
         <is>
           <t>Confirmed at 100 yd, 65°F, 1500 ft DA. 10-shot string.</t>
         </is>
@@ -25245,10 +25255,10 @@
       <c r="A6" s="184" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="700" t="n">
+      <c r="B6" s="701" t="n">
         <v>45971</v>
       </c>
-      <c r="C6" s="701" t="inlineStr">
+      <c r="C6" s="702" t="inlineStr">
         <is>
           <t>6.5 CM 140 Berger Hybrid / H4350 42.1 / 0.020 jump</t>
         </is>
@@ -25302,7 +25312,7 @@
       <c r="P6" s="189" t="n">
         <v>0.24</v>
       </c>
-      <c r="Q6" s="702" t="inlineStr">
+      <c r="Q6" s="703" t="inlineStr">
         <is>
           <t>Prior season — switched to ELD-M for lower SD.</t>
         </is>
@@ -25321,10 +25331,10 @@
       <c r="A7" s="247" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="697" t="n">
+      <c r="B7" s="698" t="n">
         <v>46099</v>
       </c>
-      <c r="C7" s="698" t="inlineStr">
+      <c r="C7" s="699" t="inlineStr">
         <is>
           <t>6 ARC 108 ELD-M / CFE 223 26.5 / 0.040 jump</t>
         </is>
@@ -25378,7 +25388,7 @@
       <c r="P7" s="268" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q7" s="699" t="inlineStr">
+      <c r="Q7" s="700" t="inlineStr">
         <is>
           <t>Truck gun build. Good cold-bore consistency.</t>
         </is>
@@ -25396,7 +25406,7 @@
     <row r="8" ht="32" customHeight="1" s="141">
       <c r="A8" s="184" t="n"/>
       <c r="B8" s="184" t="n"/>
-      <c r="C8" s="701" t="n"/>
+      <c r="C8" s="702" t="n"/>
       <c r="D8" s="184" t="n"/>
       <c r="E8" s="184" t="n"/>
       <c r="F8" s="186" t="n"/>
@@ -25424,7 +25434,7 @@
     <row r="9" ht="32" customHeight="1" s="141">
       <c r="A9" s="247" t="n"/>
       <c r="B9" s="247" t="n"/>
-      <c r="C9" s="698" t="n"/>
+      <c r="C9" s="699" t="n"/>
       <c r="D9" s="247" t="n"/>
       <c r="E9" s="239" t="n"/>
       <c r="F9" s="245" t="n"/>
@@ -25452,7 +25462,7 @@
     <row r="10" ht="32" customHeight="1" s="141">
       <c r="A10" s="184" t="n"/>
       <c r="B10" s="184" t="n"/>
-      <c r="C10" s="701" t="n"/>
+      <c r="C10" s="702" t="n"/>
       <c r="D10" s="184" t="n"/>
       <c r="E10" s="184" t="n"/>
       <c r="F10" s="186" t="n"/>
@@ -25480,7 +25490,7 @@
     <row r="11" ht="32" customHeight="1" s="141">
       <c r="A11" s="247" t="n"/>
       <c r="B11" s="247" t="n"/>
-      <c r="C11" s="698" t="n"/>
+      <c r="C11" s="699" t="n"/>
       <c r="D11" s="247" t="n"/>
       <c r="E11" s="239" t="n"/>
       <c r="F11" s="245" t="n"/>
@@ -25508,7 +25518,7 @@
     <row r="12" ht="32" customHeight="1" s="141">
       <c r="A12" s="184" t="n"/>
       <c r="B12" s="184" t="n"/>
-      <c r="C12" s="701" t="n"/>
+      <c r="C12" s="702" t="n"/>
       <c r="D12" s="184" t="n"/>
       <c r="E12" s="184" t="n"/>
       <c r="F12" s="186" t="n"/>
@@ -25536,7 +25546,7 @@
     <row r="13" ht="32" customHeight="1" s="141">
       <c r="A13" s="247" t="n"/>
       <c r="B13" s="247" t="n"/>
-      <c r="C13" s="698" t="n"/>
+      <c r="C13" s="699" t="n"/>
       <c r="D13" s="247" t="n"/>
       <c r="E13" s="239" t="n"/>
       <c r="F13" s="245" t="n"/>
@@ -25564,7 +25574,7 @@
     <row r="14" ht="32" customHeight="1" s="141">
       <c r="A14" s="184" t="n"/>
       <c r="B14" s="184" t="n"/>
-      <c r="C14" s="701" t="n"/>
+      <c r="C14" s="702" t="n"/>
       <c r="D14" s="184" t="n"/>
       <c r="E14" s="184" t="n"/>
       <c r="F14" s="186" t="n"/>
@@ -25754,9 +25764,15 @@
       <c r="J2" s="631" t="n"/>
       <c r="K2" s="632" t="n"/>
     </row>
-    <row r="3" ht="6" customHeight="1" s="141"/>
+    <row r="3" ht="22" customHeight="1" s="141">
+      <c r="A3" s="635" t="inlineStr">
+        <is>
+          <t>→  Print This Workbook  ←</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="36" customHeight="1" s="141">
-      <c r="A4" s="703" t="inlineStr">
+      <c r="A4" s="704" t="inlineStr">
         <is>
           <t>📍  After your range session — type the elevation and wind values you dialed at each distance into the columns below. Click counts fill in automatically.</t>
         </is>
@@ -25778,7 +25794,7 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B5" s="704" t="inlineStr">
+      <c r="B5" s="705" t="inlineStr">
         <is>
           <t>Tikka T3X CTR 6.5 CM</t>
         </is>
@@ -25789,7 +25805,7 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E5" s="705" t="inlineStr">
+      <c r="E5" s="706" t="inlineStr">
         <is>
           <t>Hornady 140gr ELD-M</t>
         </is>
@@ -25800,7 +25816,7 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H5" s="705" t="n">
+      <c r="H5" s="706" t="n">
         <v>42.4</v>
       </c>
       <c r="I5" s="271" t="n"/>
@@ -25809,7 +25825,7 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K5" s="705" t="n">
+      <c r="K5" s="706" t="n">
         <v>2780</v>
       </c>
     </row>
@@ -25819,7 +25835,7 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B6" s="706" t="inlineStr">
+      <c r="B6" s="707" t="inlineStr">
         <is>
           <t>Leupold Mark 5HD 5-25x56</t>
         </is>
@@ -25855,7 +25871,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="141">
-      <c r="A7" s="707" t="inlineStr">
+      <c r="A7" s="708" t="inlineStr">
         <is>
           <t>↓  Type your dialed Mils or MOA into the columns below — click counts auto-fill in the gray columns next to each.</t>
         </is>
@@ -25921,34 +25937,34 @@
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" s="141">
-      <c r="A9" s="708" t="n">
+      <c r="A9" s="709" t="n">
         <v>100</v>
       </c>
       <c r="B9" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="709">
+      <c r="C9" s="710">
         <f>IF(B9="","",IF('Load Log'!$G$7="0.1 Mil",B9*10,IF('Load Log'!$G$7="0.05 Mil",B9*20,"")))</f>
         <v/>
       </c>
       <c r="D9" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="709">
+      <c r="E9" s="710">
         <f>IF(D9="","",IF('Load Log'!$G$7="1/4 MOA",D9*4,IF('Load Log'!$G$7="1/8 MOA",D9*8,"")))</f>
         <v/>
       </c>
       <c r="F9" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="709">
+      <c r="G9" s="710">
         <f>IF(F9="","",IF('Load Log'!$G$7="0.1 Mil",F9*10,IF('Load Log'!$G$7="0.05 Mil",F9*20,"")))</f>
         <v/>
       </c>
       <c r="H9" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="709">
+      <c r="I9" s="710">
         <f>IF(H9="","",IF('Load Log'!$G$7="1/4 MOA",H9*4,IF('Load Log'!$G$7="1/8 MOA",H9*8,"")))</f>
         <v/>
       </c>
@@ -25958,34 +25974,34 @@
       <c r="K9" s="276" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" s="141">
-      <c r="A10" s="710" t="n">
+      <c r="A10" s="711" t="n">
         <v>200</v>
       </c>
       <c r="B10" s="185" t="n">
         <v>0.1</v>
       </c>
-      <c r="C10" s="711">
+      <c r="C10" s="712">
         <f>IF(B10="","",IF('Load Log'!$G$7="0.1 Mil",B10*10,IF('Load Log'!$G$7="0.05 Mil",B10*20,"")))</f>
         <v/>
       </c>
       <c r="D10" s="185" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="711">
+      <c r="E10" s="712">
         <f>IF(D10="","",IF('Load Log'!$G$7="1/4 MOA",D10*4,IF('Load Log'!$G$7="1/8 MOA",D10*8,"")))</f>
         <v/>
       </c>
       <c r="F10" s="185" t="n">
         <v>0.3</v>
       </c>
-      <c r="G10" s="711">
+      <c r="G10" s="712">
         <f>IF(F10="","",IF('Load Log'!$G$7="0.1 Mil",F10*10,IF('Load Log'!$G$7="0.05 Mil",F10*20,"")))</f>
         <v/>
       </c>
       <c r="H10" s="185" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="711">
+      <c r="I10" s="712">
         <f>IF(H10="","",IF('Load Log'!$G$7="1/4 MOA",H10*4,IF('Load Log'!$G$7="1/8 MOA",H10*8,"")))</f>
         <v/>
       </c>
@@ -25995,34 +26011,34 @@
       <c r="K10" s="277" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" s="141">
-      <c r="A11" s="708" t="n">
+      <c r="A11" s="709" t="n">
         <v>300</v>
       </c>
       <c r="B11" s="178" t="n">
         <v>0.6</v>
       </c>
-      <c r="C11" s="709">
+      <c r="C11" s="710">
         <f>IF(B11="","",IF('Load Log'!$G$7="0.1 Mil",B11*10,IF('Load Log'!$G$7="0.05 Mil",B11*20,"")))</f>
         <v/>
       </c>
       <c r="D11" s="178" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="709">
+      <c r="E11" s="710">
         <f>IF(D11="","",IF('Load Log'!$G$7="1/4 MOA",D11*4,IF('Load Log'!$G$7="1/8 MOA",D11*8,"")))</f>
         <v/>
       </c>
       <c r="F11" s="178" t="n">
         <v>0.5</v>
       </c>
-      <c r="G11" s="709">
+      <c r="G11" s="710">
         <f>IF(F11="","",IF('Load Log'!$G$7="0.1 Mil",F11*10,IF('Load Log'!$G$7="0.05 Mil",F11*20,"")))</f>
         <v/>
       </c>
       <c r="H11" s="178" t="n">
         <v>1.7</v>
       </c>
-      <c r="I11" s="709">
+      <c r="I11" s="710">
         <f>IF(H11="","",IF('Load Log'!$G$7="1/4 MOA",H11*4,IF('Load Log'!$G$7="1/8 MOA",H11*8,"")))</f>
         <v/>
       </c>
@@ -26032,34 +26048,34 @@
       <c r="K11" s="276" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1" s="141">
-      <c r="A12" s="710" t="n">
+      <c r="A12" s="711" t="n">
         <v>400</v>
       </c>
       <c r="B12" s="185" t="n">
         <v>1.2</v>
       </c>
-      <c r="C12" s="711">
+      <c r="C12" s="712">
         <f>IF(B12="","",IF('Load Log'!$G$7="0.1 Mil",B12*10,IF('Load Log'!$G$7="0.05 Mil",B12*20,"")))</f>
         <v/>
       </c>
       <c r="D12" s="185" t="n">
         <v>4.1</v>
       </c>
-      <c r="E12" s="711">
+      <c r="E12" s="712">
         <f>IF(D12="","",IF('Load Log'!$G$7="1/4 MOA",D12*4,IF('Load Log'!$G$7="1/8 MOA",D12*8,"")))</f>
         <v/>
       </c>
       <c r="F12" s="185" t="n">
         <v>0.7</v>
       </c>
-      <c r="G12" s="711">
+      <c r="G12" s="712">
         <f>IF(F12="","",IF('Load Log'!$G$7="0.1 Mil",F12*10,IF('Load Log'!$G$7="0.05 Mil",F12*20,"")))</f>
         <v/>
       </c>
       <c r="H12" s="185" t="n">
         <v>2.4</v>
       </c>
-      <c r="I12" s="711">
+      <c r="I12" s="712">
         <f>IF(H12="","",IF('Load Log'!$G$7="1/4 MOA",H12*4,IF('Load Log'!$G$7="1/8 MOA",H12*8,"")))</f>
         <v/>
       </c>
@@ -26069,34 +26085,34 @@
       <c r="K12" s="277" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1" s="141">
-      <c r="A13" s="708" t="n">
+      <c r="A13" s="709" t="n">
         <v>500</v>
       </c>
       <c r="B13" s="178" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="709">
+      <c r="C13" s="710">
         <f>IF(B13="","",IF('Load Log'!$G$7="0.1 Mil",B13*10,IF('Load Log'!$G$7="0.05 Mil",B13*20,"")))</f>
         <v/>
       </c>
       <c r="D13" s="178" t="n">
         <v>6.9</v>
       </c>
-      <c r="E13" s="709">
+      <c r="E13" s="710">
         <f>IF(D13="","",IF('Load Log'!$G$7="1/4 MOA",D13*4,IF('Load Log'!$G$7="1/8 MOA",D13*8,"")))</f>
         <v/>
       </c>
       <c r="F13" s="178" t="n">
         <v>0.9</v>
       </c>
-      <c r="G13" s="709">
+      <c r="G13" s="710">
         <f>IF(F13="","",IF('Load Log'!$G$7="0.1 Mil",F13*10,IF('Load Log'!$G$7="0.05 Mil",F13*20,"")))</f>
         <v/>
       </c>
       <c r="H13" s="178" t="n">
         <v>3.1</v>
       </c>
-      <c r="I13" s="709">
+      <c r="I13" s="710">
         <f>IF(H13="","",IF('Load Log'!$G$7="1/4 MOA",H13*4,IF('Load Log'!$G$7="1/8 MOA",H13*8,"")))</f>
         <v/>
       </c>
@@ -26106,34 +26122,34 @@
       <c r="K13" s="276" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" s="141">
-      <c r="A14" s="710" t="n">
+      <c r="A14" s="711" t="n">
         <v>600</v>
       </c>
       <c r="B14" s="185" t="n">
         <v>2.8</v>
       </c>
-      <c r="C14" s="711">
+      <c r="C14" s="712">
         <f>IF(B14="","",IF('Load Log'!$G$7="0.1 Mil",B14*10,IF('Load Log'!$G$7="0.05 Mil",B14*20,"")))</f>
         <v/>
       </c>
       <c r="D14" s="185" t="n">
         <v>9.6</v>
       </c>
-      <c r="E14" s="711">
+      <c r="E14" s="712">
         <f>IF(D14="","",IF('Load Log'!$G$7="1/4 MOA",D14*4,IF('Load Log'!$G$7="1/8 MOA",D14*8,"")))</f>
         <v/>
       </c>
       <c r="F14" s="185" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" s="711">
+      <c r="G14" s="712">
         <f>IF(F14="","",IF('Load Log'!$G$7="0.1 Mil",F14*10,IF('Load Log'!$G$7="0.05 Mil",F14*20,"")))</f>
         <v/>
       </c>
       <c r="H14" s="185" t="n">
         <v>4.1</v>
       </c>
-      <c r="I14" s="711">
+      <c r="I14" s="712">
         <f>IF(H14="","",IF('Load Log'!$G$7="1/4 MOA",H14*4,IF('Load Log'!$G$7="1/8 MOA",H14*8,"")))</f>
         <v/>
       </c>
@@ -26143,34 +26159,34 @@
       <c r="K14" s="277" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" s="141">
-      <c r="A15" s="708" t="n">
+      <c r="A15" s="709" t="n">
         <v>700</v>
       </c>
       <c r="B15" s="178" t="n">
         <v>3.7</v>
       </c>
-      <c r="C15" s="709">
+      <c r="C15" s="710">
         <f>IF(B15="","",IF('Load Log'!$G$7="0.1 Mil",B15*10,IF('Load Log'!$G$7="0.05 Mil",B15*20,"")))</f>
         <v/>
       </c>
       <c r="D15" s="178" t="n">
         <v>12.7</v>
       </c>
-      <c r="E15" s="709">
+      <c r="E15" s="710">
         <f>IF(D15="","",IF('Load Log'!$G$7="1/4 MOA",D15*4,IF('Load Log'!$G$7="1/8 MOA",D15*8,"")))</f>
         <v/>
       </c>
       <c r="F15" s="178" t="n">
         <v>1.5</v>
       </c>
-      <c r="G15" s="709">
+      <c r="G15" s="710">
         <f>IF(F15="","",IF('Load Log'!$G$7="0.1 Mil",F15*10,IF('Load Log'!$G$7="0.05 Mil",F15*20,"")))</f>
         <v/>
       </c>
       <c r="H15" s="178" t="n">
         <v>5.1</v>
       </c>
-      <c r="I15" s="709">
+      <c r="I15" s="710">
         <f>IF(H15="","",IF('Load Log'!$G$7="1/4 MOA",H15*4,IF('Load Log'!$G$7="1/8 MOA",H15*8,"")))</f>
         <v/>
       </c>
@@ -26180,34 +26196,34 @@
       <c r="K15" s="276" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" s="141">
-      <c r="A16" s="710" t="n">
+      <c r="A16" s="711" t="n">
         <v>800</v>
       </c>
       <c r="B16" s="185" t="n">
         <v>4.8</v>
       </c>
-      <c r="C16" s="711">
+      <c r="C16" s="712">
         <f>IF(B16="","",IF('Load Log'!$G$7="0.1 Mil",B16*10,IF('Load Log'!$G$7="0.05 Mil",B16*20,"")))</f>
         <v/>
       </c>
       <c r="D16" s="185" t="n">
         <v>16.5</v>
       </c>
-      <c r="E16" s="711">
+      <c r="E16" s="712">
         <f>IF(D16="","",IF('Load Log'!$G$7="1/4 MOA",D16*4,IF('Load Log'!$G$7="1/8 MOA",D16*8,"")))</f>
         <v/>
       </c>
       <c r="F16" s="185" t="n">
         <v>1.8</v>
       </c>
-      <c r="G16" s="711">
+      <c r="G16" s="712">
         <f>IF(F16="","",IF('Load Log'!$G$7="0.1 Mil",F16*10,IF('Load Log'!$G$7="0.05 Mil",F16*20,"")))</f>
         <v/>
       </c>
       <c r="H16" s="185" t="n">
         <v>6.2</v>
       </c>
-      <c r="I16" s="711">
+      <c r="I16" s="712">
         <f>IF(H16="","",IF('Load Log'!$G$7="1/4 MOA",H16*4,IF('Load Log'!$G$7="1/8 MOA",H16*8,"")))</f>
         <v/>
       </c>
@@ -26217,34 +26233,34 @@
       <c r="K16" s="277" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" s="141">
-      <c r="A17" s="708" t="n">
+      <c r="A17" s="709" t="n">
         <v>900</v>
       </c>
       <c r="B17" s="178" t="n">
         <v>6</v>
       </c>
-      <c r="C17" s="709">
+      <c r="C17" s="710">
         <f>IF(B17="","",IF('Load Log'!$G$7="0.1 Mil",B17*10,IF('Load Log'!$G$7="0.05 Mil",B17*20,"")))</f>
         <v/>
       </c>
       <c r="D17" s="178" t="n">
         <v>20.6</v>
       </c>
-      <c r="E17" s="709">
+      <c r="E17" s="710">
         <f>IF(D17="","",IF('Load Log'!$G$7="1/4 MOA",D17*4,IF('Load Log'!$G$7="1/8 MOA",D17*8,"")))</f>
         <v/>
       </c>
       <c r="F17" s="178" t="n">
         <v>2.1</v>
       </c>
-      <c r="G17" s="709">
+      <c r="G17" s="710">
         <f>IF(F17="","",IF('Load Log'!$G$7="0.1 Mil",F17*10,IF('Load Log'!$G$7="0.05 Mil",F17*20,"")))</f>
         <v/>
       </c>
       <c r="H17" s="178" t="n">
         <v>7.2</v>
       </c>
-      <c r="I17" s="709">
+      <c r="I17" s="710">
         <f>IF(H17="","",IF('Load Log'!$G$7="1/4 MOA",H17*4,IF('Load Log'!$G$7="1/8 MOA",H17*8,"")))</f>
         <v/>
       </c>
@@ -26254,34 +26270,34 @@
       <c r="K17" s="276" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" s="141">
-      <c r="A18" s="710" t="n">
+      <c r="A18" s="711" t="n">
         <v>1000</v>
       </c>
       <c r="B18" s="185" t="n">
         <v>7.3</v>
       </c>
-      <c r="C18" s="711">
+      <c r="C18" s="712">
         <f>IF(B18="","",IF('Load Log'!$G$7="0.1 Mil",B18*10,IF('Load Log'!$G$7="0.05 Mil",B18*20,"")))</f>
         <v/>
       </c>
       <c r="D18" s="185" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="711">
+      <c r="E18" s="712">
         <f>IF(D18="","",IF('Load Log'!$G$7="1/4 MOA",D18*4,IF('Load Log'!$G$7="1/8 MOA",D18*8,"")))</f>
         <v/>
       </c>
       <c r="F18" s="185" t="n">
         <v>2.4</v>
       </c>
-      <c r="G18" s="711">
+      <c r="G18" s="712">
         <f>IF(F18="","",IF('Load Log'!$G$7="0.1 Mil",F18*10,IF('Load Log'!$G$7="0.05 Mil",F18*20,"")))</f>
         <v/>
       </c>
       <c r="H18" s="185" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I18" s="711">
+      <c r="I18" s="712">
         <f>IF(H18="","",IF('Load Log'!$G$7="1/4 MOA",H18*4,IF('Load Log'!$G$7="1/8 MOA",H18*8,"")))</f>
         <v/>
       </c>
@@ -26294,7 +26310,7 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22" ht="24" customHeight="1" s="141">
-      <c r="A22" s="712">
+      <c r="A22" s="713">
         <f>IF(IFERROR('Load Library'!C6,"")="","LOAD #2  —  (empty — fill in Load Library row 6)","LOAD #2  —  "&amp;'Load Library'!C6)</f>
         <v/>
       </c>
@@ -26305,7 +26321,7 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B23" s="705">
+      <c r="B23" s="706">
         <f>IF(IFERROR('Load Library'!D6,"")="","",'Load Library'!D6)</f>
         <v/>
       </c>
@@ -26315,7 +26331,7 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E23" s="705">
+      <c r="E23" s="706">
         <f>IF(IFERROR('Load Library'!E6,"")="","",'Load Library'!E6&amp;" ("&amp;'Load Library'!F6&amp;"gr)")</f>
         <v/>
       </c>
@@ -26325,7 +26341,7 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H23" s="705">
+      <c r="H23" s="706">
         <f>IF(IFERROR('Load Library'!H6,"")="","",'Load Library'!H6&amp;" gr "&amp;'Load Library'!G6)</f>
         <v/>
       </c>
@@ -26335,7 +26351,7 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K23" s="705">
+      <c r="K23" s="706">
         <f>IF(IFERROR('Load Library'!M6,"")="","",'Load Library'!M6&amp;" fps")</f>
         <v/>
       </c>
@@ -26436,26 +26452,26 @@
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1" s="141">
-      <c r="A27" s="708" t="n">
+      <c r="A27" s="709" t="n">
         <v>100</v>
       </c>
       <c r="B27" s="178" t="n"/>
-      <c r="C27" s="709">
+      <c r="C27" s="710">
         <f>IF(B27="","",IF('Load Log'!$G$7="0.1 Mil",B27*10,IF('Load Log'!$G$7="0.05 Mil",B27*20,"")))</f>
         <v/>
       </c>
       <c r="D27" s="178" t="n"/>
-      <c r="E27" s="709">
+      <c r="E27" s="710">
         <f>IF(D27="","",IF('Load Log'!$G$7="1/4 MOA",D27*4,IF('Load Log'!$G$7="1/8 MOA",D27*8,"")))</f>
         <v/>
       </c>
       <c r="F27" s="178" t="n"/>
-      <c r="G27" s="709">
+      <c r="G27" s="710">
         <f>IF(F27="","",IF('Load Log'!$G$7="0.1 Mil",F27*10,IF('Load Log'!$G$7="0.05 Mil",F27*20,"")))</f>
         <v/>
       </c>
       <c r="H27" s="178" t="n"/>
-      <c r="I27" s="709">
+      <c r="I27" s="710">
         <f>IF(H27="","",IF('Load Log'!$G$7="1/4 MOA",H27*4,IF('Load Log'!$G$7="1/8 MOA",H27*8,"")))</f>
         <v/>
       </c>
@@ -26463,26 +26479,26 @@
       <c r="K27" s="276" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1" s="141">
-      <c r="A28" s="710" t="n">
+      <c r="A28" s="711" t="n">
         <v>200</v>
       </c>
       <c r="B28" s="185" t="n"/>
-      <c r="C28" s="711">
+      <c r="C28" s="712">
         <f>IF(B28="","",IF('Load Log'!$G$7="0.1 Mil",B28*10,IF('Load Log'!$G$7="0.05 Mil",B28*20,"")))</f>
         <v/>
       </c>
       <c r="D28" s="185" t="n"/>
-      <c r="E28" s="711">
+      <c r="E28" s="712">
         <f>IF(D28="","",IF('Load Log'!$G$7="1/4 MOA",D28*4,IF('Load Log'!$G$7="1/8 MOA",D28*8,"")))</f>
         <v/>
       </c>
       <c r="F28" s="185" t="n"/>
-      <c r="G28" s="711">
+      <c r="G28" s="712">
         <f>IF(F28="","",IF('Load Log'!$G$7="0.1 Mil",F28*10,IF('Load Log'!$G$7="0.05 Mil",F28*20,"")))</f>
         <v/>
       </c>
       <c r="H28" s="185" t="n"/>
-      <c r="I28" s="711">
+      <c r="I28" s="712">
         <f>IF(H28="","",IF('Load Log'!$G$7="1/4 MOA",H28*4,IF('Load Log'!$G$7="1/8 MOA",H28*8,"")))</f>
         <v/>
       </c>
@@ -26490,26 +26506,26 @@
       <c r="K28" s="277" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" s="141">
-      <c r="A29" s="708" t="n">
+      <c r="A29" s="709" t="n">
         <v>300</v>
       </c>
       <c r="B29" s="178" t="n"/>
-      <c r="C29" s="709">
+      <c r="C29" s="710">
         <f>IF(B29="","",IF('Load Log'!$G$7="0.1 Mil",B29*10,IF('Load Log'!$G$7="0.05 Mil",B29*20,"")))</f>
         <v/>
       </c>
       <c r="D29" s="178" t="n"/>
-      <c r="E29" s="709">
+      <c r="E29" s="710">
         <f>IF(D29="","",IF('Load Log'!$G$7="1/4 MOA",D29*4,IF('Load Log'!$G$7="1/8 MOA",D29*8,"")))</f>
         <v/>
       </c>
       <c r="F29" s="178" t="n"/>
-      <c r="G29" s="709">
+      <c r="G29" s="710">
         <f>IF(F29="","",IF('Load Log'!$G$7="0.1 Mil",F29*10,IF('Load Log'!$G$7="0.05 Mil",F29*20,"")))</f>
         <v/>
       </c>
       <c r="H29" s="178" t="n"/>
-      <c r="I29" s="709">
+      <c r="I29" s="710">
         <f>IF(H29="","",IF('Load Log'!$G$7="1/4 MOA",H29*4,IF('Load Log'!$G$7="1/8 MOA",H29*8,"")))</f>
         <v/>
       </c>
@@ -26517,26 +26533,26 @@
       <c r="K29" s="276" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" s="141">
-      <c r="A30" s="710" t="n">
+      <c r="A30" s="711" t="n">
         <v>400</v>
       </c>
       <c r="B30" s="185" t="n"/>
-      <c r="C30" s="711">
+      <c r="C30" s="712">
         <f>IF(B30="","",IF('Load Log'!$G$7="0.1 Mil",B30*10,IF('Load Log'!$G$7="0.05 Mil",B30*20,"")))</f>
         <v/>
       </c>
       <c r="D30" s="185" t="n"/>
-      <c r="E30" s="711">
+      <c r="E30" s="712">
         <f>IF(D30="","",IF('Load Log'!$G$7="1/4 MOA",D30*4,IF('Load Log'!$G$7="1/8 MOA",D30*8,"")))</f>
         <v/>
       </c>
       <c r="F30" s="185" t="n"/>
-      <c r="G30" s="711">
+      <c r="G30" s="712">
         <f>IF(F30="","",IF('Load Log'!$G$7="0.1 Mil",F30*10,IF('Load Log'!$G$7="0.05 Mil",F30*20,"")))</f>
         <v/>
       </c>
       <c r="H30" s="185" t="n"/>
-      <c r="I30" s="711">
+      <c r="I30" s="712">
         <f>IF(H30="","",IF('Load Log'!$G$7="1/4 MOA",H30*4,IF('Load Log'!$G$7="1/8 MOA",H30*8,"")))</f>
         <v/>
       </c>
@@ -26544,26 +26560,26 @@
       <c r="K30" s="277" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" s="141">
-      <c r="A31" s="708" t="n">
+      <c r="A31" s="709" t="n">
         <v>500</v>
       </c>
       <c r="B31" s="178" t="n"/>
-      <c r="C31" s="709">
+      <c r="C31" s="710">
         <f>IF(B31="","",IF('Load Log'!$G$7="0.1 Mil",B31*10,IF('Load Log'!$G$7="0.05 Mil",B31*20,"")))</f>
         <v/>
       </c>
       <c r="D31" s="178" t="n"/>
-      <c r="E31" s="709">
+      <c r="E31" s="710">
         <f>IF(D31="","",IF('Load Log'!$G$7="1/4 MOA",D31*4,IF('Load Log'!$G$7="1/8 MOA",D31*8,"")))</f>
         <v/>
       </c>
       <c r="F31" s="178" t="n"/>
-      <c r="G31" s="709">
+      <c r="G31" s="710">
         <f>IF(F31="","",IF('Load Log'!$G$7="0.1 Mil",F31*10,IF('Load Log'!$G$7="0.05 Mil",F31*20,"")))</f>
         <v/>
       </c>
       <c r="H31" s="178" t="n"/>
-      <c r="I31" s="709">
+      <c r="I31" s="710">
         <f>IF(H31="","",IF('Load Log'!$G$7="1/4 MOA",H31*4,IF('Load Log'!$G$7="1/8 MOA",H31*8,"")))</f>
         <v/>
       </c>
@@ -26571,26 +26587,26 @@
       <c r="K31" s="276" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" s="141">
-      <c r="A32" s="710" t="n">
+      <c r="A32" s="711" t="n">
         <v>600</v>
       </c>
       <c r="B32" s="185" t="n"/>
-      <c r="C32" s="711">
+      <c r="C32" s="712">
         <f>IF(B32="","",IF('Load Log'!$G$7="0.1 Mil",B32*10,IF('Load Log'!$G$7="0.05 Mil",B32*20,"")))</f>
         <v/>
       </c>
       <c r="D32" s="185" t="n"/>
-      <c r="E32" s="711">
+      <c r="E32" s="712">
         <f>IF(D32="","",IF('Load Log'!$G$7="1/4 MOA",D32*4,IF('Load Log'!$G$7="1/8 MOA",D32*8,"")))</f>
         <v/>
       </c>
       <c r="F32" s="185" t="n"/>
-      <c r="G32" s="711">
+      <c r="G32" s="712">
         <f>IF(F32="","",IF('Load Log'!$G$7="0.1 Mil",F32*10,IF('Load Log'!$G$7="0.05 Mil",F32*20,"")))</f>
         <v/>
       </c>
       <c r="H32" s="185" t="n"/>
-      <c r="I32" s="711">
+      <c r="I32" s="712">
         <f>IF(H32="","",IF('Load Log'!$G$7="1/4 MOA",H32*4,IF('Load Log'!$G$7="1/8 MOA",H32*8,"")))</f>
         <v/>
       </c>
@@ -26598,26 +26614,26 @@
       <c r="K32" s="277" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" s="141">
-      <c r="A33" s="708" t="n">
+      <c r="A33" s="709" t="n">
         <v>700</v>
       </c>
       <c r="B33" s="178" t="n"/>
-      <c r="C33" s="709">
+      <c r="C33" s="710">
         <f>IF(B33="","",IF('Load Log'!$G$7="0.1 Mil",B33*10,IF('Load Log'!$G$7="0.05 Mil",B33*20,"")))</f>
         <v/>
       </c>
       <c r="D33" s="178" t="n"/>
-      <c r="E33" s="709">
+      <c r="E33" s="710">
         <f>IF(D33="","",IF('Load Log'!$G$7="1/4 MOA",D33*4,IF('Load Log'!$G$7="1/8 MOA",D33*8,"")))</f>
         <v/>
       </c>
       <c r="F33" s="178" t="n"/>
-      <c r="G33" s="709">
+      <c r="G33" s="710">
         <f>IF(F33="","",IF('Load Log'!$G$7="0.1 Mil",F33*10,IF('Load Log'!$G$7="0.05 Mil",F33*20,"")))</f>
         <v/>
       </c>
       <c r="H33" s="178" t="n"/>
-      <c r="I33" s="709">
+      <c r="I33" s="710">
         <f>IF(H33="","",IF('Load Log'!$G$7="1/4 MOA",H33*4,IF('Load Log'!$G$7="1/8 MOA",H33*8,"")))</f>
         <v/>
       </c>
@@ -26625,26 +26641,26 @@
       <c r="K33" s="276" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" s="141">
-      <c r="A34" s="710" t="n">
+      <c r="A34" s="711" t="n">
         <v>800</v>
       </c>
       <c r="B34" s="185" t="n"/>
-      <c r="C34" s="711">
+      <c r="C34" s="712">
         <f>IF(B34="","",IF('Load Log'!$G$7="0.1 Mil",B34*10,IF('Load Log'!$G$7="0.05 Mil",B34*20,"")))</f>
         <v/>
       </c>
       <c r="D34" s="185" t="n"/>
-      <c r="E34" s="711">
+      <c r="E34" s="712">
         <f>IF(D34="","",IF('Load Log'!$G$7="1/4 MOA",D34*4,IF('Load Log'!$G$7="1/8 MOA",D34*8,"")))</f>
         <v/>
       </c>
       <c r="F34" s="185" t="n"/>
-      <c r="G34" s="711">
+      <c r="G34" s="712">
         <f>IF(F34="","",IF('Load Log'!$G$7="0.1 Mil",F34*10,IF('Load Log'!$G$7="0.05 Mil",F34*20,"")))</f>
         <v/>
       </c>
       <c r="H34" s="185" t="n"/>
-      <c r="I34" s="711">
+      <c r="I34" s="712">
         <f>IF(H34="","",IF('Load Log'!$G$7="1/4 MOA",H34*4,IF('Load Log'!$G$7="1/8 MOA",H34*8,"")))</f>
         <v/>
       </c>
@@ -26652,26 +26668,26 @@
       <c r="K34" s="277" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" s="141">
-      <c r="A35" s="708" t="n">
+      <c r="A35" s="709" t="n">
         <v>900</v>
       </c>
       <c r="B35" s="178" t="n"/>
-      <c r="C35" s="709">
+      <c r="C35" s="710">
         <f>IF(B35="","",IF('Load Log'!$G$7="0.1 Mil",B35*10,IF('Load Log'!$G$7="0.05 Mil",B35*20,"")))</f>
         <v/>
       </c>
       <c r="D35" s="178" t="n"/>
-      <c r="E35" s="709">
+      <c r="E35" s="710">
         <f>IF(D35="","",IF('Load Log'!$G$7="1/4 MOA",D35*4,IF('Load Log'!$G$7="1/8 MOA",D35*8,"")))</f>
         <v/>
       </c>
       <c r="F35" s="178" t="n"/>
-      <c r="G35" s="709">
+      <c r="G35" s="710">
         <f>IF(F35="","",IF('Load Log'!$G$7="0.1 Mil",F35*10,IF('Load Log'!$G$7="0.05 Mil",F35*20,"")))</f>
         <v/>
       </c>
       <c r="H35" s="178" t="n"/>
-      <c r="I35" s="709">
+      <c r="I35" s="710">
         <f>IF(H35="","",IF('Load Log'!$G$7="1/4 MOA",H35*4,IF('Load Log'!$G$7="1/8 MOA",H35*8,"")))</f>
         <v/>
       </c>
@@ -26679,26 +26695,26 @@
       <c r="K35" s="276" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" s="141">
-      <c r="A36" s="710" t="n">
+      <c r="A36" s="711" t="n">
         <v>1000</v>
       </c>
       <c r="B36" s="185" t="n"/>
-      <c r="C36" s="711">
+      <c r="C36" s="712">
         <f>IF(B36="","",IF('Load Log'!$G$7="0.1 Mil",B36*10,IF('Load Log'!$G$7="0.05 Mil",B36*20,"")))</f>
         <v/>
       </c>
       <c r="D36" s="185" t="n"/>
-      <c r="E36" s="711">
+      <c r="E36" s="712">
         <f>IF(D36="","",IF('Load Log'!$G$7="1/4 MOA",D36*4,IF('Load Log'!$G$7="1/8 MOA",D36*8,"")))</f>
         <v/>
       </c>
       <c r="F36" s="185" t="n"/>
-      <c r="G36" s="711">
+      <c r="G36" s="712">
         <f>IF(F36="","",IF('Load Log'!$G$7="0.1 Mil",F36*10,IF('Load Log'!$G$7="0.05 Mil",F36*20,"")))</f>
         <v/>
       </c>
       <c r="H36" s="185" t="n"/>
-      <c r="I36" s="711">
+      <c r="I36" s="712">
         <f>IF(H36="","",IF('Load Log'!$G$7="1/4 MOA",H36*4,IF('Load Log'!$G$7="1/8 MOA",H36*8,"")))</f>
         <v/>
       </c>
@@ -26709,7 +26725,7 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40" ht="24" customHeight="1" s="141">
-      <c r="A40" s="712">
+      <c r="A40" s="713">
         <f>IF(IFERROR('Load Library'!C7,"")="","LOAD #3  —  (empty — fill in Load Library row 7)","LOAD #3  —  "&amp;'Load Library'!C7)</f>
         <v/>
       </c>
@@ -26720,7 +26736,7 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B41" s="705">
+      <c r="B41" s="706">
         <f>IF(IFERROR('Load Library'!D7,"")="","",'Load Library'!D7)</f>
         <v/>
       </c>
@@ -26730,7 +26746,7 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E41" s="705">
+      <c r="E41" s="706">
         <f>IF(IFERROR('Load Library'!E7,"")="","",'Load Library'!E7&amp;" ("&amp;'Load Library'!F7&amp;"gr)")</f>
         <v/>
       </c>
@@ -26740,7 +26756,7 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H41" s="705">
+      <c r="H41" s="706">
         <f>IF(IFERROR('Load Library'!H7,"")="","",'Load Library'!H7&amp;" gr "&amp;'Load Library'!G7)</f>
         <v/>
       </c>
@@ -26750,7 +26766,7 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K41" s="705">
+      <c r="K41" s="706">
         <f>IF(IFERROR('Load Library'!M7,"")="","",'Load Library'!M7&amp;" fps")</f>
         <v/>
       </c>
@@ -26851,26 +26867,26 @@
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1" s="141">
-      <c r="A45" s="708" t="n">
+      <c r="A45" s="709" t="n">
         <v>100</v>
       </c>
       <c r="B45" s="178" t="n"/>
-      <c r="C45" s="709">
+      <c r="C45" s="710">
         <f>IF(B45="","",IF('Load Log'!$G$7="0.1 Mil",B45*10,IF('Load Log'!$G$7="0.05 Mil",B45*20,"")))</f>
         <v/>
       </c>
       <c r="D45" s="178" t="n"/>
-      <c r="E45" s="709">
+      <c r="E45" s="710">
         <f>IF(D45="","",IF('Load Log'!$G$7="1/4 MOA",D45*4,IF('Load Log'!$G$7="1/8 MOA",D45*8,"")))</f>
         <v/>
       </c>
       <c r="F45" s="178" t="n"/>
-      <c r="G45" s="709">
+      <c r="G45" s="710">
         <f>IF(F45="","",IF('Load Log'!$G$7="0.1 Mil",F45*10,IF('Load Log'!$G$7="0.05 Mil",F45*20,"")))</f>
         <v/>
       </c>
       <c r="H45" s="178" t="n"/>
-      <c r="I45" s="709">
+      <c r="I45" s="710">
         <f>IF(H45="","",IF('Load Log'!$G$7="1/4 MOA",H45*4,IF('Load Log'!$G$7="1/8 MOA",H45*8,"")))</f>
         <v/>
       </c>
@@ -26878,26 +26894,26 @@
       <c r="K45" s="276" t="n"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" s="141">
-      <c r="A46" s="710" t="n">
+      <c r="A46" s="711" t="n">
         <v>200</v>
       </c>
       <c r="B46" s="185" t="n"/>
-      <c r="C46" s="711">
+      <c r="C46" s="712">
         <f>IF(B46="","",IF('Load Log'!$G$7="0.1 Mil",B46*10,IF('Load Log'!$G$7="0.05 Mil",B46*20,"")))</f>
         <v/>
       </c>
       <c r="D46" s="185" t="n"/>
-      <c r="E46" s="711">
+      <c r="E46" s="712">
         <f>IF(D46="","",IF('Load Log'!$G$7="1/4 MOA",D46*4,IF('Load Log'!$G$7="1/8 MOA",D46*8,"")))</f>
         <v/>
       </c>
       <c r="F46" s="185" t="n"/>
-      <c r="G46" s="711">
+      <c r="G46" s="712">
         <f>IF(F46="","",IF('Load Log'!$G$7="0.1 Mil",F46*10,IF('Load Log'!$G$7="0.05 Mil",F46*20,"")))</f>
         <v/>
       </c>
       <c r="H46" s="185" t="n"/>
-      <c r="I46" s="711">
+      <c r="I46" s="712">
         <f>IF(H46="","",IF('Load Log'!$G$7="1/4 MOA",H46*4,IF('Load Log'!$G$7="1/8 MOA",H46*8,"")))</f>
         <v/>
       </c>
@@ -26905,26 +26921,26 @@
       <c r="K46" s="277" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1" s="141">
-      <c r="A47" s="708" t="n">
+      <c r="A47" s="709" t="n">
         <v>300</v>
       </c>
       <c r="B47" s="178" t="n"/>
-      <c r="C47" s="709">
+      <c r="C47" s="710">
         <f>IF(B47="","",IF('Load Log'!$G$7="0.1 Mil",B47*10,IF('Load Log'!$G$7="0.05 Mil",B47*20,"")))</f>
         <v/>
       </c>
       <c r="D47" s="178" t="n"/>
-      <c r="E47" s="709">
+      <c r="E47" s="710">
         <f>IF(D47="","",IF('Load Log'!$G$7="1/4 MOA",D47*4,IF('Load Log'!$G$7="1/8 MOA",D47*8,"")))</f>
         <v/>
       </c>
       <c r="F47" s="178" t="n"/>
-      <c r="G47" s="709">
+      <c r="G47" s="710">
         <f>IF(F47="","",IF('Load Log'!$G$7="0.1 Mil",F47*10,IF('Load Log'!$G$7="0.05 Mil",F47*20,"")))</f>
         <v/>
       </c>
       <c r="H47" s="178" t="n"/>
-      <c r="I47" s="709">
+      <c r="I47" s="710">
         <f>IF(H47="","",IF('Load Log'!$G$7="1/4 MOA",H47*4,IF('Load Log'!$G$7="1/8 MOA",H47*8,"")))</f>
         <v/>
       </c>
@@ -26932,26 +26948,26 @@
       <c r="K47" s="276" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1" s="141">
-      <c r="A48" s="710" t="n">
+      <c r="A48" s="711" t="n">
         <v>400</v>
       </c>
       <c r="B48" s="185" t="n"/>
-      <c r="C48" s="711">
+      <c r="C48" s="712">
         <f>IF(B48="","",IF('Load Log'!$G$7="0.1 Mil",B48*10,IF('Load Log'!$G$7="0.05 Mil",B48*20,"")))</f>
         <v/>
       </c>
       <c r="D48" s="185" t="n"/>
-      <c r="E48" s="711">
+      <c r="E48" s="712">
         <f>IF(D48="","",IF('Load Log'!$G$7="1/4 MOA",D48*4,IF('Load Log'!$G$7="1/8 MOA",D48*8,"")))</f>
         <v/>
       </c>
       <c r="F48" s="185" t="n"/>
-      <c r="G48" s="711">
+      <c r="G48" s="712">
         <f>IF(F48="","",IF('Load Log'!$G$7="0.1 Mil",F48*10,IF('Load Log'!$G$7="0.05 Mil",F48*20,"")))</f>
         <v/>
       </c>
       <c r="H48" s="185" t="n"/>
-      <c r="I48" s="711">
+      <c r="I48" s="712">
         <f>IF(H48="","",IF('Load Log'!$G$7="1/4 MOA",H48*4,IF('Load Log'!$G$7="1/8 MOA",H48*8,"")))</f>
         <v/>
       </c>
@@ -26959,26 +26975,26 @@
       <c r="K48" s="277" t="n"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" s="141">
-      <c r="A49" s="708" t="n">
+      <c r="A49" s="709" t="n">
         <v>500</v>
       </c>
       <c r="B49" s="178" t="n"/>
-      <c r="C49" s="709">
+      <c r="C49" s="710">
         <f>IF(B49="","",IF('Load Log'!$G$7="0.1 Mil",B49*10,IF('Load Log'!$G$7="0.05 Mil",B49*20,"")))</f>
         <v/>
       </c>
       <c r="D49" s="178" t="n"/>
-      <c r="E49" s="709">
+      <c r="E49" s="710">
         <f>IF(D49="","",IF('Load Log'!$G$7="1/4 MOA",D49*4,IF('Load Log'!$G$7="1/8 MOA",D49*8,"")))</f>
         <v/>
       </c>
       <c r="F49" s="178" t="n"/>
-      <c r="G49" s="709">
+      <c r="G49" s="710">
         <f>IF(F49="","",IF('Load Log'!$G$7="0.1 Mil",F49*10,IF('Load Log'!$G$7="0.05 Mil",F49*20,"")))</f>
         <v/>
       </c>
       <c r="H49" s="178" t="n"/>
-      <c r="I49" s="709">
+      <c r="I49" s="710">
         <f>IF(H49="","",IF('Load Log'!$G$7="1/4 MOA",H49*4,IF('Load Log'!$G$7="1/8 MOA",H49*8,"")))</f>
         <v/>
       </c>
@@ -26986,26 +27002,26 @@
       <c r="K49" s="276" t="n"/>
     </row>
     <row r="50" ht="18.75" customHeight="1" s="141">
-      <c r="A50" s="710" t="n">
+      <c r="A50" s="711" t="n">
         <v>600</v>
       </c>
       <c r="B50" s="185" t="n"/>
-      <c r="C50" s="711">
+      <c r="C50" s="712">
         <f>IF(B50="","",IF('Load Log'!$G$7="0.1 Mil",B50*10,IF('Load Log'!$G$7="0.05 Mil",B50*20,"")))</f>
         <v/>
       </c>
       <c r="D50" s="185" t="n"/>
-      <c r="E50" s="711">
+      <c r="E50" s="712">
         <f>IF(D50="","",IF('Load Log'!$G$7="1/4 MOA",D50*4,IF('Load Log'!$G$7="1/8 MOA",D50*8,"")))</f>
         <v/>
       </c>
       <c r="F50" s="185" t="n"/>
-      <c r="G50" s="711">
+      <c r="G50" s="712">
         <f>IF(F50="","",IF('Load Log'!$G$7="0.1 Mil",F50*10,IF('Load Log'!$G$7="0.05 Mil",F50*20,"")))</f>
         <v/>
       </c>
       <c r="H50" s="185" t="n"/>
-      <c r="I50" s="711">
+      <c r="I50" s="712">
         <f>IF(H50="","",IF('Load Log'!$G$7="1/4 MOA",H50*4,IF('Load Log'!$G$7="1/8 MOA",H50*8,"")))</f>
         <v/>
       </c>
@@ -27013,26 +27029,26 @@
       <c r="K50" s="277" t="n"/>
     </row>
     <row r="51" ht="18.75" customHeight="1" s="141">
-      <c r="A51" s="708" t="n">
+      <c r="A51" s="709" t="n">
         <v>700</v>
       </c>
       <c r="B51" s="178" t="n"/>
-      <c r="C51" s="709">
+      <c r="C51" s="710">
         <f>IF(B51="","",IF('Load Log'!$G$7="0.1 Mil",B51*10,IF('Load Log'!$G$7="0.05 Mil",B51*20,"")))</f>
         <v/>
       </c>
       <c r="D51" s="178" t="n"/>
-      <c r="E51" s="709">
+      <c r="E51" s="710">
         <f>IF(D51="","",IF('Load Log'!$G$7="1/4 MOA",D51*4,IF('Load Log'!$G$7="1/8 MOA",D51*8,"")))</f>
         <v/>
       </c>
       <c r="F51" s="178" t="n"/>
-      <c r="G51" s="709">
+      <c r="G51" s="710">
         <f>IF(F51="","",IF('Load Log'!$G$7="0.1 Mil",F51*10,IF('Load Log'!$G$7="0.05 Mil",F51*20,"")))</f>
         <v/>
       </c>
       <c r="H51" s="178" t="n"/>
-      <c r="I51" s="709">
+      <c r="I51" s="710">
         <f>IF(H51="","",IF('Load Log'!$G$7="1/4 MOA",H51*4,IF('Load Log'!$G$7="1/8 MOA",H51*8,"")))</f>
         <v/>
       </c>
@@ -27040,26 +27056,26 @@
       <c r="K51" s="276" t="n"/>
     </row>
     <row r="52" ht="18.75" customHeight="1" s="141">
-      <c r="A52" s="710" t="n">
+      <c r="A52" s="711" t="n">
         <v>800</v>
       </c>
       <c r="B52" s="185" t="n"/>
-      <c r="C52" s="711">
+      <c r="C52" s="712">
         <f>IF(B52="","",IF('Load Log'!$G$7="0.1 Mil",B52*10,IF('Load Log'!$G$7="0.05 Mil",B52*20,"")))</f>
         <v/>
       </c>
       <c r="D52" s="185" t="n"/>
-      <c r="E52" s="711">
+      <c r="E52" s="712">
         <f>IF(D52="","",IF('Load Log'!$G$7="1/4 MOA",D52*4,IF('Load Log'!$G$7="1/8 MOA",D52*8,"")))</f>
         <v/>
       </c>
       <c r="F52" s="185" t="n"/>
-      <c r="G52" s="711">
+      <c r="G52" s="712">
         <f>IF(F52="","",IF('Load Log'!$G$7="0.1 Mil",F52*10,IF('Load Log'!$G$7="0.05 Mil",F52*20,"")))</f>
         <v/>
       </c>
       <c r="H52" s="185" t="n"/>
-      <c r="I52" s="711">
+      <c r="I52" s="712">
         <f>IF(H52="","",IF('Load Log'!$G$7="1/4 MOA",H52*4,IF('Load Log'!$G$7="1/8 MOA",H52*8,"")))</f>
         <v/>
       </c>
@@ -27067,26 +27083,26 @@
       <c r="K52" s="277" t="n"/>
     </row>
     <row r="53" ht="18.75" customHeight="1" s="141">
-      <c r="A53" s="708" t="n">
+      <c r="A53" s="709" t="n">
         <v>900</v>
       </c>
       <c r="B53" s="178" t="n"/>
-      <c r="C53" s="709">
+      <c r="C53" s="710">
         <f>IF(B53="","",IF('Load Log'!$G$7="0.1 Mil",B53*10,IF('Load Log'!$G$7="0.05 Mil",B53*20,"")))</f>
         <v/>
       </c>
       <c r="D53" s="178" t="n"/>
-      <c r="E53" s="709">
+      <c r="E53" s="710">
         <f>IF(D53="","",IF('Load Log'!$G$7="1/4 MOA",D53*4,IF('Load Log'!$G$7="1/8 MOA",D53*8,"")))</f>
         <v/>
       </c>
       <c r="F53" s="178" t="n"/>
-      <c r="G53" s="709">
+      <c r="G53" s="710">
         <f>IF(F53="","",IF('Load Log'!$G$7="0.1 Mil",F53*10,IF('Load Log'!$G$7="0.05 Mil",F53*20,"")))</f>
         <v/>
       </c>
       <c r="H53" s="178" t="n"/>
-      <c r="I53" s="709">
+      <c r="I53" s="710">
         <f>IF(H53="","",IF('Load Log'!$G$7="1/4 MOA",H53*4,IF('Load Log'!$G$7="1/8 MOA",H53*8,"")))</f>
         <v/>
       </c>
@@ -27094,26 +27110,26 @@
       <c r="K53" s="276" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1" s="141">
-      <c r="A54" s="710" t="n">
+      <c r="A54" s="711" t="n">
         <v>1000</v>
       </c>
       <c r="B54" s="185" t="n"/>
-      <c r="C54" s="711">
+      <c r="C54" s="712">
         <f>IF(B54="","",IF('Load Log'!$G$7="0.1 Mil",B54*10,IF('Load Log'!$G$7="0.05 Mil",B54*20,"")))</f>
         <v/>
       </c>
       <c r="D54" s="185" t="n"/>
-      <c r="E54" s="711">
+      <c r="E54" s="712">
         <f>IF(D54="","",IF('Load Log'!$G$7="1/4 MOA",D54*4,IF('Load Log'!$G$7="1/8 MOA",D54*8,"")))</f>
         <v/>
       </c>
       <c r="F54" s="185" t="n"/>
-      <c r="G54" s="711">
+      <c r="G54" s="712">
         <f>IF(F54="","",IF('Load Log'!$G$7="0.1 Mil",F54*10,IF('Load Log'!$G$7="0.05 Mil",F54*20,"")))</f>
         <v/>
       </c>
       <c r="H54" s="185" t="n"/>
-      <c r="I54" s="711">
+      <c r="I54" s="712">
         <f>IF(H54="","",IF('Load Log'!$G$7="1/4 MOA",H54*4,IF('Load Log'!$G$7="1/8 MOA",H54*8,"")))</f>
         <v/>
       </c>
@@ -27124,7 +27140,7 @@
     <row r="56"/>
     <row r="57"/>
     <row r="58" ht="24" customHeight="1" s="141">
-      <c r="A58" s="712">
+      <c r="A58" s="713">
         <f>IF(IFERROR('Load Library'!C8,"")="","LOAD #4  —  (empty — fill in Load Library row 8)","LOAD #4  —  "&amp;'Load Library'!C8)</f>
         <v/>
       </c>
@@ -27135,7 +27151,7 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B59" s="705">
+      <c r="B59" s="706">
         <f>IF(IFERROR('Load Library'!D8,"")="","",'Load Library'!D8)</f>
         <v/>
       </c>
@@ -27145,7 +27161,7 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E59" s="705">
+      <c r="E59" s="706">
         <f>IF(IFERROR('Load Library'!E8,"")="","",'Load Library'!E8&amp;" ("&amp;'Load Library'!F8&amp;"gr)")</f>
         <v/>
       </c>
@@ -27155,7 +27171,7 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H59" s="705">
+      <c r="H59" s="706">
         <f>IF(IFERROR('Load Library'!H8,"")="","",'Load Library'!H8&amp;" gr "&amp;'Load Library'!G8)</f>
         <v/>
       </c>
@@ -27165,7 +27181,7 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K59" s="705">
+      <c r="K59" s="706">
         <f>IF(IFERROR('Load Library'!M8,"")="","",'Load Library'!M8&amp;" fps")</f>
         <v/>
       </c>
@@ -27266,26 +27282,26 @@
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1" s="141">
-      <c r="A63" s="708" t="n">
+      <c r="A63" s="709" t="n">
         <v>100</v>
       </c>
       <c r="B63" s="178" t="n"/>
-      <c r="C63" s="709">
+      <c r="C63" s="710">
         <f>IF(B63="","",IF('Load Log'!$G$7="0.1 Mil",B63*10,IF('Load Log'!$G$7="0.05 Mil",B63*20,"")))</f>
         <v/>
       </c>
       <c r="D63" s="178" t="n"/>
-      <c r="E63" s="709">
+      <c r="E63" s="710">
         <f>IF(D63="","",IF('Load Log'!$G$7="1/4 MOA",D63*4,IF('Load Log'!$G$7="1/8 MOA",D63*8,"")))</f>
         <v/>
       </c>
       <c r="F63" s="178" t="n"/>
-      <c r="G63" s="709">
+      <c r="G63" s="710">
         <f>IF(F63="","",IF('Load Log'!$G$7="0.1 Mil",F63*10,IF('Load Log'!$G$7="0.05 Mil",F63*20,"")))</f>
         <v/>
       </c>
       <c r="H63" s="178" t="n"/>
-      <c r="I63" s="709">
+      <c r="I63" s="710">
         <f>IF(H63="","",IF('Load Log'!$G$7="1/4 MOA",H63*4,IF('Load Log'!$G$7="1/8 MOA",H63*8,"")))</f>
         <v/>
       </c>
@@ -27293,26 +27309,26 @@
       <c r="K63" s="276" t="n"/>
     </row>
     <row r="64" ht="18.75" customHeight="1" s="141">
-      <c r="A64" s="710" t="n">
+      <c r="A64" s="711" t="n">
         <v>200</v>
       </c>
       <c r="B64" s="185" t="n"/>
-      <c r="C64" s="711">
+      <c r="C64" s="712">
         <f>IF(B64="","",IF('Load Log'!$G$7="0.1 Mil",B64*10,IF('Load Log'!$G$7="0.05 Mil",B64*20,"")))</f>
         <v/>
       </c>
       <c r="D64" s="185" t="n"/>
-      <c r="E64" s="711">
+      <c r="E64" s="712">
         <f>IF(D64="","",IF('Load Log'!$G$7="1/4 MOA",D64*4,IF('Load Log'!$G$7="1/8 MOA",D64*8,"")))</f>
         <v/>
       </c>
       <c r="F64" s="185" t="n"/>
-      <c r="G64" s="711">
+      <c r="G64" s="712">
         <f>IF(F64="","",IF('Load Log'!$G$7="0.1 Mil",F64*10,IF('Load Log'!$G$7="0.05 Mil",F64*20,"")))</f>
         <v/>
       </c>
       <c r="H64" s="185" t="n"/>
-      <c r="I64" s="711">
+      <c r="I64" s="712">
         <f>IF(H64="","",IF('Load Log'!$G$7="1/4 MOA",H64*4,IF('Load Log'!$G$7="1/8 MOA",H64*8,"")))</f>
         <v/>
       </c>
@@ -27320,26 +27336,26 @@
       <c r="K64" s="277" t="n"/>
     </row>
     <row r="65" ht="18.75" customHeight="1" s="141">
-      <c r="A65" s="708" t="n">
+      <c r="A65" s="709" t="n">
         <v>300</v>
       </c>
       <c r="B65" s="178" t="n"/>
-      <c r="C65" s="709">
+      <c r="C65" s="710">
         <f>IF(B65="","",IF('Load Log'!$G$7="0.1 Mil",B65*10,IF('Load Log'!$G$7="0.05 Mil",B65*20,"")))</f>
         <v/>
       </c>
       <c r="D65" s="178" t="n"/>
-      <c r="E65" s="709">
+      <c r="E65" s="710">
         <f>IF(D65="","",IF('Load Log'!$G$7="1/4 MOA",D65*4,IF('Load Log'!$G$7="1/8 MOA",D65*8,"")))</f>
         <v/>
       </c>
       <c r="F65" s="178" t="n"/>
-      <c r="G65" s="709">
+      <c r="G65" s="710">
         <f>IF(F65="","",IF('Load Log'!$G$7="0.1 Mil",F65*10,IF('Load Log'!$G$7="0.05 Mil",F65*20,"")))</f>
         <v/>
       </c>
       <c r="H65" s="178" t="n"/>
-      <c r="I65" s="709">
+      <c r="I65" s="710">
         <f>IF(H65="","",IF('Load Log'!$G$7="1/4 MOA",H65*4,IF('Load Log'!$G$7="1/8 MOA",H65*8,"")))</f>
         <v/>
       </c>
@@ -27347,26 +27363,26 @@
       <c r="K65" s="276" t="n"/>
     </row>
     <row r="66" ht="18.75" customHeight="1" s="141">
-      <c r="A66" s="710" t="n">
+      <c r="A66" s="711" t="n">
         <v>400</v>
       </c>
       <c r="B66" s="185" t="n"/>
-      <c r="C66" s="711">
+      <c r="C66" s="712">
         <f>IF(B66="","",IF('Load Log'!$G$7="0.1 Mil",B66*10,IF('Load Log'!$G$7="0.05 Mil",B66*20,"")))</f>
         <v/>
       </c>
       <c r="D66" s="185" t="n"/>
-      <c r="E66" s="711">
+      <c r="E66" s="712">
         <f>IF(D66="","",IF('Load Log'!$G$7="1/4 MOA",D66*4,IF('Load Log'!$G$7="1/8 MOA",D66*8,"")))</f>
         <v/>
       </c>
       <c r="F66" s="185" t="n"/>
-      <c r="G66" s="711">
+      <c r="G66" s="712">
         <f>IF(F66="","",IF('Load Log'!$G$7="0.1 Mil",F66*10,IF('Load Log'!$G$7="0.05 Mil",F66*20,"")))</f>
         <v/>
       </c>
       <c r="H66" s="185" t="n"/>
-      <c r="I66" s="711">
+      <c r="I66" s="712">
         <f>IF(H66="","",IF('Load Log'!$G$7="1/4 MOA",H66*4,IF('Load Log'!$G$7="1/8 MOA",H66*8,"")))</f>
         <v/>
       </c>
@@ -27374,26 +27390,26 @@
       <c r="K66" s="277" t="n"/>
     </row>
     <row r="67" ht="18.75" customHeight="1" s="141">
-      <c r="A67" s="708" t="n">
+      <c r="A67" s="709" t="n">
         <v>500</v>
       </c>
       <c r="B67" s="178" t="n"/>
-      <c r="C67" s="709">
+      <c r="C67" s="710">
         <f>IF(B67="","",IF('Load Log'!$G$7="0.1 Mil",B67*10,IF('Load Log'!$G$7="0.05 Mil",B67*20,"")))</f>
         <v/>
       </c>
       <c r="D67" s="178" t="n"/>
-      <c r="E67" s="709">
+      <c r="E67" s="710">
         <f>IF(D67="","",IF('Load Log'!$G$7="1/4 MOA",D67*4,IF('Load Log'!$G$7="1/8 MOA",D67*8,"")))</f>
         <v/>
       </c>
       <c r="F67" s="178" t="n"/>
-      <c r="G67" s="709">
+      <c r="G67" s="710">
         <f>IF(F67="","",IF('Load Log'!$G$7="0.1 Mil",F67*10,IF('Load Log'!$G$7="0.05 Mil",F67*20,"")))</f>
         <v/>
       </c>
       <c r="H67" s="178" t="n"/>
-      <c r="I67" s="709">
+      <c r="I67" s="710">
         <f>IF(H67="","",IF('Load Log'!$G$7="1/4 MOA",H67*4,IF('Load Log'!$G$7="1/8 MOA",H67*8,"")))</f>
         <v/>
       </c>
@@ -27401,26 +27417,26 @@
       <c r="K67" s="276" t="n"/>
     </row>
     <row r="68" ht="18.75" customHeight="1" s="141">
-      <c r="A68" s="710" t="n">
+      <c r="A68" s="711" t="n">
         <v>600</v>
       </c>
       <c r="B68" s="185" t="n"/>
-      <c r="C68" s="711">
+      <c r="C68" s="712">
         <f>IF(B68="","",IF('Load Log'!$G$7="0.1 Mil",B68*10,IF('Load Log'!$G$7="0.05 Mil",B68*20,"")))</f>
         <v/>
       </c>
       <c r="D68" s="185" t="n"/>
-      <c r="E68" s="711">
+      <c r="E68" s="712">
         <f>IF(D68="","",IF('Load Log'!$G$7="1/4 MOA",D68*4,IF('Load Log'!$G$7="1/8 MOA",D68*8,"")))</f>
         <v/>
       </c>
       <c r="F68" s="185" t="n"/>
-      <c r="G68" s="711">
+      <c r="G68" s="712">
         <f>IF(F68="","",IF('Load Log'!$G$7="0.1 Mil",F68*10,IF('Load Log'!$G$7="0.05 Mil",F68*20,"")))</f>
         <v/>
       </c>
       <c r="H68" s="185" t="n"/>
-      <c r="I68" s="711">
+      <c r="I68" s="712">
         <f>IF(H68="","",IF('Load Log'!$G$7="1/4 MOA",H68*4,IF('Load Log'!$G$7="1/8 MOA",H68*8,"")))</f>
         <v/>
       </c>
@@ -27428,26 +27444,26 @@
       <c r="K68" s="277" t="n"/>
     </row>
     <row r="69" ht="18.75" customHeight="1" s="141">
-      <c r="A69" s="708" t="n">
+      <c r="A69" s="709" t="n">
         <v>700</v>
       </c>
       <c r="B69" s="178" t="n"/>
-      <c r="C69" s="709">
+      <c r="C69" s="710">
         <f>IF(B69="","",IF('Load Log'!$G$7="0.1 Mil",B69*10,IF('Load Log'!$G$7="0.05 Mil",B69*20,"")))</f>
         <v/>
       </c>
       <c r="D69" s="178" t="n"/>
-      <c r="E69" s="709">
+      <c r="E69" s="710">
         <f>IF(D69="","",IF('Load Log'!$G$7="1/4 MOA",D69*4,IF('Load Log'!$G$7="1/8 MOA",D69*8,"")))</f>
         <v/>
       </c>
       <c r="F69" s="178" t="n"/>
-      <c r="G69" s="709">
+      <c r="G69" s="710">
         <f>IF(F69="","",IF('Load Log'!$G$7="0.1 Mil",F69*10,IF('Load Log'!$G$7="0.05 Mil",F69*20,"")))</f>
         <v/>
       </c>
       <c r="H69" s="178" t="n"/>
-      <c r="I69" s="709">
+      <c r="I69" s="710">
         <f>IF(H69="","",IF('Load Log'!$G$7="1/4 MOA",H69*4,IF('Load Log'!$G$7="1/8 MOA",H69*8,"")))</f>
         <v/>
       </c>
@@ -27455,26 +27471,26 @@
       <c r="K69" s="276" t="n"/>
     </row>
     <row r="70" ht="18.75" customHeight="1" s="141">
-      <c r="A70" s="710" t="n">
+      <c r="A70" s="711" t="n">
         <v>800</v>
       </c>
       <c r="B70" s="185" t="n"/>
-      <c r="C70" s="711">
+      <c r="C70" s="712">
         <f>IF(B70="","",IF('Load Log'!$G$7="0.1 Mil",B70*10,IF('Load Log'!$G$7="0.05 Mil",B70*20,"")))</f>
         <v/>
       </c>
       <c r="D70" s="185" t="n"/>
-      <c r="E70" s="711">
+      <c r="E70" s="712">
         <f>IF(D70="","",IF('Load Log'!$G$7="1/4 MOA",D70*4,IF('Load Log'!$G$7="1/8 MOA",D70*8,"")))</f>
         <v/>
       </c>
       <c r="F70" s="185" t="n"/>
-      <c r="G70" s="711">
+      <c r="G70" s="712">
         <f>IF(F70="","",IF('Load Log'!$G$7="0.1 Mil",F70*10,IF('Load Log'!$G$7="0.05 Mil",F70*20,"")))</f>
         <v/>
       </c>
       <c r="H70" s="185" t="n"/>
-      <c r="I70" s="711">
+      <c r="I70" s="712">
         <f>IF(H70="","",IF('Load Log'!$G$7="1/4 MOA",H70*4,IF('Load Log'!$G$7="1/8 MOA",H70*8,"")))</f>
         <v/>
       </c>
@@ -27482,26 +27498,26 @@
       <c r="K70" s="277" t="n"/>
     </row>
     <row r="71" ht="18.75" customHeight="1" s="141">
-      <c r="A71" s="708" t="n">
+      <c r="A71" s="709" t="n">
         <v>900</v>
       </c>
       <c r="B71" s="178" t="n"/>
-      <c r="C71" s="709">
+      <c r="C71" s="710">
         <f>IF(B71="","",IF('Load Log'!$G$7="0.1 Mil",B71*10,IF('Load Log'!$G$7="0.05 Mil",B71*20,"")))</f>
         <v/>
       </c>
       <c r="D71" s="178" t="n"/>
-      <c r="E71" s="709">
+      <c r="E71" s="710">
         <f>IF(D71="","",IF('Load Log'!$G$7="1/4 MOA",D71*4,IF('Load Log'!$G$7="1/8 MOA",D71*8,"")))</f>
         <v/>
       </c>
       <c r="F71" s="178" t="n"/>
-      <c r="G71" s="709">
+      <c r="G71" s="710">
         <f>IF(F71="","",IF('Load Log'!$G$7="0.1 Mil",F71*10,IF('Load Log'!$G$7="0.05 Mil",F71*20,"")))</f>
         <v/>
       </c>
       <c r="H71" s="178" t="n"/>
-      <c r="I71" s="709">
+      <c r="I71" s="710">
         <f>IF(H71="","",IF('Load Log'!$G$7="1/4 MOA",H71*4,IF('Load Log'!$G$7="1/8 MOA",H71*8,"")))</f>
         <v/>
       </c>
@@ -27509,26 +27525,26 @@
       <c r="K71" s="276" t="n"/>
     </row>
     <row r="72" ht="18.75" customHeight="1" s="141">
-      <c r="A72" s="710" t="n">
+      <c r="A72" s="711" t="n">
         <v>1000</v>
       </c>
       <c r="B72" s="185" t="n"/>
-      <c r="C72" s="711">
+      <c r="C72" s="712">
         <f>IF(B72="","",IF('Load Log'!$G$7="0.1 Mil",B72*10,IF('Load Log'!$G$7="0.05 Mil",B72*20,"")))</f>
         <v/>
       </c>
       <c r="D72" s="185" t="n"/>
-      <c r="E72" s="711">
+      <c r="E72" s="712">
         <f>IF(D72="","",IF('Load Log'!$G$7="1/4 MOA",D72*4,IF('Load Log'!$G$7="1/8 MOA",D72*8,"")))</f>
         <v/>
       </c>
       <c r="F72" s="185" t="n"/>
-      <c r="G72" s="711">
+      <c r="G72" s="712">
         <f>IF(F72="","",IF('Load Log'!$G$7="0.1 Mil",F72*10,IF('Load Log'!$G$7="0.05 Mil",F72*20,"")))</f>
         <v/>
       </c>
       <c r="H72" s="185" t="n"/>
-      <c r="I72" s="711">
+      <c r="I72" s="712">
         <f>IF(H72="","",IF('Load Log'!$G$7="1/4 MOA",H72*4,IF('Load Log'!$G$7="1/8 MOA",H72*8,"")))</f>
         <v/>
       </c>
@@ -27539,7 +27555,7 @@
     <row r="74"/>
     <row r="75"/>
     <row r="76" ht="24" customHeight="1" s="141">
-      <c r="A76" s="712">
+      <c r="A76" s="713">
         <f>IF(IFERROR('Load Library'!C9,"")="","LOAD #5  —  (empty — fill in Load Library row 9)","LOAD #5  —  "&amp;'Load Library'!C9)</f>
         <v/>
       </c>
@@ -27550,7 +27566,7 @@
           <t>Rifle:</t>
         </is>
       </c>
-      <c r="B77" s="705">
+      <c r="B77" s="706">
         <f>IF(IFERROR('Load Library'!D9,"")="","",'Load Library'!D9)</f>
         <v/>
       </c>
@@ -27560,7 +27576,7 @@
           <t>Bullet:</t>
         </is>
       </c>
-      <c r="E77" s="705">
+      <c r="E77" s="706">
         <f>IF(IFERROR('Load Library'!E9,"")="","",'Load Library'!E9&amp;" ("&amp;'Load Library'!F9&amp;"gr)")</f>
         <v/>
       </c>
@@ -27570,7 +27586,7 @@
           <t>Charge:</t>
         </is>
       </c>
-      <c r="H77" s="705">
+      <c r="H77" s="706">
         <f>IF(IFERROR('Load Library'!H9,"")="","",'Load Library'!H9&amp;" gr "&amp;'Load Library'!G9)</f>
         <v/>
       </c>
@@ -27580,7 +27596,7 @@
           <t>Vel:</t>
         </is>
       </c>
-      <c r="K77" s="705">
+      <c r="K77" s="706">
         <f>IF(IFERROR('Load Library'!M9,"")="","",'Load Library'!M9&amp;" fps")</f>
         <v/>
       </c>
@@ -27681,26 +27697,26 @@
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1" s="141">
-      <c r="A81" s="708" t="n">
+      <c r="A81" s="709" t="n">
         <v>100</v>
       </c>
       <c r="B81" s="178" t="n"/>
-      <c r="C81" s="709">
+      <c r="C81" s="710">
         <f>IF(B81="","",IF('Load Log'!$G$7="0.1 Mil",B81*10,IF('Load Log'!$G$7="0.05 Mil",B81*20,"")))</f>
         <v/>
       </c>
       <c r="D81" s="178" t="n"/>
-      <c r="E81" s="709">
+      <c r="E81" s="710">
         <f>IF(D81="","",IF('Load Log'!$G$7="1/4 MOA",D81*4,IF('Load Log'!$G$7="1/8 MOA",D81*8,"")))</f>
         <v/>
       </c>
       <c r="F81" s="178" t="n"/>
-      <c r="G81" s="709">
+      <c r="G81" s="710">
         <f>IF(F81="","",IF('Load Log'!$G$7="0.1 Mil",F81*10,IF('Load Log'!$G$7="0.05 Mil",F81*20,"")))</f>
         <v/>
       </c>
       <c r="H81" s="178" t="n"/>
-      <c r="I81" s="709">
+      <c r="I81" s="710">
         <f>IF(H81="","",IF('Load Log'!$G$7="1/4 MOA",H81*4,IF('Load Log'!$G$7="1/8 MOA",H81*8,"")))</f>
         <v/>
       </c>
@@ -27708,26 +27724,26 @@
       <c r="K81" s="276" t="n"/>
     </row>
     <row r="82" ht="18.75" customHeight="1" s="141">
-      <c r="A82" s="710" t="n">
+      <c r="A82" s="711" t="n">
         <v>200</v>
       </c>
       <c r="B82" s="185" t="n"/>
-      <c r="C82" s="711">
+      <c r="C82" s="712">
         <f>IF(B82="","",IF('Load Log'!$G$7="0.1 Mil",B82*10,IF('Load Log'!$G$7="0.05 Mil",B82*20,"")))</f>
         <v/>
       </c>
       <c r="D82" s="185" t="n"/>
-      <c r="E82" s="711">
+      <c r="E82" s="712">
         <f>IF(D82="","",IF('Load Log'!$G$7="1/4 MOA",D82*4,IF('Load Log'!$G$7="1/8 MOA",D82*8,"")))</f>
         <v/>
       </c>
       <c r="F82" s="185" t="n"/>
-      <c r="G82" s="711">
+      <c r="G82" s="712">
         <f>IF(F82="","",IF('Load Log'!$G$7="0.1 Mil",F82*10,IF('Load Log'!$G$7="0.05 Mil",F82*20,"")))</f>
         <v/>
       </c>
       <c r="H82" s="185" t="n"/>
-      <c r="I82" s="711">
+      <c r="I82" s="712">
         <f>IF(H82="","",IF('Load Log'!$G$7="1/4 MOA",H82*4,IF('Load Log'!$G$7="1/8 MOA",H82*8,"")))</f>
         <v/>
       </c>
@@ -27735,26 +27751,26 @@
       <c r="K82" s="277" t="n"/>
     </row>
     <row r="83" ht="18.75" customHeight="1" s="141">
-      <c r="A83" s="708" t="n">
+      <c r="A83" s="709" t="n">
         <v>300</v>
       </c>
       <c r="B83" s="178" t="n"/>
-      <c r="C83" s="709">
+      <c r="C83" s="710">
         <f>IF(B83="","",IF('Load Log'!$G$7="0.1 Mil",B83*10,IF('Load Log'!$G$7="0.05 Mil",B83*20,"")))</f>
         <v/>
       </c>
       <c r="D83" s="178" t="n"/>
-      <c r="E83" s="709">
+      <c r="E83" s="710">
         <f>IF(D83="","",IF('Load Log'!$G$7="1/4 MOA",D83*4,IF('Load Log'!$G$7="1/8 MOA",D83*8,"")))</f>
         <v/>
       </c>
       <c r="F83" s="178" t="n"/>
-      <c r="G83" s="709">
+      <c r="G83" s="710">
         <f>IF(F83="","",IF('Load Log'!$G$7="0.1 Mil",F83*10,IF('Load Log'!$G$7="0.05 Mil",F83*20,"")))</f>
         <v/>
       </c>
       <c r="H83" s="178" t="n"/>
-      <c r="I83" s="709">
+      <c r="I83" s="710">
         <f>IF(H83="","",IF('Load Log'!$G$7="1/4 MOA",H83*4,IF('Load Log'!$G$7="1/8 MOA",H83*8,"")))</f>
         <v/>
       </c>
@@ -27762,26 +27778,26 @@
       <c r="K83" s="276" t="n"/>
     </row>
     <row r="84" ht="18.75" customHeight="1" s="141">
-      <c r="A84" s="710" t="n">
+      <c r="A84" s="711" t="n">
         <v>400</v>
       </c>
       <c r="B84" s="185" t="n"/>
-      <c r="C84" s="711">
+      <c r="C84" s="712">
         <f>IF(B84="","",IF('Load Log'!$G$7="0.1 Mil",B84*10,IF('Load Log'!$G$7="0.05 Mil",B84*20,"")))</f>
         <v/>
       </c>
       <c r="D84" s="185" t="n"/>
-      <c r="E84" s="711">
+      <c r="E84" s="712">
         <f>IF(D84="","",IF('Load Log'!$G$7="1/4 MOA",D84*4,IF('Load Log'!$G$7="1/8 MOA",D84*8,"")))</f>
         <v/>
       </c>
       <c r="F84" s="185" t="n"/>
-      <c r="G84" s="711">
+      <c r="G84" s="712">
         <f>IF(F84="","",IF('Load Log'!$G$7="0.1 Mil",F84*10,IF('Load Log'!$G$7="0.05 Mil",F84*20,"")))</f>
         <v/>
       </c>
       <c r="H84" s="185" t="n"/>
-      <c r="I84" s="711">
+      <c r="I84" s="712">
         <f>IF(H84="","",IF('Load Log'!$G$7="1/4 MOA",H84*4,IF('Load Log'!$G$7="1/8 MOA",H84*8,"")))</f>
         <v/>
       </c>
@@ -27789,26 +27805,26 @@
       <c r="K84" s="277" t="n"/>
     </row>
     <row r="85" ht="18.75" customHeight="1" s="141">
-      <c r="A85" s="708" t="n">
+      <c r="A85" s="709" t="n">
         <v>500</v>
       </c>
       <c r="B85" s="178" t="n"/>
-      <c r="C85" s="709">
+      <c r="C85" s="710">
         <f>IF(B85="","",IF('Load Log'!$G$7="0.1 Mil",B85*10,IF('Load Log'!$G$7="0.05 Mil",B85*20,"")))</f>
         <v/>
       </c>
       <c r="D85" s="178" t="n"/>
-      <c r="E85" s="709">
+      <c r="E85" s="710">
         <f>IF(D85="","",IF('Load Log'!$G$7="1/4 MOA",D85*4,IF('Load Log'!$G$7="1/8 MOA",D85*8,"")))</f>
         <v/>
       </c>
       <c r="F85" s="178" t="n"/>
-      <c r="G85" s="709">
+      <c r="G85" s="710">
         <f>IF(F85="","",IF('Load Log'!$G$7="0.1 Mil",F85*10,IF('Load Log'!$G$7="0.05 Mil",F85*20,"")))</f>
         <v/>
       </c>
       <c r="H85" s="178" t="n"/>
-      <c r="I85" s="709">
+      <c r="I85" s="710">
         <f>IF(H85="","",IF('Load Log'!$G$7="1/4 MOA",H85*4,IF('Load Log'!$G$7="1/8 MOA",H85*8,"")))</f>
         <v/>
       </c>
@@ -27816,26 +27832,26 @@
       <c r="K85" s="276" t="n"/>
     </row>
     <row r="86" ht="18.75" customHeight="1" s="141">
-      <c r="A86" s="710" t="n">
+      <c r="A86" s="711" t="n">
         <v>600</v>
       </c>
       <c r="B86" s="185" t="n"/>
-      <c r="C86" s="711">
+      <c r="C86" s="712">
         <f>IF(B86="","",IF('Load Log'!$G$7="0.1 Mil",B86*10,IF('Load Log'!$G$7="0.05 Mil",B86*20,"")))</f>
         <v/>
       </c>
       <c r="D86" s="185" t="n"/>
-      <c r="E86" s="711">
+      <c r="E86" s="712">
         <f>IF(D86="","",IF('Load Log'!$G$7="1/4 MOA",D86*4,IF('Load Log'!$G$7="1/8 MOA",D86*8,"")))</f>
         <v/>
       </c>
       <c r="F86" s="185" t="n"/>
-      <c r="G86" s="711">
+      <c r="G86" s="712">
         <f>IF(F86="","",IF('Load Log'!$G$7="0.1 Mil",F86*10,IF('Load Log'!$G$7="0.05 Mil",F86*20,"")))</f>
         <v/>
       </c>
       <c r="H86" s="185" t="n"/>
-      <c r="I86" s="711">
+      <c r="I86" s="712">
         <f>IF(H86="","",IF('Load Log'!$G$7="1/4 MOA",H86*4,IF('Load Log'!$G$7="1/8 MOA",H86*8,"")))</f>
         <v/>
       </c>
@@ -27843,26 +27859,26 @@
       <c r="K86" s="277" t="n"/>
     </row>
     <row r="87" ht="18.75" customHeight="1" s="141">
-      <c r="A87" s="708" t="n">
+      <c r="A87" s="709" t="n">
         <v>700</v>
       </c>
       <c r="B87" s="178" t="n"/>
-      <c r="C87" s="709">
+      <c r="C87" s="710">
         <f>IF(B87="","",IF('Load Log'!$G$7="0.1 Mil",B87*10,IF('Load Log'!$G$7="0.05 Mil",B87*20,"")))</f>
         <v/>
       </c>
       <c r="D87" s="178" t="n"/>
-      <c r="E87" s="709">
+      <c r="E87" s="710">
         <f>IF(D87="","",IF('Load Log'!$G$7="1/4 MOA",D87*4,IF('Load Log'!$G$7="1/8 MOA",D87*8,"")))</f>
         <v/>
       </c>
       <c r="F87" s="178" t="n"/>
-      <c r="G87" s="709">
+      <c r="G87" s="710">
         <f>IF(F87="","",IF('Load Log'!$G$7="0.1 Mil",F87*10,IF('Load Log'!$G$7="0.05 Mil",F87*20,"")))</f>
         <v/>
       </c>
       <c r="H87" s="178" t="n"/>
-      <c r="I87" s="709">
+      <c r="I87" s="710">
         <f>IF(H87="","",IF('Load Log'!$G$7="1/4 MOA",H87*4,IF('Load Log'!$G$7="1/8 MOA",H87*8,"")))</f>
         <v/>
       </c>
@@ -27870,26 +27886,26 @@
       <c r="K87" s="276" t="n"/>
     </row>
     <row r="88" ht="18.75" customHeight="1" s="141">
-      <c r="A88" s="710" t="n">
+      <c r="A88" s="711" t="n">
         <v>800</v>
       </c>
       <c r="B88" s="185" t="n"/>
-      <c r="C88" s="711">
+      <c r="C88" s="712">
         <f>IF(B88="","",IF('Load Log'!$G$7="0.1 Mil",B88*10,IF('Load Log'!$G$7="0.05 Mil",B88*20,"")))</f>
         <v/>
       </c>
       <c r="D88" s="185" t="n"/>
-      <c r="E88" s="711">
+      <c r="E88" s="712">
         <f>IF(D88="","",IF('Load Log'!$G$7="1/4 MOA",D88*4,IF('Load Log'!$G$7="1/8 MOA",D88*8,"")))</f>
         <v/>
       </c>
       <c r="F88" s="185" t="n"/>
-      <c r="G88" s="711">
+      <c r="G88" s="712">
         <f>IF(F88="","",IF('Load Log'!$G$7="0.1 Mil",F88*10,IF('Load Log'!$G$7="0.05 Mil",F88*20,"")))</f>
         <v/>
       </c>
       <c r="H88" s="185" t="n"/>
-      <c r="I88" s="711">
+      <c r="I88" s="712">
         <f>IF(H88="","",IF('Load Log'!$G$7="1/4 MOA",H88*4,IF('Load Log'!$G$7="1/8 MOA",H88*8,"")))</f>
         <v/>
       </c>
@@ -27897,26 +27913,26 @@
       <c r="K88" s="277" t="n"/>
     </row>
     <row r="89" ht="18.75" customHeight="1" s="141">
-      <c r="A89" s="708" t="n">
+      <c r="A89" s="709" t="n">
         <v>900</v>
       </c>
       <c r="B89" s="178" t="n"/>
-      <c r="C89" s="709">
+      <c r="C89" s="710">
         <f>IF(B89="","",IF('Load Log'!$G$7="0.1 Mil",B89*10,IF('Load Log'!$G$7="0.05 Mil",B89*20,"")))</f>
         <v/>
       </c>
       <c r="D89" s="178" t="n"/>
-      <c r="E89" s="709">
+      <c r="E89" s="710">
         <f>IF(D89="","",IF('Load Log'!$G$7="1/4 MOA",D89*4,IF('Load Log'!$G$7="1/8 MOA",D89*8,"")))</f>
         <v/>
       </c>
       <c r="F89" s="178" t="n"/>
-      <c r="G89" s="709">
+      <c r="G89" s="710">
         <f>IF(F89="","",IF('Load Log'!$G$7="0.1 Mil",F89*10,IF('Load Log'!$G$7="0.05 Mil",F89*20,"")))</f>
         <v/>
       </c>
       <c r="H89" s="178" t="n"/>
-      <c r="I89" s="709">
+      <c r="I89" s="710">
         <f>IF(H89="","",IF('Load Log'!$G$7="1/4 MOA",H89*4,IF('Load Log'!$G$7="1/8 MOA",H89*8,"")))</f>
         <v/>
       </c>
@@ -27924,26 +27940,26 @@
       <c r="K89" s="276" t="n"/>
     </row>
     <row r="90" ht="18.75" customHeight="1" s="141">
-      <c r="A90" s="710" t="n">
+      <c r="A90" s="711" t="n">
         <v>1000</v>
       </c>
       <c r="B90" s="185" t="n"/>
-      <c r="C90" s="711">
+      <c r="C90" s="712">
         <f>IF(B90="","",IF('Load Log'!$G$7="0.1 Mil",B90*10,IF('Load Log'!$G$7="0.05 Mil",B90*20,"")))</f>
         <v/>
       </c>
       <c r="D90" s="185" t="n"/>
-      <c r="E90" s="711">
+      <c r="E90" s="712">
         <f>IF(D90="","",IF('Load Log'!$G$7="1/4 MOA",D90*4,IF('Load Log'!$G$7="1/8 MOA",D90*8,"")))</f>
         <v/>
       </c>
       <c r="F90" s="185" t="n"/>
-      <c r="G90" s="711">
+      <c r="G90" s="712">
         <f>IF(F90="","",IF('Load Log'!$G$7="0.1 Mil",F90*10,IF('Load Log'!$G$7="0.05 Mil",F90*20,"")))</f>
         <v/>
       </c>
       <c r="H90" s="185" t="n"/>
-      <c r="I90" s="711">
+      <c r="I90" s="712">
         <f>IF(H90="","",IF('Load Log'!$G$7="1/4 MOA",H90*4,IF('Load Log'!$G$7="1/8 MOA",H90*8,"")))</f>
         <v/>
       </c>
@@ -27967,6 +27983,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" display="Print Pocket Range Card" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
